--- a/01 Proyecto_Mercado_Mayorista/02 Excel Maestro/MAESTRO_Mercado_Mayorista_v1.xlsx
+++ b/01 Proyecto_Mercado_Mayorista/02 Excel Maestro/MAESTRO_Mercado_Mayorista_v1.xlsx
@@ -438,7 +438,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>Personal calificado - Topógrafo</v>
+        <v>¿El trazo lo ejecutó un topógrafo calificado?</v>
       </c>
       <c r="E2" t="str">
         <v>Verificación documental</v>
@@ -458,7 +458,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>Terreno liberado</v>
+        <v>¿El terreno fue liberado y entregado para iniciar el trazo?</v>
       </c>
       <c r="E3" t="str">
         <v>Verificación documental</v>
@@ -478,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>Verificación de alineamiento, medidas y escuadra</v>
+        <v>¿Se verificaron el alineamiento, las medidas y la escuadra del trazo?</v>
       </c>
       <c r="E4" t="str">
         <v>Medición topográfica</v>
@@ -498,7 +498,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="str">
-        <v>Modificación al plano base</v>
+        <v>¿El trazo coincide con el plano base, sin modificaciones? (de haberlas, detallarlas en observaciones)</v>
       </c>
       <c r="E5" t="str">
         <v>Verificación contra plano</v>
@@ -518,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="str">
-        <v>Verificación de dimensiones de estructura</v>
+        <v>¿Las dimensiones replanteadas de la estructura coinciden con el plano?</v>
       </c>
       <c r="E6" t="str">
         <v>Medición topográfica</v>
@@ -538,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="str">
-        <v>Trazo de vértices en campo</v>
+        <v>¿Se materializaron en campo los vértices de la estructura?</v>
       </c>
       <c r="E7" t="str">
         <v>Medición topográfica</v>
@@ -558,7 +558,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="str">
-        <v>Trazo final de estructura</v>
+        <v>¿El trazo final de la estructura quedó marcado y verificado?</v>
       </c>
       <c r="E8" t="str">
         <v>Medición topográfica</v>
@@ -578,7 +578,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="str">
-        <v>Equipo topográfico calibrado</v>
+        <v>¿El equipo topográfico cuenta con certificado de calibración vigente?</v>
       </c>
       <c r="E9" t="str">
         <v>Verificación documental</v>
@@ -598,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="str">
-        <v>Personal calificado - Topógrafo</v>
+        <v>¿El levantamiento lo ejecutó un topógrafo calificado?</v>
       </c>
       <c r="E10" t="str">
         <v>Verificación documental</v>
@@ -618,7 +618,7 @@
         <v>2</v>
       </c>
       <c r="D11" t="str">
-        <v>Terreno liberado</v>
+        <v>¿El terreno fue liberado y entregado para iniciar el levantamiento?</v>
       </c>
       <c r="E11" t="str">
         <v>Verificación documental</v>
@@ -638,7 +638,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="str">
-        <v>Verificación de alineamiento, medidas y escuadra</v>
+        <v>¿Se verificaron el alineamiento, las medidas y la escuadra del levantamiento?</v>
       </c>
       <c r="E12" t="str">
         <v>Medición topográfica</v>
@@ -658,7 +658,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="str">
-        <v>Modificación al plano base</v>
+        <v>¿El levantamiento coincide con el plano base, sin modificaciones? (de haberlas, detallarlas en observaciones)</v>
       </c>
       <c r="E13" t="str">
         <v>Verificación contra plano</v>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="str">
-        <v>Verificación de dimensiones de estructura</v>
+        <v>¿Las dimensiones levantadas de la estructura coinciden con el plano?</v>
       </c>
       <c r="E14" t="str">
         <v>Medición topográfica</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="str">
-        <v>Trazo de vértices en campo</v>
+        <v>¿Se materializaron en campo los vértices de la estructura?</v>
       </c>
       <c r="E15" t="str">
         <v>Medición topográfica</v>
@@ -718,7 +718,7 @@
         <v>7</v>
       </c>
       <c r="D16" t="str">
-        <v>Trazo final de estructura</v>
+        <v>¿El trazo final de la estructura quedó marcado y verificado?</v>
       </c>
       <c r="E16" t="str">
         <v>Medición topográfica</v>
@@ -738,7 +738,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="str">
-        <v>Señalización de espacios</v>
+        <v>¿Los espacios levantados quedaron señalizados en campo?</v>
       </c>
       <c r="E17" t="str">
         <v>Inspección visual</v>
@@ -838,7 +838,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="str">
-        <v>Base de planchas metálicas</v>
+        <v>¿La base de la plancha metálica está correctamente ejecutada?</v>
       </c>
       <c r="E22" t="str">
         <v>list-[CONFORME, OBSERVADO, N/A]</v>
@@ -858,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="str">
-        <v>Pernos de anclaje (longitud y diámetro)</v>
+        <v>¿Los pernos de anclaje tienen la longitud y el diámetro especificados?</v>
       </c>
       <c r="E23" t="str">
         <v>list-[CONFORME, OBSERVADO, N/A]</v>
@@ -878,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="D24" t="str">
-        <v>Alineamiento de plancha metálica</v>
+        <v>¿La plancha metálica está alineada según el plano?</v>
       </c>
       <c r="E24" t="str">
         <v>list-[CONFORME, OBSERVADO, N/A]</v>
@@ -898,7 +898,7 @@
         <v>8</v>
       </c>
       <c r="D25" t="str">
-        <v>Nivelación de plancha metálica y pernos</v>
+        <v>¿La plancha metálica y los pernos están nivelados?</v>
       </c>
       <c r="E25" t="str">
         <v>list-[CONFORME, OBSERVADO, N/A]</v>
@@ -918,7 +918,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="str">
-        <v>Alineamiento de plancha y pernos de anclaje</v>
+        <v>¿La plancha y los pernos de anclaje guardan el alineamiento entre sí?</v>
       </c>
       <c r="E26" t="str">
         <v>list-[CONFORME, OBSERVADO, N/A]</v>
@@ -1058,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="str">
-        <v>CUMPLIMIENTO DEL PROCEDIMIENTO DE TRABAJO</v>
+        <v>¿Se ejecutó el trabajo conforme al procedimiento aprobado?</v>
       </c>
       <c r="E33" t="str">
         <v>Verificación documental</v>
@@ -1078,7 +1078,7 @@
         <v>2</v>
       </c>
       <c r="D34" t="str">
-        <v>CONTRASTE DE ESPECIALIDADES (Arquitectura, Estructuras e Instalaciones)</v>
+        <v>¿Se contrastaron los planos de las especialidades y se resolvieron las interferencias? (arquitectura, estructuras e instalaciones)</v>
       </c>
       <c r="E34" t="str">
         <v>Verificación contra plano</v>
@@ -1098,7 +1098,7 @@
         <v>3</v>
       </c>
       <c r="D35" t="str">
-        <v>VERIFICACIÓN TOPOGRÁFICA (trazo, alineamiento y niveles)</v>
+        <v>¿Se realizó la verificación topográfica? (trazo, alineamiento y niveles)</v>
       </c>
       <c r="E35" t="str">
         <v>Medición topográfica</v>
@@ -1118,7 +1118,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="str">
-        <v>VERIFICACIÓN DE LOS DIÁMETROS DE ACERO, SEGÚN DETALLES DEL PLANO</v>
+        <v>¿Los diámetros del acero corresponden a los detalles del plano?</v>
       </c>
       <c r="E36" t="str">
         <v>Medición en campo</v>
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="str">
-        <v>VERIFICACIÓN DE LA DISTRIBUCIÓN DE ACERO (cantidad y espaciamiento entre barras)</v>
+        <v>¿La distribución del acero cumple lo indicado? (cantidad y espaciamiento entre barras)</v>
       </c>
       <c r="E37" t="str">
         <v>Medición en campo</v>
@@ -1158,7 +1158,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="str">
-        <v>CORRECTA UBICACIÓN DE EMPALMES (traslapes, según el RNE)</v>
+        <v>¿Los empalmes están ubicados donde corresponde? (traslapes según el RNE)</v>
       </c>
       <c r="E38" t="str">
         <v>Verificación contra plano</v>
@@ -1178,7 +1178,7 @@
         <v>7</v>
       </c>
       <c r="D39" t="str">
-        <v>CORRECTA EQUIDISTANCIA DE ESTRIBOS SEGÚN DETALLES</v>
+        <v>¿El espaciamiento de estribos coincide con los detalles del plano?</v>
       </c>
       <c r="E39" t="str">
         <v>Medición en campo</v>
@@ -1198,7 +1198,7 @@
         <v>8</v>
       </c>
       <c r="D40" t="str">
-        <v>VERIFICACIÓN DE COLOCACIÓN DE MECHAS, ANCLAJES, FIJACIÓN Y ARRIOSTRE DE LAS ARMADURAS (según detalles de planos)</v>
+        <v>¿Las armaduras están correctamente ancladas, fijadas y arriostradas? (mechas, anclajes y arriostres según planos)</v>
       </c>
       <c r="E40" t="str">
         <v>Verificación contra plano</v>
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="D41" t="str">
-        <v>VERIFICACIÓN DE LA LIMPIEZA DE LAS ARMADURAS (libre de rebabas, sin deformaciones)</v>
+        <v>¿Las armaduras están limpias y sin defectos? (libres de óxido suelto, rebabas y deformaciones)</v>
       </c>
       <c r="E41" t="str">
         <v>Inspección visual</v>
@@ -1238,7 +1238,7 @@
         <v>10</v>
       </c>
       <c r="D42" t="str">
-        <v>ÓPTIMAS CONDICIONES DE SEGURIDAD (líneas de vida, plataformas de acceso, barandas, etc.)</v>
+        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas? (líneas de vida, plataformas de acceso y barandas)</v>
       </c>
       <c r="E42" t="str">
         <v>Inspección visual</v>
@@ -1258,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="D43" t="str">
-        <v>Cumplimiento del procedimiento de trabajo</v>
+        <v>¿Se ejecutó el trabajo conforme al procedimiento aprobado?</v>
       </c>
       <c r="E43" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1278,7 +1278,7 @@
         <v>2</v>
       </c>
       <c r="D44" t="str">
-        <v>Verificación topográfica</v>
+        <v>¿Se verificaron los niveles y el alineamiento antes del vaciado?</v>
       </c>
       <c r="E44" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1298,7 +1298,7 @@
         <v>3</v>
       </c>
       <c r="D45" t="str">
-        <v>Preparación y verificación de juntas</v>
+        <v>¿Las juntas fueron preparadas y verificadas?</v>
       </c>
       <c r="E45" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1318,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="str">
-        <v>Verificación acero de refuerzo</v>
+        <v>¿El acero de refuerzo fue liberado?</v>
       </c>
       <c r="E46" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1338,7 +1338,7 @@
         <v>5</v>
       </c>
       <c r="D47" t="str">
-        <v>Verificación encofrado</v>
+        <v>¿El encofrado fue liberado?</v>
       </c>
       <c r="E47" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1358,7 +1358,7 @@
         <v>6</v>
       </c>
       <c r="D48" t="str">
-        <v>Verificación instalaciones sanitarias</v>
+        <v>¿Las instalaciones sanitarias embebidas fueron verificadas?</v>
       </c>
       <c r="E48" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1378,7 +1378,7 @@
         <v>7</v>
       </c>
       <c r="D49" t="str">
-        <v>Verificación instalaciones eléctricas</v>
+        <v>¿Las instalaciones eléctricas embebidas fueron verificadas?</v>
       </c>
       <c r="E49" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1398,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="D50" t="str">
-        <v>Verificación instalaciones mecánicas</v>
+        <v>¿Las instalaciones mecánicas embebidas fueron verificadas?</v>
       </c>
       <c r="E50" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1418,7 +1418,7 @@
         <v>9</v>
       </c>
       <c r="D51" t="str">
-        <v>Verificación anclajes de estructuras metálicas</v>
+        <v>¿Los anclajes para estructuras metálicas fueron verificados?</v>
       </c>
       <c r="E51" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1738,7 +1738,7 @@
         <v>25</v>
       </c>
       <c r="D67" t="str">
-        <v>Acabado superficial de acuerdo a lo especificado</v>
+        <v>¿El acabado superficial corresponde a lo especificado?</v>
       </c>
       <c r="E67" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1758,7 +1758,7 @@
         <v>26</v>
       </c>
       <c r="D68" t="str">
-        <v>Nivel y aplomo final del elemento de acuerdo a lo indicado en planos</v>
+        <v>¿El nivel y el aplomo final del elemento cumplen lo indicado en planos?</v>
       </c>
       <c r="E68" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1778,7 +1778,7 @@
         <v>27</v>
       </c>
       <c r="D69" t="str">
-        <v>Correcta posición final de elementos embebidos</v>
+        <v>¿Los elementos embebidos quedaron en su posición final correcta?</v>
       </c>
       <c r="E69" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1798,7 +1798,7 @@
         <v>28</v>
       </c>
       <c r="D70" t="str">
-        <v>Verificación del orden y limpieza</v>
+        <v>¿El área quedó ordenada y limpia tras el vaciado?</v>
       </c>
       <c r="E70" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1818,7 +1818,7 @@
         <v>29</v>
       </c>
       <c r="D71" t="str">
-        <v>Curado adecuado (agua / membrana / otros)</v>
+        <v>¿Se aplicó el curado especificado? (agua, membrana u otro)</v>
       </c>
       <c r="E71" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="D72" t="str">
-        <v>CUMPLIMIENTO DEL PROCEDIMIENTO DE TRABAJO</v>
+        <v>¿Se ejecutó el trabajo conforme al procedimiento aprobado?</v>
       </c>
       <c r="E72" t="str">
         <v>Verificación documental</v>
@@ -1858,7 +1858,7 @@
         <v>2</v>
       </c>
       <c r="D73" t="str">
-        <v>VERIFICACIÓN DE TRAZO Y UBICACIÓN (ejes, alineamiento, distancias, coordenadas y niveles)</v>
+        <v>¿El trazo y la ubicación del encofrado coinciden con el plano? (ejes, alineamiento, distancias y niveles)</v>
       </c>
       <c r="E73" t="str">
         <v>Medición topográfica</v>
@@ -1878,7 +1878,7 @@
         <v>3</v>
       </c>
       <c r="D74" t="str">
-        <v>VERIFICACIÓN DE ENCOFRADOS (alineamiento, verticalidad y sin deformaciones)</v>
+        <v>¿El encofrado está alineado, aplomado y sin deformaciones?</v>
       </c>
       <c r="E74" t="str">
         <v>Medición en campo</v>
@@ -1898,7 +1898,7 @@
         <v>4</v>
       </c>
       <c r="D75" t="str">
-        <v>CORRECTA COLOCACIÓN DE DADOS Y SEPARADORES LATERALES</v>
+        <v>¿Se colocaron los dados y separadores laterales que garantizan el recubrimiento?</v>
       </c>
       <c r="E75" t="str">
         <v>Inspección visual</v>
@@ -1918,7 +1918,7 @@
         <v>5</v>
       </c>
       <c r="D76" t="str">
-        <v>CORRECTO MONTAJE, FIJACIÓN Y ARRIOSTRE DEL ENCOFRADO</v>
+        <v>¿El encofrado está montado, fijado y arriostrado de forma estable?</v>
       </c>
       <c r="E76" t="str">
         <v>Inspección visual</v>
@@ -1938,7 +1938,7 @@
         <v>6</v>
       </c>
       <c r="D77" t="str">
-        <v>DIMENSIONES DEL ENCOFRADO DE ACUERDO A LO ESPECIFICADO</v>
+        <v>¿Las dimensiones internas del encofrado corresponden a lo especificado?</v>
       </c>
       <c r="E77" t="str">
         <v>Medición en campo</v>
@@ -1958,7 +1958,7 @@
         <v>7</v>
       </c>
       <c r="D78" t="str">
-        <v>VERIFICACIÓN DE COLOCACIÓN DE DESMOLDANTE Y LIMPIEZA INTERIOR DE LOS ENCOFRADOS</v>
+        <v>¿Se aplicó desmoldante y el interior del encofrado quedó limpio?</v>
       </c>
       <c r="E78" t="str">
         <v>Inspección visual</v>
@@ -1978,7 +1978,7 @@
         <v>8</v>
       </c>
       <c r="D79" t="str">
-        <v>VERIFICACIÓN DE PASES O TUBOS DE INSTALACIONES SANITARIAS</v>
+        <v>¿Están colocados los pases y tubos de instalaciones sanitarias según plano?</v>
       </c>
       <c r="E79" t="str">
         <v>Verificación contra plano</v>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="str">
-        <v>VERIFICACIÓN DE PASES O TUBOS DE INSTALACIONES ELÉCTRICAS</v>
+        <v>¿Están colocados los pases y tubos de instalaciones eléctricas según plano?</v>
       </c>
       <c r="E80" t="str">
         <v>Verificación contra plano</v>
@@ -2018,7 +2018,7 @@
         <v>10</v>
       </c>
       <c r="D81" t="str">
-        <v>VERIFICACIÓN DE COLOCACIÓN DE SOPORTES Y/O ANCLAJES PARA PASES E INSTALACIONES VARIAS</v>
+        <v>¿Se colocaron los soportes y anclajes para los pases e instalaciones varias?</v>
       </c>
       <c r="E81" t="str">
         <v>Verificación contra plano</v>
@@ -2038,7 +2038,7 @@
         <v>11</v>
       </c>
       <c r="D82" t="str">
-        <v>CONDICIONES DE SEGURIDAD ADECUADAS</v>
+        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas?</v>
       </c>
       <c r="E82" t="str">
         <v>Inspección visual</v>
@@ -2058,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="D83" t="str">
-        <v>Alinea y centra la columna o varilla en la posición definitiva</v>
+        <v>¿La varilla quedó alineada y centrada en su posición definitiva?</v>
       </c>
       <c r="E83" t="str">
         <v>Medición topográfica</v>
@@ -2078,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="D84" t="str">
-        <v>Respeta siempre un recubrimiento de concreto mínimo de 2 cm en los bordes para evitar la oxidación futura del acero</v>
+        <v>¿Se respetó el recubrimiento mínimo de 2 cm respecto al borde del concreto?</v>
       </c>
       <c r="E84" t="str">
         <v>Medición en campo</v>
@@ -2098,7 +2098,7 @@
         <v>3</v>
       </c>
       <c r="D85" t="str">
-        <v>Utiliza un rotomartillo con broca para concreto (punta de carburo)</v>
+        <v>¿La perforación se ejecutó con rotomartillo y broca de carburo para concreto?</v>
       </c>
       <c r="E85" t="str">
         <v>Inspección visual</v>
@@ -2118,7 +2118,7 @@
         <v>4</v>
       </c>
       <c r="D86" t="str">
-        <v>Diámetro del agujero: debe ser más grande que el diámetro de la varilla</v>
+        <v>¿El diámetro de la perforación es mayor que el de la varilla, según la ficha técnica del anclaje?</v>
       </c>
       <c r="E86" t="str">
         <v>Medición en campo</v>
@@ -2138,7 +2138,7 @@
         <v>5</v>
       </c>
       <c r="D87" t="str">
-        <v>Debe penetrar al menos 200 mm en el concreto estructural</v>
+        <v>¿La perforación alcanza al menos 200 mm de profundidad en el concreto estructural?</v>
       </c>
       <c r="E87" t="str">
         <v>Medición en campo</v>
@@ -2158,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="D88" t="str">
-        <v>Limpieza: soplar con aire comprimido, limpiar con escobilla y volver a soplar</v>
+        <v>¿Se limpió la perforación con aire comprimido y escobilla antes de inyectar?</v>
       </c>
       <c r="E88" t="str">
         <v>Inspección visual</v>
@@ -2178,7 +2178,7 @@
         <v>7</v>
       </c>
       <c r="D89" t="str">
-        <v>Inyectar desde el fondo hasta los 2/3 del volumen</v>
+        <v>¿El adhesivo se inyectó desde el fondo hasta dos tercios del volumen de la perforación?</v>
       </c>
       <c r="E89" t="str">
         <v>Inspección visual</v>
@@ -2198,7 +2198,7 @@
         <v>8</v>
       </c>
       <c r="D90" t="str">
-        <v>Insertar girando hasta el fondo para que la resina llegue a cubrir todo el corrugado</v>
+        <v>¿La varilla se insertó girando hasta el fondo, cubriendo todo el corrugado con resina?</v>
       </c>
       <c r="E90" t="str">
         <v>Inspección visual</v>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="str">
-        <v>El tiempo de curado dependerá de la temperatura del día (20 °C - 24 horas, 10 °C - 48 horas y &lt;5 °C - 72 horas)</v>
+        <v>¿Se respetó el tiempo de curado según la temperatura ambiente? (20 °C: 24 h · 10 °C: 48 h · menos de 5 °C: 72 h)</v>
       </c>
       <c r="E91" t="str">
         <v>Verificación documental</v>
@@ -2238,7 +2238,7 @@
         <v>10</v>
       </c>
       <c r="D92" t="str">
-        <v>Condiciones de seguridad adecuadas</v>
+        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas?</v>
       </c>
       <c r="E92" t="str">
         <v>Inspección visual</v>
@@ -2258,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="str">
-        <v>Instalación de tuberías y accesorios de acuerdo a planos</v>
+        <v>¿Las tuberías y accesorios se instalaron según el plano?</v>
       </c>
       <c r="E93" t="str">
         <v>Verificación contra plano</v>
@@ -2278,7 +2278,7 @@
         <v>2</v>
       </c>
       <c r="D94" t="str">
-        <v>Material especificado (PVC)</v>
+        <v>¿El material instalado corresponde al especificado? (PVC)</v>
       </c>
       <c r="E94" t="str">
         <v>Inspección visual</v>
@@ -2298,7 +2298,7 @@
         <v>3</v>
       </c>
       <c r="D95" t="str">
-        <v>Verificar diámetro de tubería, de acuerdo al plano</v>
+        <v>¿El diámetro de la tubería corresponde al indicado en el plano?</v>
       </c>
       <c r="E95" t="str">
         <v>Medición en campo</v>
@@ -2318,7 +2318,7 @@
         <v>4</v>
       </c>
       <c r="D96" t="str">
-        <v>Material libre de defectos (inspección visual)</v>
+        <v>¿El material está libre de defectos? (fisuras, deformaciones o golpes)</v>
       </c>
       <c r="E96" t="str">
         <v>Inspección visual</v>
@@ -2338,7 +2338,7 @@
         <v>5</v>
       </c>
       <c r="D97" t="str">
-        <v>Soportada adecuadamente (fijación de tuberías y accesorios)</v>
+        <v>¿Las tuberías y accesorios están adecuadamente soportados y fijados?</v>
       </c>
       <c r="E97" t="str">
         <v>Inspección visual</v>
@@ -2358,7 +2358,7 @@
         <v>6</v>
       </c>
       <c r="D98" t="str">
-        <v>Taponear los terminales expuestos de la tubería así como las cajas de pase</v>
+        <v>¿Los terminales expuestos de tubería y las cajas de paso quedaron taponeados?</v>
       </c>
       <c r="E98" t="str">
         <v>Inspección visual</v>
@@ -2378,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="D99" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos están ubicados según el plano?</v>
       </c>
       <c r="E99" t="str">
         <v>Verificación contra plano</v>
@@ -2398,7 +2398,7 @@
         <v>2</v>
       </c>
       <c r="D100" t="str">
-        <v>Las tuberías están libres de aplastamientos, roturas o dobleces excesivos que reduzcan su diámetro interior</v>
+        <v>¿Las tuberías están libres de aplastamientos, roturas o dobleces que reduzcan su diámetro interior?</v>
       </c>
       <c r="E100" t="str">
         <v>Inspección visual</v>
@@ -2418,7 +2418,7 @@
         <v>3</v>
       </c>
       <c r="D101" t="str">
-        <v>Los accesorios (uniones, conectores y curvas) son del mismo material y clase que la tubería (PVC)</v>
+        <v>¿Los accesorios son del mismo material y clase que la tubería? (uniones, conectores y curvas en PVC)</v>
       </c>
       <c r="E101" t="str">
         <v>Inspección visual</v>
@@ -2438,7 +2438,7 @@
         <v>4</v>
       </c>
       <c r="D102" t="str">
-        <v>Colocación de las cajas (octogonales, rectangulares, de paso) según trazo topográfico</v>
+        <v>¿Las cajas se colocaron según el trazo topográfico? (octogonales, rectangulares y de paso)</v>
       </c>
       <c r="E102" t="str">
         <v>Medición topográfica</v>
@@ -2458,7 +2458,7 @@
         <v>5</v>
       </c>
       <c r="D103" t="str">
-        <v>Soporte adecuado (fijación de tuberías y accesorios)</v>
+        <v>¿Las tuberías y accesorios están adecuadamente soportados y fijados?</v>
       </c>
       <c r="E103" t="str">
         <v>Inspección visual</v>
@@ -2478,7 +2478,7 @@
         <v>6</v>
       </c>
       <c r="D104" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E104" t="str">
         <v>Inspección visual</v>
@@ -2498,7 +2498,7 @@
         <v>7</v>
       </c>
       <c r="D105" t="str">
-        <v>Diámetro de tubería de acuerdo al plano</v>
+        <v>¿El diámetro de la tubería corresponde al indicado en el plano?</v>
       </c>
       <c r="E105" t="str">
         <v>Medición en campo</v>
@@ -2518,7 +2518,7 @@
         <v>8</v>
       </c>
       <c r="D106" t="str">
-        <v>Condición en buen estado (tuberías, accesorios)</v>
+        <v>¿Las tuberías y accesorios están en buen estado?</v>
       </c>
       <c r="E106" t="str">
         <v>Inspección visual</v>
@@ -2538,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="D107" t="str">
-        <v>Verificación de red: agua fría / agua caliente</v>
+        <v>¿La red instalada corresponde al tipo previsto? (agua fría o agua caliente)</v>
       </c>
       <c r="E107" t="str">
         <v>Verificación contra plano</v>
@@ -2558,7 +2558,7 @@
         <v>2</v>
       </c>
       <c r="D108" t="str">
-        <v>Material de red: PVC / PPR / acero</v>
+        <v>¿El material de la red corresponde al especificado? (PVC, PPR o acero)</v>
       </c>
       <c r="E108" t="str">
         <v>Inspección visual</v>
@@ -2578,7 +2578,7 @@
         <v>3</v>
       </c>
       <c r="D109" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos de agua están ubicados según el plano?</v>
       </c>
       <c r="E109" t="str">
         <v>Verificación contra plano</v>
@@ -2598,7 +2598,7 @@
         <v>4</v>
       </c>
       <c r="D110" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E110" t="str">
         <v>Medición en campo</v>
@@ -2618,7 +2618,7 @@
         <v>5</v>
       </c>
       <c r="D111" t="str">
-        <v>Inspección visual de diámetro y recorrido de tubería</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano?</v>
       </c>
       <c r="E111" t="str">
         <v>Inspección visual</v>
@@ -2638,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="D112" t="str">
-        <v>Tipo de salida de agua: ovalín / inodoro</v>
+        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
       </c>
       <c r="E112" t="str">
         <v>Inspección visual</v>
@@ -2658,7 +2658,7 @@
         <v>7</v>
       </c>
       <c r="D113" t="str">
-        <v>Válvula de paso</v>
+        <v>¿Se instaló la válvula de paso donde indica el plano?</v>
       </c>
       <c r="E113" t="str">
         <v>Inspección visual</v>
@@ -2678,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="D114" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E114" t="str">
         <v>Inspección visual</v>
@@ -2698,7 +2698,7 @@
         <v>9</v>
       </c>
       <c r="D115" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos de desagüe están ubicados según el plano?</v>
       </c>
       <c r="E115" t="str">
         <v>Verificación contra plano</v>
@@ -2718,7 +2718,7 @@
         <v>10</v>
       </c>
       <c r="D116" t="str">
-        <v>Material de red: PVC / PPR</v>
+        <v>¿El material de la red corresponde al especificado? (PVC o PPR)</v>
       </c>
       <c r="E116" t="str">
         <v>Inspección visual</v>
@@ -2738,7 +2738,7 @@
         <v>11</v>
       </c>
       <c r="D117" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E117" t="str">
         <v>Medición en campo</v>
@@ -2758,7 +2758,7 @@
         <v>12</v>
       </c>
       <c r="D118" t="str">
-        <v>Inspección visual de diámetro y recorrido de tubería</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano?</v>
       </c>
       <c r="E118" t="str">
         <v>Inspección visual</v>
@@ -2778,7 +2778,7 @@
         <v>13</v>
       </c>
       <c r="D119" t="str">
-        <v>Tipo de salida de desagüe: ovalín / inodoro</v>
+        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
       </c>
       <c r="E119" t="str">
         <v>Inspección visual</v>
@@ -2798,7 +2798,7 @@
         <v>14</v>
       </c>
       <c r="D120" t="str">
-        <v>Urinario / registro / sumidero</v>
+        <v>¿Se instalaron los puntos de urinario, registro y sumidero previstos?</v>
       </c>
       <c r="E120" t="str">
         <v>Inspección visual</v>
@@ -2818,7 +2818,7 @@
         <v>15</v>
       </c>
       <c r="D121" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E121" t="str">
         <v>Inspección visual</v>
@@ -2838,7 +2838,7 @@
         <v>16</v>
       </c>
       <c r="D122" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos de ventilación están ubicados según el plano?</v>
       </c>
       <c r="E122" t="str">
         <v>Verificación contra plano</v>
@@ -2858,7 +2858,7 @@
         <v>17</v>
       </c>
       <c r="D123" t="str">
-        <v>Material de red: PVC / PPR</v>
+        <v>¿El material de la red corresponde al especificado? (PVC o PPR)</v>
       </c>
       <c r="E123" t="str">
         <v>Inspección visual</v>
@@ -2878,7 +2878,7 @@
         <v>18</v>
       </c>
       <c r="D124" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E124" t="str">
         <v>Medición en campo</v>
@@ -2898,7 +2898,7 @@
         <v>19</v>
       </c>
       <c r="D125" t="str">
-        <v>Inspección visual de diámetro y recorrido de tubería</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano?</v>
       </c>
       <c r="E125" t="str">
         <v>Inspección visual</v>
@@ -2918,7 +2918,7 @@
         <v>20</v>
       </c>
       <c r="D126" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E126" t="str">
         <v>Inspección visual</v>
@@ -2938,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="D127" t="str">
-        <v>Ubicación de caja equipotencial y caja de paso, según plano</v>
+        <v>¿La caja equipotencial y las cajas de paso están ubicadas según el plano?</v>
       </c>
       <c r="E127" t="str">
         <v>Verificación contra plano</v>
@@ -2958,7 +2958,7 @@
         <v>2</v>
       </c>
       <c r="D128" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E128" t="str">
         <v>Inspección visual</v>
@@ -2978,7 +2978,7 @@
         <v>3</v>
       </c>
       <c r="D129" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E129" t="str">
         <v>Medición en campo</v>
@@ -2998,7 +2998,7 @@
         <v>4</v>
       </c>
       <c r="D130" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E130" t="str">
         <v>Inspección visual</v>
@@ -3018,7 +3018,7 @@
         <v>5</v>
       </c>
       <c r="D131" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos están ubicados según el plano?</v>
       </c>
       <c r="E131" t="str">
         <v>Verificación contra plano</v>
@@ -3038,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E132" t="str">
         <v>Inspección visual</v>
@@ -3058,7 +3058,7 @@
         <v>7</v>
       </c>
       <c r="D133" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E133" t="str">
         <v>Medición en campo</v>
@@ -3078,7 +3078,7 @@
         <v>8</v>
       </c>
       <c r="D134" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E134" t="str">
         <v>Inspección visual</v>
@@ -3098,7 +3098,7 @@
         <v>9</v>
       </c>
       <c r="D135" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos están ubicados según el plano?</v>
       </c>
       <c r="E135" t="str">
         <v>Verificación contra plano</v>
@@ -3118,7 +3118,7 @@
         <v>10</v>
       </c>
       <c r="D136" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E136" t="str">
         <v>Inspección visual</v>
@@ -3138,7 +3138,7 @@
         <v>11</v>
       </c>
       <c r="D137" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E137" t="str">
         <v>Medición en campo</v>
@@ -3158,7 +3158,7 @@
         <v>12</v>
       </c>
       <c r="D138" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E138" t="str">
         <v>Inspección visual</v>
@@ -3178,7 +3178,7 @@
         <v>13</v>
       </c>
       <c r="D139" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos están ubicados según el plano?</v>
       </c>
       <c r="E139" t="str">
         <v>Verificación contra plano</v>
@@ -3198,7 +3198,7 @@
         <v>14</v>
       </c>
       <c r="D140" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E140" t="str">
         <v>Inspección visual</v>
@@ -3218,7 +3218,7 @@
         <v>15</v>
       </c>
       <c r="D141" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E141" t="str">
         <v>Medición en campo</v>
@@ -3238,7 +3238,7 @@
         <v>16</v>
       </c>
       <c r="D142" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E142" t="str">
         <v>Inspección visual</v>
@@ -3258,7 +3258,7 @@
         <v>17</v>
       </c>
       <c r="D143" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos están ubicados según el plano?</v>
       </c>
       <c r="E143" t="str">
         <v>Verificación contra plano</v>
@@ -3278,7 +3278,7 @@
         <v>18</v>
       </c>
       <c r="D144" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E144" t="str">
         <v>Inspección visual</v>
@@ -3298,7 +3298,7 @@
         <v>19</v>
       </c>
       <c r="D145" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E145" t="str">
         <v>Medición en campo</v>
@@ -3318,7 +3318,7 @@
         <v>20</v>
       </c>
       <c r="D146" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E146" t="str">
         <v>Inspección visual</v>
@@ -3338,7 +3338,7 @@
         <v>21</v>
       </c>
       <c r="D147" t="str">
-        <v>Correcta ubicación de puntos, según plano (ACI / plano de intrusión)</v>
+        <v>¿Los puntos están ubicados según el plano? (ACI y plano de intrusión)</v>
       </c>
       <c r="E147" t="str">
         <v>Verificación contra plano</v>
@@ -3358,7 +3358,7 @@
         <v>22</v>
       </c>
       <c r="D148" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E148" t="str">
         <v>Inspección visual</v>
@@ -3378,7 +3378,7 @@
         <v>23</v>
       </c>
       <c r="D149" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E149" t="str">
         <v>Medición en campo</v>
@@ -3398,7 +3398,7 @@
         <v>24</v>
       </c>
       <c r="D150" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E150" t="str">
         <v>Inspección visual</v>
@@ -3418,7 +3418,7 @@
         <v>25</v>
       </c>
       <c r="D151" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos están ubicados según el plano?</v>
       </c>
       <c r="E151" t="str">
         <v>Verificación contra plano</v>
@@ -3438,7 +3438,7 @@
         <v>26</v>
       </c>
       <c r="D152" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E152" t="str">
         <v>Inspección visual</v>
@@ -3458,7 +3458,7 @@
         <v>27</v>
       </c>
       <c r="D153" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E153" t="str">
         <v>Medición en campo</v>
@@ -3478,7 +3478,7 @@
         <v>28</v>
       </c>
       <c r="D154" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E154" t="str">
         <v>Inspección visual</v>
@@ -3498,7 +3498,7 @@
         <v>29</v>
       </c>
       <c r="D155" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos están ubicados según el plano?</v>
       </c>
       <c r="E155" t="str">
         <v>Verificación contra plano</v>
@@ -3518,7 +3518,7 @@
         <v>30</v>
       </c>
       <c r="D156" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E156" t="str">
         <v>Inspección visual</v>
@@ -3538,7 +3538,7 @@
         <v>31</v>
       </c>
       <c r="D157" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E157" t="str">
         <v>Medición en campo</v>
@@ -3558,7 +3558,7 @@
         <v>32</v>
       </c>
       <c r="D158" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E158" t="str">
         <v>Inspección visual</v>
@@ -3578,7 +3578,7 @@
         <v>33</v>
       </c>
       <c r="D159" t="str">
-        <v>Correcta ubicación de puntos, según plano</v>
+        <v>¿Los puntos están ubicados según el plano?</v>
       </c>
       <c r="E159" t="str">
         <v>Verificación contra plano</v>
@@ -3598,7 +3598,7 @@
         <v>34</v>
       </c>
       <c r="D160" t="str">
-        <v>Inspección visual: diámetro, recorrido de tubería, caja y altura</v>
+        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
       </c>
       <c r="E160" t="str">
         <v>Inspección visual</v>
@@ -3618,7 +3618,7 @@
         <v>35</v>
       </c>
       <c r="D161" t="str">
-        <v>Cantidad de puntos de salida</v>
+        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
       </c>
       <c r="E161" t="str">
         <v>Medición en campo</v>
@@ -3638,7 +3638,7 @@
         <v>36</v>
       </c>
       <c r="D162" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E162" t="str">
         <v>Inspección visual</v>
@@ -3658,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="D163" t="str">
-        <v>Ubicación de zanja</v>
+        <v>¿La zanja está ubicada según el plano?</v>
       </c>
       <c r="E163" t="str">
         <v>Verificación contra plano</v>
@@ -3678,7 +3678,7 @@
         <v>2</v>
       </c>
       <c r="D164" t="str">
-        <v>Verificación de corte de zanja</v>
+        <v>¿Las dimensiones de corte de la zanja cumplen el detalle? (ancho y profundidad)</v>
       </c>
       <c r="E164" t="str">
         <v>Medición en campo</v>
@@ -3698,7 +3698,7 @@
         <v>3</v>
       </c>
       <c r="D165" t="str">
-        <v>Altura de cama de arena (según detalle)</v>
+        <v>¿La cama de arena tiene la altura indicada en el detalle?</v>
       </c>
       <c r="E165" t="str">
         <v>Medición en campo</v>
@@ -3718,7 +3718,7 @@
         <v>4</v>
       </c>
       <c r="D166" t="str">
-        <v>Inspección visual de diámetro y recorrido de tubería</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano?</v>
       </c>
       <c r="E166" t="str">
         <v>Inspección visual</v>
@@ -3738,7 +3738,7 @@
         <v>5</v>
       </c>
       <c r="D167" t="str">
-        <v>Verificación de cantidad de tuberías</v>
+        <v>¿La cantidad de tuberías coincide con el plano?</v>
       </c>
       <c r="E167" t="str">
         <v>Medición en campo</v>
@@ -3758,7 +3758,7 @@
         <v>6</v>
       </c>
       <c r="D168" t="str">
-        <v>Separación entre tuberías según detalle</v>
+        <v>¿La separación entre tuberías cumple el detalle?</v>
       </c>
       <c r="E168" t="str">
         <v>Medición en campo</v>
@@ -3778,7 +3778,7 @@
         <v>7</v>
       </c>
       <c r="D169" t="str">
-        <v>Señalización según detalle</v>
+        <v>¿Se colocó la señalización de la red según el detalle? (cinta o malla de advertencia)</v>
       </c>
       <c r="E169" t="str">
         <v>Inspección visual</v>
@@ -3798,7 +3798,7 @@
         <v>8</v>
       </c>
       <c r="D170" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E170" t="str">
         <v>Inspección visual</v>
@@ -3818,7 +3818,7 @@
         <v>9</v>
       </c>
       <c r="D171" t="str">
-        <v>Inspección visual de diámetro de tubería</v>
+        <v>¿El diámetro de la tubería que llega al buzón corresponde al plano?</v>
       </c>
       <c r="E171" t="str">
         <v>Inspección visual</v>
@@ -3838,7 +3838,7 @@
         <v>10</v>
       </c>
       <c r="D172" t="str">
-        <v>Verificación de cantidad de tuberías</v>
+        <v>¿La cantidad de tuberías coincide con el plano?</v>
       </c>
       <c r="E172" t="str">
         <v>Medición en campo</v>
@@ -3858,7 +3858,7 @@
         <v>11</v>
       </c>
       <c r="D173" t="str">
-        <v>Separación entre tuberías según detalle</v>
+        <v>¿La separación entre tuberías cumple el detalle?</v>
       </c>
       <c r="E173" t="str">
         <v>Medición en campo</v>
@@ -3878,7 +3878,7 @@
         <v>12</v>
       </c>
       <c r="D174" t="str">
-        <v>Distancia mínima entre NPT y tubería</v>
+        <v>¿Se respeta la distancia mínima entre el NPT y la tubería?</v>
       </c>
       <c r="E174" t="str">
         <v>Medición en campo</v>
@@ -3898,7 +3898,7 @@
         <v>13</v>
       </c>
       <c r="D175" t="str">
-        <v>Verificación de sumidero (según detalle)</v>
+        <v>¿El sumidero del buzón se ejecutó según el detalle?</v>
       </c>
       <c r="E175" t="str">
         <v>Verificación contra plano</v>
@@ -3918,7 +3918,7 @@
         <v>14</v>
       </c>
       <c r="D176" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E176" t="str">
         <v>Inspección visual</v>
@@ -3938,7 +3938,7 @@
         <v>15</v>
       </c>
       <c r="D177" t="str">
-        <v>Trazo y replanteo</v>
+        <v>¿El trazo y replanteo de la red colgada fue verificado?</v>
       </c>
       <c r="E177" t="str">
         <v>Medición topográfica</v>
@@ -3958,7 +3958,7 @@
         <v>16</v>
       </c>
       <c r="D178" t="str">
-        <v>Inspección visual de diámetro de tubería / bandeja</v>
+        <v>¿El diámetro de la tubería o bandeja corresponde al plano?</v>
       </c>
       <c r="E178" t="str">
         <v>Inspección visual</v>
@@ -3978,7 +3978,7 @@
         <v>17</v>
       </c>
       <c r="D179" t="str">
-        <v>Verificación de cantidad de tuberías / bandejas</v>
+        <v>¿La cantidad de tuberías o bandejas coincide con el plano?</v>
       </c>
       <c r="E179" t="str">
         <v>Medición en campo</v>
@@ -3998,7 +3998,7 @@
         <v>18</v>
       </c>
       <c r="D180" t="str">
-        <v>Separación entre tuberías / bandeja según detalle</v>
+        <v>¿La separación entre tuberías o bandejas cumple el detalle?</v>
       </c>
       <c r="E180" t="str">
         <v>Medición en campo</v>
@@ -4018,7 +4018,7 @@
         <v>19</v>
       </c>
       <c r="D181" t="str">
-        <v>Distancia mínima entre NPT y tubería / bandeja</v>
+        <v>¿Se respeta la distancia mínima entre el NPT y la tubería o bandeja?</v>
       </c>
       <c r="E181" t="str">
         <v>Medición en campo</v>
@@ -4038,7 +4038,7 @@
         <v>20</v>
       </c>
       <c r="D182" t="str">
-        <v>Limpieza de área de trabajo</v>
+        <v>¿El área de trabajo quedó limpia y ordenada?</v>
       </c>
       <c r="E182" t="str">
         <v>Inspección visual</v>
@@ -4058,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="D183" t="str">
-        <v>Ubicación correcta según detalles y plano (sensor de temperatura, detector de humo, luz estroboscópica, estación manual, sirena)</v>
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
       </c>
       <c r="E183" t="str">
         <v>Verificación contra plano</v>
@@ -4078,7 +4078,7 @@
         <v>2</v>
       </c>
       <c r="D184" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el sensor de temperatura y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
       </c>
       <c r="E184" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4098,7 +4098,7 @@
         <v>3</v>
       </c>
       <c r="D185" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el detector de humo y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el detector de humo?</v>
       </c>
       <c r="E185" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4118,7 +4118,7 @@
         <v>4</v>
       </c>
       <c r="D186" t="str">
-        <v>Reconocimiento y correspondencia del tablero de control detector del circuito de alarmas contra incendios</v>
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
       </c>
       <c r="E186" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4138,7 +4138,7 @@
         <v>5</v>
       </c>
       <c r="D187" t="str">
-        <v>Ubicación correcta según detalles y plano (sensor de temperatura, detector de humo, luz estroboscópica, estación manual, sirena)</v>
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
       </c>
       <c r="E187" t="str">
         <v>Verificación contra plano</v>
@@ -4158,7 +4158,7 @@
         <v>6</v>
       </c>
       <c r="D188" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el sensor de temperatura y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
       </c>
       <c r="E188" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4178,7 +4178,7 @@
         <v>7</v>
       </c>
       <c r="D189" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el detector de humo y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el detector de humo?</v>
       </c>
       <c r="E189" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4198,7 +4198,7 @@
         <v>8</v>
       </c>
       <c r="D190" t="str">
-        <v>Reconocimiento y correspondencia del tablero de control detector del circuito de alarmas contra incendios</v>
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
       </c>
       <c r="E190" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4218,7 +4218,7 @@
         <v>9</v>
       </c>
       <c r="D191" t="str">
-        <v>Ubicación correcta según detalles y plano (sensor de temperatura, detector de humo, luz estroboscópica, estación manual, sirena)</v>
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
       </c>
       <c r="E191" t="str">
         <v>Verificación contra plano</v>
@@ -4238,7 +4238,7 @@
         <v>10</v>
       </c>
       <c r="D192" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el sensor de temperatura y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
       </c>
       <c r="E192" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4258,7 +4258,7 @@
         <v>11</v>
       </c>
       <c r="D193" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el detector de humo y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el detector de humo?</v>
       </c>
       <c r="E193" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4278,7 +4278,7 @@
         <v>12</v>
       </c>
       <c r="D194" t="str">
-        <v>Reconocimiento y correspondencia del tablero de control detector del circuito de alarmas contra incendios</v>
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
       </c>
       <c r="E194" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4298,7 +4298,7 @@
         <v>13</v>
       </c>
       <c r="D195" t="str">
-        <v>Ubicación correcta según detalles y plano (sensor de temperatura, detector de humo, luz estroboscópica, estación manual, sirena)</v>
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
       </c>
       <c r="E195" t="str">
         <v>Verificación contra plano</v>
@@ -4318,7 +4318,7 @@
         <v>14</v>
       </c>
       <c r="D196" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el sensor de temperatura y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
       </c>
       <c r="E196" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4338,7 +4338,7 @@
         <v>15</v>
       </c>
       <c r="D197" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el detector de humo y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el detector de humo?</v>
       </c>
       <c r="E197" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4358,7 +4358,7 @@
         <v>16</v>
       </c>
       <c r="D198" t="str">
-        <v>Reconocimiento y correspondencia del tablero de control detector del circuito de alarmas contra incendios</v>
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
       </c>
       <c r="E198" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4378,7 +4378,7 @@
         <v>17</v>
       </c>
       <c r="D199" t="str">
-        <v>Ubicación correcta según detalles y plano (sensor de temperatura, detector de humo, luz estroboscópica, estación manual, sirena)</v>
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
       </c>
       <c r="E199" t="str">
         <v>Verificación contra plano</v>
@@ -4398,7 +4398,7 @@
         <v>18</v>
       </c>
       <c r="D200" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el sensor de temperatura y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
       </c>
       <c r="E200" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4418,7 +4418,7 @@
         <v>19</v>
       </c>
       <c r="D201" t="str">
-        <v>Correcto funcionamiento de sirena al detectar el detector de humo y activación de alarma contra incendios</v>
+        <v>¿La sirena se activa al operar el detector de humo?</v>
       </c>
       <c r="E201" t="str">
         <v>Prueba de funcionamiento</v>
@@ -4438,7 +4438,7 @@
         <v>20</v>
       </c>
       <c r="D202" t="str">
-        <v>Reconocimiento y correspondencia del tablero de control detector del circuito de alarmas contra incendios</v>
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
       </c>
       <c r="E202" t="str">
         <v>Prueba de funcionamiento</v>

--- a/01 Proyecto_Mercado_Mayorista/02 Excel Maestro/MAESTRO_Mercado_Mayorista_v1.xlsx
+++ b/01 Proyecto_Mercado_Mayorista/02 Excel Maestro/MAESTRO_Mercado_Mayorista_v1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F232"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -1058,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="str">
-        <v>¿Se ejecutó el trabajo conforme al procedimiento aprobado?</v>
+        <v>¿El acero cuenta con certificado de calidad del lote y corresponde al grado especificado? (grado y diámetro trazables a la colada)</v>
       </c>
       <c r="E33" t="str">
         <v>Verificación documental</v>
@@ -1078,10 +1078,10 @@
         <v>2</v>
       </c>
       <c r="D34" t="str">
-        <v>¿Se contrastaron los planos de las especialidades y se resolvieron las interferencias? (arquitectura, estructuras e instalaciones)</v>
+        <v>¿El procedimiento de habilitación y colocación vigente está disponible en el frente y el personal fue instruido en él?</v>
       </c>
       <c r="E34" t="str">
-        <v>Verificación contra plano</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F34" t="str">
         <v>INSPECCIÓN</v>
@@ -1098,10 +1098,10 @@
         <v>3</v>
       </c>
       <c r="D35" t="str">
-        <v>¿Se realizó la verificación topográfica? (trazo, alineamiento y niveles)</v>
+        <v>¿Se contrastaron los planos de las tres especialidades y NO quedan interferencias sin resolver? (listarlas en observaciones)</v>
       </c>
       <c r="E35" t="str">
-        <v>Medición topográfica</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F35" t="str">
         <v>INSPECCIÓN</v>
@@ -1118,10 +1118,10 @@
         <v>4</v>
       </c>
       <c r="D36" t="str">
-        <v>¿Los diámetros del acero corresponden a los detalles del plano?</v>
+        <v>¿Los ejes y niveles del elemento fueron verificados topográficamente, con desviación dentro de ±10 mm respecto al plano?</v>
       </c>
       <c r="E36" t="str">
-        <v>Medición en campo</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F36" t="str">
         <v>INSPECCIÓN</v>
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="str">
-        <v>¿La distribución del acero cumple lo indicado? (cantidad y espaciamiento entre barras)</v>
+        <v>¿Los diámetros de las barras coinciden con el plano, verificados por marca de laminado o calibrador en al menos 3 barras por lecho?</v>
       </c>
       <c r="E37" t="str">
         <v>Medición en campo</v>
@@ -1158,10 +1158,10 @@
         <v>6</v>
       </c>
       <c r="D38" t="str">
-        <v>¿Los empalmes están ubicados donde corresponde? (traslapes según el RNE)</v>
+        <v>¿La cantidad de barras es EXACTAMENTE la del plano y el espaciamiento no se desvía más de ±2 cm?</v>
       </c>
       <c r="E38" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F38" t="str">
         <v>INSPECCIÓN</v>
@@ -1178,7 +1178,7 @@
         <v>7</v>
       </c>
       <c r="D39" t="str">
-        <v>¿El espaciamiento de estribos coincide con los detalles del plano?</v>
+        <v>¿Los traslapes cumplen la longitud indicada en el plano?</v>
       </c>
       <c r="E39" t="str">
         <v>Medición en campo</v>
@@ -1198,7 +1198,7 @@
         <v>8</v>
       </c>
       <c r="D40" t="str">
-        <v>¿Las armaduras están correctamente ancladas, fijadas y arriostradas? (mechas, anclajes y arriostres según planos)</v>
+        <v>¿NINGÚN traslape cae en zona de confinamiento ni donde el plano lo prohíbe? (RNE E.060 — cumplir la longitud no basta si está en la zona de máximo esfuerzo)</v>
       </c>
       <c r="E40" t="str">
         <v>Verificación contra plano</v>
@@ -1218,10 +1218,10 @@
         <v>9</v>
       </c>
       <c r="D41" t="str">
-        <v>¿Las armaduras están limpias y sin defectos? (libres de óxido suelto, rebabas y deformaciones)</v>
+        <v>¿El espaciamiento de estribos cumple ±2 cm y la longitud de la zona de confinamiento coincide con el detalle? (RNE E.060)</v>
       </c>
       <c r="E41" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F41" t="str">
         <v>INSPECCIÓN</v>
@@ -1238,10 +1238,10 @@
         <v>10</v>
       </c>
       <c r="D42" t="str">
-        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas? (líneas de vida, plataformas de acceso y barandas)</v>
+        <v>¿El recubrimiento está garantizado con dados o separadores del espesor especificado, en cantidad suficiente para que la armadura no ceda durante el vaciado?</v>
       </c>
       <c r="E42" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F42" t="str">
         <v>INSPECCIÓN</v>
@@ -1249,62 +1249,62 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B43" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C43" t="str">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D43" t="str">
-        <v>¿Se ejecutó el trabajo conforme al procedimiento aprobado?</v>
+        <v>¿Las armaduras están ancladas, fijadas y arriostradas de modo que no se desplacen durante el vaciado y el vibrado?</v>
       </c>
       <c r="E43" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F43" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B44" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C44" t="str">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D44" t="str">
-        <v>¿Se verificaron los niveles y el alineamiento antes del vaciado?</v>
+        <v>¿Las barras están libres de óxido no adherente, grasa, aceite, pintura o lechada que reduzcan la adherencia con el concreto?</v>
       </c>
       <c r="E44" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F44" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B45" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C45" t="str">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D45" t="str">
-        <v>¿Las juntas fueron preparadas y verificadas?</v>
+        <v>¿El frente cuenta con las protecciones colectivas requeridas y las esperas verticales están tapadas? (líneas de vida, plataformas, barandas y tapas antiempalamiento)</v>
       </c>
       <c r="E45" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F45" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="46">
@@ -1315,10 +1315,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C46" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46" t="str">
-        <v>¿El acero de refuerzo fue liberado?</v>
+        <v>¿El procedimiento de vaciado está definido para este elemento, incluyendo qué hacer ante lluvia, falla de bomba o junta fría no prevista?</v>
       </c>
       <c r="E46" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1335,10 +1335,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C47" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D47" t="str">
-        <v>¿El encofrado fue liberado?</v>
+        <v>¿Los niveles de vaciado están marcados en el elemento y verificados topográficamente?</v>
       </c>
       <c r="E47" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1355,10 +1355,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C48" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D48" t="str">
-        <v>¿Las instalaciones sanitarias embebidas fueron verificadas?</v>
+        <v>¿Las juntas de construcción están en la ubicación prevista, con la superficie rugosa, limpia y saturada pero sin agua libre?</v>
       </c>
       <c r="E48" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1375,10 +1375,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C49" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D49" t="str">
-        <v>¿Las instalaciones eléctricas embebidas fueron verificadas?</v>
+        <v>¿El acero de refuerzo está LIBERADO con su protocolo aprobado?</v>
       </c>
       <c r="E49" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1395,10 +1395,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C50" t="str">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D50" t="str">
-        <v>¿Las instalaciones mecánicas embebidas fueron verificadas?</v>
+        <v>¿El encofrado está LIBERADO con su protocolo aprobado?</v>
       </c>
       <c r="E50" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1415,10 +1415,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C51" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D51" t="str">
-        <v>¿Los anclajes para estructuras metálicas fueron verificados?</v>
+        <v>¿Las instalaciones sanitarias embebidas están liberadas, tapadas y aseguradas para que no se desplacen durante el vaciado?</v>
       </c>
       <c r="E51" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1435,16 +1435,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C52" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D52" t="str">
-        <v>N° de batch</v>
+        <v>¿Las instalaciones eléctricas embebidas están liberadas, con guía y tapadas para que no se llenen de concreto?</v>
       </c>
       <c r="E52" t="str">
-        <v>texto-[]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F52" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="53">
@@ -1455,16 +1455,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C53" t="str">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D53" t="str">
-        <v>Tipo de concreto</v>
+        <v>¿Las instalaciones mecánicas embebidas están liberadas y aseguradas?</v>
       </c>
       <c r="E53" t="str">
-        <v>list-[HECHO EN OBRA, PREMEZCLADO]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F53" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="54">
@@ -1475,16 +1475,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C54" t="str">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D54" t="str">
-        <v>f'c de diseño (kg/cm²)</v>
+        <v>¿Los anclajes para estructuras metálicas están en posición, con plantilla y nivel verificados?</v>
       </c>
       <c r="E54" t="str">
-        <v>numerico-[100:700]:dec[0]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F54" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="55">
@@ -1495,16 +1495,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C55" t="str">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D55" t="str">
-        <v>Slump de diseño (pulg)</v>
+        <v>¿El equipo de vaciado está operativo y se cuenta con vibrador de RESERVA en el frente? (una falla a media losa deja cangrejeras)</v>
       </c>
       <c r="E55" t="str">
-        <v>numerico-[1:10]:dec[1]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F55" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="56">
@@ -1515,16 +1515,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C56" t="str">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D56" t="str">
-        <v>Volumen total (m³)</v>
+        <v>¿Las condiciones de clima y temperatura permiten vaciar según especificación, y se previó el manejo si cambian?</v>
       </c>
       <c r="E56" t="str">
-        <v>numerico-[0:500]:dec[2]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F56" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="57">
@@ -1535,13 +1535,13 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C57" t="str">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D57" t="str">
-        <v>Tipo de colocación</v>
+        <v>N° de batch</v>
       </c>
       <c r="E57" t="str">
-        <v>list-[DIRECTO, CON BOMBA, OTROS]</v>
+        <v>texto-[]</v>
       </c>
       <c r="F57" t="str">
         <v>DATOS DE LA COLOCACIÓN</v>
@@ -1555,13 +1555,13 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C58" t="str">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D58" t="str">
-        <v>Tipo de acabado</v>
+        <v>Tipo de concreto</v>
       </c>
       <c r="E58" t="str">
-        <v>list-[CARAVISTA, FROTACHADO, OTROS]</v>
+        <v>list-[HECHO EN OBRA, PREMEZCLADO]</v>
       </c>
       <c r="F58" t="str">
         <v>DATOS DE LA COLOCACIÓN</v>
@@ -1575,16 +1575,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C59" t="str">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D59" t="str">
-        <v>col-[A][Guía / Batch] // col-[B][Hora inicio] // col-[C][Hora fin] // col-[D][Slump (pulg)] // col-[E][Volumen (m³)] // col-[F][Código de testigos]</v>
+        <v>f'c de diseño (kg/cm²)</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>numerico-[100:700]:dec[0]</v>
       </c>
       <c r="F59" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="60">
@@ -1595,16 +1595,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C60" t="str">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D60" t="str">
-        <v>Batch 1</v>
+        <v>Slump de diseño (pulg)</v>
       </c>
       <c r="E60" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>numerico-[1:10]:dec[1]</v>
       </c>
       <c r="F60" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="61">
@@ -1615,16 +1615,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C61" t="str">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D61" t="str">
-        <v>Batch 2</v>
+        <v>Volumen total (m³)</v>
       </c>
       <c r="E61" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>numerico-[0:500]:dec[2]</v>
       </c>
       <c r="F61" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="62">
@@ -1635,16 +1635,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C62" t="str">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D62" t="str">
-        <v>Batch 3</v>
+        <v>Tipo de colocación</v>
       </c>
       <c r="E62" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>list-[DIRECTO, CON BOMBA, OTROS]</v>
       </c>
       <c r="F62" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="63">
@@ -1655,16 +1655,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C63" t="str">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D63" t="str">
-        <v>Batch 4</v>
+        <v>Tipo de acabado</v>
       </c>
       <c r="E63" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>list-[CARAVISTA, FROTACHADO, OTROS]</v>
       </c>
       <c r="F63" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="64">
@@ -1675,13 +1675,13 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C64" t="str">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D64" t="str">
-        <v>Batch 5</v>
+        <v>col-[A][Guía / Batch] // col-[B][Hora mezclado] // col-[C][Hora colocación] // col-[D][Slump (pulg)] // col-[E][Temp. (°C)] // col-[F][Volumen (m³)] // col-[G][Código de testigos]</v>
       </c>
       <c r="E64" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v/>
       </c>
       <c r="F64" t="str">
         <v>REGISTRO DE BATCHES</v>
@@ -1695,13 +1695,13 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C65" t="str">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D65" t="str">
-        <v>Batch 6</v>
+        <v>Batch 1</v>
       </c>
       <c r="E65" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F65" t="str">
         <v>REGISTRO DE BATCHES</v>
@@ -1715,13 +1715,13 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C66" t="str">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D66" t="str">
-        <v>Volumen total colocado (m³)</v>
+        <v>Batch 2</v>
       </c>
       <c r="E66" t="str">
-        <v>numerico-fx[SUMA(#18E:#23E)]:dec[2]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F66" t="str">
         <v>REGISTRO DE BATCHES</v>
@@ -1735,16 +1735,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C67" t="str">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D67" t="str">
-        <v>¿El acabado superficial corresponde a lo especificado?</v>
+        <v>Batch 3</v>
       </c>
       <c r="E67" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F67" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="68">
@@ -1755,16 +1755,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C68" t="str">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D68" t="str">
-        <v>¿El nivel y el aplomo final del elemento cumplen lo indicado en planos?</v>
+        <v>Batch 4</v>
       </c>
       <c r="E68" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F68" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="69">
@@ -1775,16 +1775,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C69" t="str">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D69" t="str">
-        <v>¿Los elementos embebidos quedaron en su posición final correcta?</v>
+        <v>Batch 5</v>
       </c>
       <c r="E69" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F69" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="70">
@@ -1795,16 +1795,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C70" t="str">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D70" t="str">
-        <v>¿El área quedó ordenada y limpia tras el vaciado?</v>
+        <v>Batch 6</v>
       </c>
       <c r="E70" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F70" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="71">
@@ -1815,156 +1815,156 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C71" t="str">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D71" t="str">
-        <v>¿Se aplicó el curado especificado? (agua, membrana u otro)</v>
+        <v>Volumen total colocado (m³)</v>
       </c>
       <c r="E71" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>numerico-fx[SUMA(#20F:#25F)]:dec[2]</v>
       </c>
       <c r="F71" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B72" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C72" t="str">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D72" t="str">
-        <v>¿Se ejecutó el trabajo conforme al procedimiento aprobado?</v>
+        <v>¿Se tomaron las probetas según norma (un juego por cada 50 m³ o fracción, mínimo uno por día de vaciado), identificadas y protegidas en obra? (NTP 339.033)</v>
       </c>
       <c r="E72" t="str">
-        <v>Verificación documental</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F72" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B73" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C73" t="str">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D73" t="str">
-        <v>¿El trazo y la ubicación del encofrado coinciden con el plano? (ejes, alineamiento, distancias y niveles)</v>
+        <v>¿El slump de cada batch se mantuvo dentro de la tolerancia del diseño y se rechazó el que no cumplía? (registrar rechazos en observaciones)</v>
       </c>
       <c r="E73" t="str">
-        <v>Medición topográfica</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F73" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B74" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C74" t="str">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D74" t="str">
-        <v>¿El encofrado está alineado, aplomado y sin deformaciones?</v>
+        <v>¿El acabado superficial corresponde al especificado y está libre de cangrejeras, segregación o juntas frías? (describir y ubicar cualquier defecto en observaciones)</v>
       </c>
       <c r="E74" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F74" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B75" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C75" t="str">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D75" t="str">
-        <v>¿Se colocaron los dados y separadores laterales que garantizan el recubrimiento?</v>
+        <v>¿El desplome del elemento terminado es menor a 6 mm por cada 3 m de altura y los niveles cumplen ±10 mm?</v>
       </c>
       <c r="E75" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F75" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B76" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C76" t="str">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D76" t="str">
-        <v>¿El encofrado está montado, fijado y arriostrado de forma estable?</v>
+        <v>¿Los elementos embebidos quedaron en su posición final, sin desplazamiento respecto al plano?</v>
       </c>
       <c r="E76" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F76" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B77" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C77" t="str">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D77" t="str">
-        <v>¿Las dimensiones internas del encofrado corresponden a lo especificado?</v>
+        <v>¿El curado se inició apenas el acabado lo permitió y se mantendrá al menos 7 días? (RNE E.060 — sin curado no se alcanza el f'c)</v>
       </c>
       <c r="E77" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F77" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B78" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C78" t="str">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D78" t="str">
-        <v>¿Se aplicó desmoldante y el interior del encofrado quedó limpio?</v>
+        <v>¿El área quedó ordenada y los residuos de concreto se retiraron antes de fraguar?</v>
       </c>
       <c r="E78" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F78" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="79">
@@ -1975,13 +1975,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C79" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D79" t="str">
-        <v>¿Están colocados los pases y tubos de instalaciones sanitarias según plano?</v>
+        <v>¿El diseño del encofrado y del apuntalamiento está aprobado y disponible en el frente, para las cargas de este elemento?</v>
       </c>
       <c r="E79" t="str">
-        <v>Verificación contra plano</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F79" t="str">
         <v>INSPECCIÓN</v>
@@ -1995,13 +1995,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C80" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D80" t="str">
-        <v>¿Están colocados los pases y tubos de instalaciones eléctricas según plano?</v>
+        <v>¿El trazo y los niveles del encofrado fueron verificados topográficamente, con desviación dentro de ±10 mm?</v>
       </c>
       <c r="E80" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F80" t="str">
         <v>INSPECCIÓN</v>
@@ -2015,13 +2015,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C81" t="str">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D81" t="str">
-        <v>¿Se colocaron los soportes y anclajes para los pases e instalaciones varias?</v>
+        <v>¿El desplome del encofrado es menor a 6 mm por cada 3 m de altura y no hay paneles alabeados ni deformados?</v>
       </c>
       <c r="E81" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F81" t="str">
         <v>INSPECCIÓN</v>
@@ -2035,13 +2035,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C82" t="str">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D82" t="str">
-        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas?</v>
+        <v>¿Las dimensiones internas están dentro de la tolerancia de la sección? (+12 mm / −6 mm respecto al plano)</v>
       </c>
       <c r="E82" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F82" t="str">
         <v>INSPECCIÓN</v>
@@ -2049,19 +2049,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B83" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C83" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D83" t="str">
-        <v>¿La varilla quedó alineada y centrada en su posición definitiva?</v>
+        <v>¿El apuntalamiento está completo, arriostrado y apoyado sobre superficie firme y nivelada, capaz de resistir el concreto fresco sin asentarse?</v>
       </c>
       <c r="E83" t="str">
-        <v>Medición topográfica</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F83" t="str">
         <v>INSPECCIÓN</v>
@@ -2069,19 +2069,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B84" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C84" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D84" t="str">
-        <v>¿Se respetó el recubrimiento mínimo de 2 cm respecto al borde del concreto?</v>
+        <v>¿Las juntas y encuentros del encofrado están sellados de modo que no se fugue lechada durante el vaciado?</v>
       </c>
       <c r="E84" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F84" t="str">
         <v>INSPECCIÓN</v>
@@ -2089,19 +2089,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B85" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C85" t="str">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D85" t="str">
-        <v>¿La perforación se ejecutó con rotomartillo y broca de carburo para concreto?</v>
+        <v>¿Los separadores laterales mantienen la armadura a la distancia correcta de la cara del encofrado en toda la altura?</v>
       </c>
       <c r="E85" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F85" t="str">
         <v>INSPECCIÓN</v>
@@ -2109,19 +2109,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B86" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C86" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D86" t="str">
-        <v>¿El diámetro de la perforación es mayor que el de la varilla, según la ficha técnica del anclaje?</v>
+        <v>¿El interior del encofrado está libre de recortes, alambres, aserrín y agua empozada?</v>
       </c>
       <c r="E86" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F86" t="str">
         <v>INSPECCIÓN</v>
@@ -2129,19 +2129,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B87" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C87" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D87" t="str">
-        <v>¿La perforación alcanza al menos 200 mm de profundidad en el concreto estructural?</v>
+        <v>¿El desmoldante se aplicó ANTES de montar la armadura, o sin contaminarla? (el desmoldante sobre las barras anula la adherencia con el concreto)</v>
       </c>
       <c r="E87" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F87" t="str">
         <v>INSPECCIÓN</v>
@@ -2149,19 +2149,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B88" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C88" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D88" t="str">
-        <v>¿Se limpió la perforación con aire comprimido y escobilla antes de inyectar?</v>
+        <v>¿Los pases y tubos de instalaciones sanitarias están según plano y fijados para no desplazarse durante el vaciado?</v>
       </c>
       <c r="E88" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F88" t="str">
         <v>INSPECCIÓN</v>
@@ -2169,19 +2169,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B89" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C89" t="str">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D89" t="str">
-        <v>¿El adhesivo se inyectó desde el fondo hasta dos tercios del volumen de la perforación?</v>
+        <v>¿Los pases y tubos de instalaciones eléctricas están según plano y fijados para no desplazarse durante el vaciado?</v>
       </c>
       <c r="E89" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F89" t="str">
         <v>INSPECCIÓN</v>
@@ -2189,19 +2189,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B90" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C90" t="str">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D90" t="str">
-        <v>¿La varilla se insertó girando hasta el fondo, cubriendo todo el corrugado con resina?</v>
+        <v>¿Los soportes y anclajes para instalaciones y estructuras metálicas están en su posición final y asegurados?</v>
       </c>
       <c r="E90" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F90" t="str">
         <v>INSPECCIÓN</v>
@@ -2209,16 +2209,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B91" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C91" t="str">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D91" t="str">
-        <v>¿Se respetó el tiempo de curado según la temperatura ambiente? (20 °C: 24 h · 10 °C: 48 h · menos de 5 °C: 72 h)</v>
+        <v>¿Está definido el plazo mínimo de desencofrado para este elemento y comunicado al personal? (evita el desencofrado prematuro)</v>
       </c>
       <c r="E91" t="str">
         <v>Verificación documental</v>
@@ -2229,16 +2229,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B92" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C92" t="str">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D92" t="str">
-        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas?</v>
+        <v>¿El frente cuenta con accesos seguros, barandas y protección de bordes, y la zona bajo el encofrado está señalizada?</v>
       </c>
       <c r="E92" t="str">
         <v>Inspección visual</v>
@@ -2249,219 +2249,216 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B93" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C93" t="str">
         <v>1</v>
       </c>
       <c r="D93" t="str">
-        <v>¿Las tuberías y accesorios se instalaron según el plano?</v>
+        <v>¿La varilla quedó alineada y centrada en su posición definitiva?</v>
       </c>
       <c r="E93" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F93" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B94" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C94" t="str">
         <v>2</v>
       </c>
       <c r="D94" t="str">
-        <v>¿El material instalado corresponde al especificado? (PVC)</v>
+        <v>¿Se respetó el recubrimiento mínimo de 2 cm respecto al borde del concreto?</v>
       </c>
       <c r="E94" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F94" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B95" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C95" t="str">
         <v>3</v>
       </c>
       <c r="D95" t="str">
-        <v>¿El diámetro de la tubería corresponde al indicado en el plano?</v>
+        <v>¿La perforación se ejecutó con rotomartillo y broca de carburo para concreto?</v>
       </c>
       <c r="E95" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F95" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B96" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C96" t="str">
         <v>4</v>
       </c>
       <c r="D96" t="str">
-        <v>¿El material está libre de defectos? (fisuras, deformaciones o golpes)</v>
+        <v>¿El diámetro de la perforación es mayor que el de la varilla, según la ficha técnica del anclaje?</v>
       </c>
       <c r="E96" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F96" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B97" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C97" t="str">
         <v>5</v>
       </c>
       <c r="D97" t="str">
-        <v>¿Las tuberías y accesorios están adecuadamente soportados y fijados?</v>
+        <v>¿La perforación alcanza al menos 200 mm de profundidad en el concreto estructural?</v>
       </c>
       <c r="E97" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F97" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B98" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C98" t="str">
         <v>6</v>
       </c>
       <c r="D98" t="str">
-        <v>¿Los terminales expuestos de tubería y las cajas de paso quedaron taponeados?</v>
+        <v>¿Se limpió la perforación con aire comprimido y escobilla antes de inyectar?</v>
       </c>
       <c r="E98" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F98" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B99" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C99" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D99" t="str">
-        <v>¿Los puntos están ubicados según el plano?</v>
+        <v>¿El adhesivo se inyectó desde el fondo hasta dos tercios del volumen de la perforación?</v>
       </c>
       <c r="E99" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F99" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B100" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C100" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D100" t="str">
-        <v>¿Las tuberías están libres de aplastamientos, roturas o dobleces que reduzcan su diámetro interior?</v>
+        <v>¿La varilla se insertó girando hasta el fondo, cubriendo todo el corrugado con resina?</v>
       </c>
       <c r="E100" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F100" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B101" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C101" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D101" t="str">
-        <v>¿Los accesorios son del mismo material y clase que la tubería? (uniones, conectores y curvas en PVC)</v>
+        <v>¿Se respetó el tiempo de curado según la temperatura ambiente? (20 °C: 24 h · 10 °C: 48 h · menos de 5 °C: 72 h)</v>
       </c>
       <c r="E101" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F101" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B102" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C102" t="str">
-        <v>4</v>
-      </c>
-      <c r="D102" t="str">
-        <v>¿Las cajas se colocaron según el trazo topográfico? (octogonales, rectangulares y de paso)</v>
+        <v>10</v>
       </c>
       <c r="E102" t="str">
-        <v>Medición topográfica</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F102" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B103" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C103" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D103" t="str">
-        <v>¿Las tuberías y accesorios están adecuadamente soportados y fijados?</v>
+        <v>¿Las tuberías y accesorios siguen el trazo del plano y los diámetros coinciden, verificados tramo por tramo?</v>
       </c>
       <c r="E103" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F103" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2469,19 +2466,19 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B104" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C104" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D104" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿El material y la clase corresponden a lo especificado, con marcado de fabricante y clase legible en la tubería?</v>
       </c>
       <c r="E104" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F104" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2489,19 +2486,19 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B105" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C105" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D105" t="str">
-        <v>¿El diámetro de la tubería corresponde al indicado en el plano?</v>
+        <v>¿El material está libre de fisuras, deformaciones por calor o golpes que comprometan la estanqueidad?</v>
       </c>
       <c r="E105" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F105" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2509,19 +2506,19 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B106" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C106" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D106" t="str">
-        <v>¿Las tuberías y accesorios están en buen estado?</v>
+        <v>¿La pendiente de los tramos de desagüe cumple el mínimo especificado (≥ 1 %), verificada con nivel en cada tramo?</v>
       </c>
       <c r="E106" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F106" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2529,262 +2526,262 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B107" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C107" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D107" t="str">
-        <v>¿La red instalada corresponde al tipo previsto? (agua fría o agua caliente)</v>
+        <v>¿Las uniones se ejecutaron con la técnica y el pegamento especificados, respetando el tiempo de fraguado antes de probar?</v>
       </c>
       <c r="E107" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F107" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B108" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C108" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D108" t="str">
-        <v>¿El material de la red corresponde al especificado? (PVC, PPR o acero)</v>
+        <v>¿Se ejecutó la prueba de estanqueidad del tramo y se mantuvo SIN pérdida durante el tiempo especificado? (registrar resultado en observaciones)</v>
       </c>
       <c r="E108" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F108" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B109" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C109" t="str">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D109" t="str">
-        <v>¿Los puntos de agua están ubicados según el plano?</v>
+        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
       </c>
       <c r="E109" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F109" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B110" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C110" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D110" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿Los terminales expuestos y las cajas de paso quedaron taponeados para impedir el ingreso de concreto o residuos?</v>
       </c>
       <c r="E110" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F110" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B111" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C111" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D111" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E111" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F111" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B112" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C112" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D112" t="str">
-        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
+        <v>¿El diámetro de la tubería corresponde al plano y el material y clase son los especificados?</v>
       </c>
       <c r="E112" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F112" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B113" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C113" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D113" t="str">
-        <v>¿Se instaló la válvula de paso donde indica el plano?</v>
+        <v>¿Las tuberías están libres de aplastamientos y roturas, y los radios de curvatura son mayores a 6 veces el diámetro? (curvas cerradas impiden el cableado)</v>
       </c>
       <c r="E113" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F113" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B114" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C114" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D114" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿Los accesorios son del mismo material y clase que la tubería, con marcado legible? (uniones, conectores y curvas)</v>
       </c>
       <c r="E114" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F114" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B115" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C115" t="str">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D115" t="str">
-        <v>¿Los puntos de desagüe están ubicados según el plano?</v>
+        <v>¿Las cajas están en el trazo y a la altura especificada, con desviación menor a ±2 cm? (octogonales, rectangulares y de paso)</v>
       </c>
       <c r="E115" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F115" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B116" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C116" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D116" t="str">
-        <v>¿El material de la red corresponde al especificado? (PVC o PPR)</v>
+        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
       </c>
       <c r="E116" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F116" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B117" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C117" t="str">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D117" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E117" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F117" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B118" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C118" t="str">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D118" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano?</v>
+        <v>¿Las tuberías y accesorios están en buen estado, sin tramos expuestos a golpes durante el vaciado?</v>
       </c>
       <c r="E118" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F118" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B119" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C119" t="str">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D119" t="str">
-        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E119" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F119" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="120">
@@ -2795,16 +2792,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C120" t="str">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D120" t="str">
-        <v>¿Se instalaron los puntos de urinario, registro y sumidero previstos?</v>
+        <v>¿La red instalada corresponde al tipo previsto y está diferenciada en obra? (agua fría / agua caliente)</v>
       </c>
       <c r="E120" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F120" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="121">
@@ -2815,16 +2812,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C121" t="str">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D121" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC, PPR o acero, con marcado legible)</v>
       </c>
       <c r="E121" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F121" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="122">
@@ -2835,16 +2832,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C122" t="str">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D122" t="str">
-        <v>¿Los puntos de ventilación están ubicados según el plano?</v>
+        <v>¿Los puntos de agua están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E122" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F122" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="123">
@@ -2855,16 +2852,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C123" t="str">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D123" t="str">
-        <v>¿El material de la red corresponde al especificado? (PVC o PPR)</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E123" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F123" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="124">
@@ -2875,16 +2872,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C124" t="str">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D124" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E124" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F124" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="125">
@@ -2895,16 +2892,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C125" t="str">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D125" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano?</v>
+        <v>¿El tipo y la separación entre salidas corresponden al aparato previsto, medida entre ejes? (ovalín, inodoro, urinario u otro)</v>
       </c>
       <c r="E125" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F125" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="126">
@@ -2915,356 +2912,356 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C126" t="str">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D126" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿Se instaló la válvula de paso donde indica el plano y queda accesible para mantenimiento?</v>
       </c>
       <c r="E126" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F126" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B127" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C127" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D127" t="str">
-        <v>¿La caja equipotencial y las cajas de paso están ubicadas según el plano?</v>
+        <v>¿El tramo pasó la prueba de presión sin pérdida durante el tiempo especificado? (registrar valor en observaciones)</v>
       </c>
       <c r="E127" t="str">
-        <v>Verificación contra plano</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F127" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B128" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C128" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D128" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E128" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F128" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B129" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C129" t="str">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D129" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿Los puntos de desagüe están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E129" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F129" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B130" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C130" t="str">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D130" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC o PPR, con marcado legible)</v>
       </c>
       <c r="E130" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F130" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B131" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C131" t="str">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D131" t="str">
-        <v>¿Los puntos están ubicados según el plano?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E131" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F131" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B132" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C132" t="str">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D132" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E132" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F132" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B133" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C133" t="str">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D133" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿La pendiente de los ramales cumple el mínimo especificado (≥ 1 %), verificada con nivel?</v>
       </c>
       <c r="E133" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F133" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B134" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C134" t="str">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D134" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
       </c>
       <c r="E134" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F134" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B135" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C135" t="str">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D135" t="str">
-        <v>¿Los puntos están ubicados según el plano?</v>
+        <v>¿Se instalaron los puntos de urinario, registro y sumidero previstos, y los registros quedan accesibles?</v>
       </c>
       <c r="E135" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F135" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B136" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C136" t="str">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D136" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿El tramo pasó la prueba de estanqueidad sin pérdida durante el tiempo especificado?</v>
       </c>
       <c r="E136" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F136" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B137" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C137" t="str">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D137" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E137" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F137" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B138" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C138" t="str">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D138" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿Los puntos de ventilación están en la ubicación y altura del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E138" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F138" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B139" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C139" t="str">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D139" t="str">
-        <v>¿Los puntos están ubicados según el plano?</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC o PPR)</v>
       </c>
       <c r="E139" t="str">
-        <v>Verificación contra plano</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F139" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B140" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C140" t="str">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D140" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E140" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F140" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B141" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C141" t="str">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D141" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E141" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F141" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B142" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C142" t="str">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D142" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿La ventilación remata según el plano y el recorrido queda libre de obstrucciones o tramos ahogados?</v>
       </c>
       <c r="E142" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F142" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B143" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C143" t="str">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D143" t="str">
-        <v>¿Los puntos están ubicados según el plano?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E143" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F143" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="144">
@@ -3275,16 +3272,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C144" t="str">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D144" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿La caja equipotencial y las cajas de paso están ubicadas según el plano y quedan accesibles para su medición posterior?</v>
       </c>
       <c r="E144" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F144" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="145">
@@ -3295,16 +3292,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C145" t="str">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D145" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E145" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F145" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="146">
@@ -3315,16 +3312,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C146" t="str">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D146" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E146" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F146" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="147">
@@ -3335,16 +3332,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C147" t="str">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D147" t="str">
-        <v>¿Los puntos están ubicados según el plano? (ACI y plano de intrusión)</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E147" t="str">
-        <v>Verificación contra plano</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F147" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="148">
@@ -3355,16 +3352,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C148" t="str">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D148" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E148" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F148" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="149">
@@ -3375,16 +3372,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C149" t="str">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D149" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E149" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F149" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="150">
@@ -3395,16 +3392,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C150" t="str">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D150" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E150" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F150" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="151">
@@ -3415,16 +3412,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C151" t="str">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D151" t="str">
-        <v>¿Los puntos están ubicados según el plano?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E151" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F151" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="152">
@@ -3435,16 +3432,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C152" t="str">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D152" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E152" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F152" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="153">
@@ -3455,16 +3452,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C153" t="str">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D153" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E153" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F153" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="154">
@@ -3475,16 +3472,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C154" t="str">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D154" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E154" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F154" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="155">
@@ -3495,16 +3492,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C155" t="str">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D155" t="str">
-        <v>¿Los puntos están ubicados según el plano?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E155" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F155" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="156">
@@ -3515,16 +3512,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C156" t="str">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D156" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E156" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F156" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="157">
@@ -3535,16 +3532,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C157" t="str">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D157" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E157" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F157" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="158">
@@ -3555,16 +3552,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C158" t="str">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D158" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E158" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F158" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="159">
@@ -3575,16 +3572,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C159" t="str">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D159" t="str">
-        <v>¿Los puntos están ubicados según el plano?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E159" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F159" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="160">
@@ -3595,16 +3592,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C160" t="str">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D160" t="str">
-        <v>¿El diámetro, el recorrido de la tubería, la caja y la altura corresponden al plano?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E160" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F160" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="161">
@@ -3615,16 +3612,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C161" t="str">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D161" t="str">
-        <v>¿La cantidad de puntos de salida coincide con el plano?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E161" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F161" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="162">
@@ -3635,821 +3632,1421 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C162" t="str">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D162" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E162" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F162" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B163" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C163" t="str">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D163" t="str">
-        <v>¿La zanja está ubicada según el plano?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E163" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F163" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B164" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C164" t="str">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D164" t="str">
-        <v>¿Las dimensiones de corte de la zanja cumplen el detalle? (ancho y profundidad)</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E164" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F164" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B165" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C165" t="str">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D165" t="str">
-        <v>¿La cama de arena tiene la altura indicada en el detalle?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E165" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F165" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B166" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C166" t="str">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D166" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E166" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F166" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B167" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C167" t="str">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D167" t="str">
-        <v>¿La cantidad de tuberías coincide con el plano?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E167" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F167" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B168" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C168" t="str">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D168" t="str">
-        <v>¿La separación entre tuberías cumple el detalle?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E168" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F168" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B169" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C169" t="str">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D169" t="str">
-        <v>¿Se colocó la señalización de la red según el detalle? (cinta o malla de advertencia)</v>
+        <v>¿Los puntos están ubicados según el plano, con desviación menor a 2 cm? (ACI y plano de intrusión)</v>
       </c>
       <c r="E169" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F169" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B170" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C170" t="str">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D170" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E170" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F170" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B171" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C171" t="str">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D171" t="str">
-        <v>¿El diámetro de la tubería que llega al buzón corresponde al plano?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E171" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F171" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B172" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C172" t="str">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D172" t="str">
-        <v>¿La cantidad de tuberías coincide con el plano?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E172" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F172" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B173" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C173" t="str">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D173" t="str">
-        <v>¿La separación entre tuberías cumple el detalle?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E173" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F173" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B174" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C174" t="str">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D174" t="str">
-        <v>¿Se respeta la distancia mínima entre el NPT y la tubería?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E174" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F174" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B175" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C175" t="str">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D175" t="str">
-        <v>¿El sumidero del buzón se ejecutó según el detalle?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E175" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F175" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B176" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C176" t="str">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D176" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E176" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F176" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B177" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C177" t="str">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D177" t="str">
-        <v>¿El trazo y replanteo de la red colgada fue verificado?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E177" t="str">
-        <v>Medición topográfica</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F177" t="str">
-        <v>REDES COLGADAS</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B178" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C178" t="str">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D178" t="str">
-        <v>¿El diámetro de la tubería o bandeja corresponde al plano?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E178" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F178" t="str">
-        <v>REDES COLGADAS</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B179" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C179" t="str">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D179" t="str">
-        <v>¿La cantidad de tuberías o bandejas coincide con el plano?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E179" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F179" t="str">
-        <v>REDES COLGADAS</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B180" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C180" t="str">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D180" t="str">
-        <v>¿La separación entre tuberías o bandejas cumple el detalle?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E180" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F180" t="str">
-        <v>REDES COLGADAS</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B181" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C181" t="str">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D181" t="str">
-        <v>¿Se respeta la distancia mínima entre el NPT y la tubería o bandeja?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E181" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F181" t="str">
-        <v>REDES COLGADAS</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B182" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C182" t="str">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D182" t="str">
-        <v>¿El área de trabajo quedó limpia y ordenada?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E182" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F182" t="str">
-        <v>REDES COLGADAS</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>PDA</v>
+        <v>PPIE</v>
       </c>
       <c r="B183" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C183" t="str">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D183" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E183" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F183" t="str">
-        <v>AMBIENTE 1</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>PDA</v>
+        <v>PPIE</v>
       </c>
       <c r="B184" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C184" t="str">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D184" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E184" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F184" t="str">
-        <v>AMBIENTE 1</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>PDA</v>
+        <v>PPIE</v>
       </c>
       <c r="B185" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C185" t="str">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D185" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E185" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F185" t="str">
-        <v>AMBIENTE 1</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>PDA</v>
+        <v>PPIE</v>
       </c>
       <c r="B186" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C186" t="str">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="D186" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E186" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F186" t="str">
-        <v>AMBIENTE 1</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>PDA</v>
+        <v>PPIE</v>
       </c>
       <c r="B187" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C187" t="str">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D187" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E187" t="str">
-        <v>Verificación contra plano</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F187" t="str">
-        <v>AMBIENTE 2</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>PDA</v>
+        <v>PPIE</v>
       </c>
       <c r="B188" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C188" t="str">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="D188" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E188" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F188" t="str">
-        <v>AMBIENTE 2</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B189" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C189" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D189" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿La zanja está en el trazo del plano y libre de interferencias con otras redes? (registrar cruces en observaciones)</v>
       </c>
       <c r="E189" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F189" t="str">
-        <v>AMBIENTE 2</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B190" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C190" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D190" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿El ancho y la PROFUNDIDAD de la zanja cumplen el detalle, medidos cada tramo? (la profundidad protege la red del tránsito superior)</v>
       </c>
       <c r="E190" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F190" t="str">
-        <v>AMBIENTE 2</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B191" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C191" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D191" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿La cama de arena tiene el espesor indicado y está libre de piedras que puedan dañar el ducto?</v>
       </c>
       <c r="E191" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F191" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B192" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C192" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D192" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E192" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F192" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B193" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C193" t="str">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D193" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿La cantidad de tuberías es exactamente la del plano, contadas una a una en el tramo?</v>
       </c>
       <c r="E193" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F193" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B194" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C194" t="str">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D194" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
       </c>
       <c r="E194" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F194" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B195" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C195" t="str">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D195" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿Se verificó que pasa la guía por cada ducto ANTES de tapar la zanja?</v>
       </c>
       <c r="E195" t="str">
-        <v>Verificación contra plano</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F195" t="str">
-        <v>AMBIENTE 4</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B196" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C196" t="str">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D196" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿La cinta o malla de advertencia está a la altura del detalle sobre el ducto, medida antes de completar el relleno? (evita el corte accidental en excavaciones futuras)</v>
       </c>
       <c r="E196" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F196" t="str">
-        <v>AMBIENTE 4</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B197" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C197" t="str">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D197" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿El relleno y la compactación se ejecutaron por capas según especificación, sin dañar el ducto?</v>
       </c>
       <c r="E197" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F197" t="str">
-        <v>AMBIENTE 4</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B198" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C198" t="str">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D198" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E198" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F198" t="str">
-        <v>AMBIENTE 4</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B199" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C199" t="str">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D199" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿El diámetro y la cantidad de tuberías que llegan al buzón corresponden al plano, contadas una a una?</v>
       </c>
       <c r="E199" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F199" t="str">
-        <v>AMBIENTE 5</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B200" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C200" t="str">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D200" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
       </c>
       <c r="E200" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F200" t="str">
-        <v>AMBIENTE 5</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B201" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C201" t="str">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D201" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿Se respeta la distancia mínima entre el NPT y la tubería, medida en el punto más desfavorable del tramo?</v>
       </c>
       <c r="E201" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F201" t="str">
-        <v>AMBIENTE 5</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B202" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C202" t="str">
+        <v>14</v>
+      </c>
+      <c r="D202" t="str">
+        <v>¿Las entradas al buzón quedaron selladas para impedir el ingreso de agua o tierra a los ductos?</v>
+      </c>
+      <c r="E202" t="str">
+        <v>Inspección visual</v>
+      </c>
+      <c r="F202" t="str">
+        <v>TRABAJOS EN BUZÓN</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B203" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C203" t="str">
+        <v>15</v>
+      </c>
+      <c r="D203" t="str">
+        <v>¿El sumidero del buzón drena sin empozar, verificado vertiendo agua?</v>
+      </c>
+      <c r="E203" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F203" t="str">
+        <v>TRABAJOS EN BUZÓN</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B204" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C204" t="str">
+        <v>16</v>
+      </c>
+      <c r="D204" t="str">
+        <v>¿La tapa instalada es de la clase especificada para el tránsito de esa zona y queda enrasada con el nivel de piso?</v>
+      </c>
+      <c r="E204" t="str">
+        <v>Verificación documental</v>
+      </c>
+      <c r="F204" t="str">
+        <v>TRABAJOS EN BUZÓN</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B205" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C205" t="str">
+        <v>17</v>
+      </c>
+      <c r="D205" t="str">
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+      </c>
+      <c r="E205" t="str">
+        <v>Inspección visual</v>
+      </c>
+      <c r="F205" t="str">
+        <v>TRABAJOS EN BUZÓN</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B206" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C206" t="str">
+        <v>18</v>
+      </c>
+      <c r="D206" t="str">
+        <v>¿El trazo y replanteo de la red colgada fue verificado topográficamente, con desviación menor a ±2 cm?</v>
+      </c>
+      <c r="E206" t="str">
+        <v>Medición topográfica</v>
+      </c>
+      <c r="F206" t="str">
+        <v>REDES COLGADAS</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B207" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C207" t="str">
+        <v>19</v>
+      </c>
+      <c r="D207" t="str">
+        <v>¿El diámetro y la cantidad de tuberías o bandejas corresponden al plano, contadas una a una?</v>
+      </c>
+      <c r="E207" t="str">
+        <v>Medición en campo</v>
+      </c>
+      <c r="F207" t="str">
+        <v>REDES COLGADAS</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B208" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C208" t="str">
+        <v>20</v>
+      </c>
+      <c r="D208" t="str">
+        <v>¿La separación entre tuberías o bandejas cumple el detalle, medida en al menos 3 puntos?</v>
+      </c>
+      <c r="E208" t="str">
+        <v>Medición en campo</v>
+      </c>
+      <c r="F208" t="str">
+        <v>REDES COLGADAS</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B209" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C209" t="str">
+        <v>21</v>
+      </c>
+      <c r="D209" t="str">
+        <v>¿Se respeta la distancia mínima entre el NPT y la tubería o bandeja, medida en el punto más desfavorable?</v>
+      </c>
+      <c r="E209" t="str">
+        <v>Medición en campo</v>
+      </c>
+      <c r="F209" t="str">
+        <v>REDES COLGADAS</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B210" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C210" t="str">
+        <v>22</v>
+      </c>
+      <c r="D210" t="str">
+        <v>¿Los soportes están al espaciamiento especificado y anclados a elemento estructural, no a falso cielo ni a tabique?</v>
+      </c>
+      <c r="E210" t="str">
+        <v>Medición en campo</v>
+      </c>
+      <c r="F210" t="str">
+        <v>REDES COLGADAS</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B211" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C211" t="str">
+        <v>23</v>
+      </c>
+      <c r="D211" t="str">
+        <v>¿Se verificó que pasa la guía por cada ducto antes de cerrar el falso cielo?</v>
+      </c>
+      <c r="E211" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F211" t="str">
+        <v>REDES COLGADAS</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>PRE</v>
+      </c>
+      <c r="B212" t="str">
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+      </c>
+      <c r="C212" t="str">
+        <v>24</v>
+      </c>
+      <c r="D212" t="str">
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+      </c>
+      <c r="E212" t="str">
+        <v>Inspección visual</v>
+      </c>
+      <c r="F212" t="str">
+        <v>REDES COLGADAS</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
         <v>PDA</v>
       </c>
-      <c r="B202" t="str">
+      <c r="B213" t="str">
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
-      <c r="C202" t="str">
+      <c r="C213" t="str">
+        <v>1</v>
+      </c>
+      <c r="D213" t="str">
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E213" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F213" t="str">
+        <v>AMBIENTE 1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B214" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C214" t="str">
+        <v>2</v>
+      </c>
+      <c r="D214" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E214" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F214" t="str">
+        <v>AMBIENTE 1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B215" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C215" t="str">
+        <v>3</v>
+      </c>
+      <c r="D215" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E215" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F215" t="str">
+        <v>AMBIENTE 1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B216" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C216" t="str">
+        <v>4</v>
+      </c>
+      <c r="D216" t="str">
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+      </c>
+      <c r="E216" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F216" t="str">
+        <v>AMBIENTE 1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B217" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C217" t="str">
+        <v>5</v>
+      </c>
+      <c r="D217" t="str">
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E217" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F217" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B218" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C218" t="str">
+        <v>6</v>
+      </c>
+      <c r="D218" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E218" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F218" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B219" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C219" t="str">
+        <v>7</v>
+      </c>
+      <c r="D219" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E219" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F219" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B220" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C220" t="str">
+        <v>8</v>
+      </c>
+      <c r="D220" t="str">
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+      </c>
+      <c r="E220" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F220" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B221" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C221" t="str">
+        <v>9</v>
+      </c>
+      <c r="D221" t="str">
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E221" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F221" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B222" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C222" t="str">
+        <v>10</v>
+      </c>
+      <c r="D222" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E222" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F222" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B223" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C223" t="str">
+        <v>11</v>
+      </c>
+      <c r="D223" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E223" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F223" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B224" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C224" t="str">
+        <v>12</v>
+      </c>
+      <c r="D224" t="str">
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+      </c>
+      <c r="E224" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F224" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B225" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C225" t="str">
+        <v>13</v>
+      </c>
+      <c r="D225" t="str">
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E225" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F225" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B226" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C226" t="str">
+        <v>14</v>
+      </c>
+      <c r="D226" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E226" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F226" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B227" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C227" t="str">
+        <v>15</v>
+      </c>
+      <c r="D227" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E227" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F227" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B228" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C228" t="str">
+        <v>16</v>
+      </c>
+      <c r="D228" t="str">
+        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+      </c>
+      <c r="E228" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F228" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B229" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C229" t="str">
+        <v>17</v>
+      </c>
+      <c r="D229" t="str">
+        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E229" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F229" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B230" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C230" t="str">
+        <v>18</v>
+      </c>
+      <c r="D230" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E230" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F230" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B231" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C231" t="str">
+        <v>19</v>
+      </c>
+      <c r="D231" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E231" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F231" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B232" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C232" t="str">
         <v>20</v>
       </c>
-      <c r="D202" t="str">
+      <c r="D232" t="str">
         <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
       </c>
-      <c r="E202" t="str">
+      <c r="E232" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
-      <c r="F202" t="str">
+      <c r="F232" t="str">
         <v>AMBIENTE 5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F232"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/01 Proyecto_Mercado_Mayorista/02 Excel Maestro/MAESTRO_Mercado_Mayorista_v1.xlsx
+++ b/01 Proyecto_Mercado_Mayorista/02 Excel Maestro/MAESTRO_Mercado_Mayorista_v1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F232"/>
+  <dimension ref="A1:F252"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -438,7 +438,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>¿El trazo lo ejecutó un topógrafo calificado?</v>
+        <v>¿El trazo lo ejecutó un topógrafo calificado, con habilitación vigente?</v>
       </c>
       <c r="E2" t="str">
         <v>Verificación documental</v>
@@ -458,7 +458,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>¿El terreno fue liberado y entregado para iniciar el trazo?</v>
+        <v>¿El equipo topográfico cuenta con certificado de calibración VIGENTE a la fecha del trabajo?</v>
       </c>
       <c r="E3" t="str">
         <v>Verificación documental</v>
@@ -478,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>¿Se verificaron el alineamiento, las medidas y la escuadra del trazo?</v>
+        <v>¿Se partió de puntos de control (BM y ejes) verificados y no alterados desde el último uso?</v>
       </c>
       <c r="E4" t="str">
         <v>Medición topográfica</v>
@@ -498,10 +498,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="str">
-        <v>¿El trazo coincide con el plano base, sin modificaciones? (de haberlas, detallarlas en observaciones)</v>
+        <v>¿El terreno fue liberado y entregado, libre de obstrucciones que impidan el trazo?</v>
       </c>
       <c r="E5" t="str">
-        <v>Verificación contra plano</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F5" t="str">
         <v>TRAZO INICIAL</v>
@@ -518,13 +518,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="str">
-        <v>¿Las dimensiones replanteadas de la estructura coinciden con el plano?</v>
+        <v>¿El alineamiento, las medidas y la escuadra cierran dentro de la tolerancia especificada? (registrar el error de cierre en observaciones)</v>
       </c>
       <c r="E6" t="str">
         <v>Medición topográfica</v>
       </c>
       <c r="F6" t="str">
-        <v>TRAZO REPLANTEADO</v>
+        <v>TRAZO INICIAL</v>
       </c>
     </row>
     <row r="7">
@@ -538,13 +538,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="str">
-        <v>¿Se materializaron en campo los vértices de la estructura?</v>
+        <v>¿El trazo coincide con el plano base, sin modificaciones? (de haberlas, detallarlas en observaciones)</v>
       </c>
       <c r="E7" t="str">
-        <v>Medición topográfica</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F7" t="str">
-        <v>TRAZO REPLANTEADO</v>
+        <v>TRAZO INICIAL</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="str">
-        <v>¿El trazo final de la estructura quedó marcado y verificado?</v>
+        <v>¿Las dimensiones replanteadas coinciden con el plano, con desviación dentro de ±10 mm?</v>
       </c>
       <c r="E8" t="str">
         <v>Medición topográfica</v>
@@ -578,10 +578,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="str">
-        <v>¿El equipo topográfico cuenta con certificado de calibración vigente?</v>
+        <v>¿Se materializaron en campo TODOS los vértices de la estructura, con marca estable y protegida?</v>
       </c>
       <c r="E9" t="str">
-        <v>Verificación documental</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F9" t="str">
         <v>TRAZO REPLANTEADO</v>
@@ -589,42 +589,42 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CTPT</v>
+        <v>CTTR</v>
       </c>
       <c r="B10" t="str">
-        <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
+        <v>CONTROL TOPOGRÁFICO TRAZO Y REPLANTEO</v>
       </c>
       <c r="C10" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D10" t="str">
-        <v>¿El levantamiento lo ejecutó un topógrafo calificado?</v>
+        <v>¿Los niveles replanteados están dentro de ±10 mm respecto a la cota de proyecto?</v>
       </c>
       <c r="E10" t="str">
-        <v>Verificación documental</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F10" t="str">
-        <v>TRAZO INICIAL</v>
+        <v>TRAZO REPLANTEADO</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CTPT</v>
+        <v>CTTR</v>
       </c>
       <c r="B11" t="str">
-        <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
+        <v>CONTROL TOPOGRÁFICO TRAZO Y REPLANTEO</v>
       </c>
       <c r="C11" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D11" t="str">
-        <v>¿El terreno fue liberado y entregado para iniciar el levantamiento?</v>
+        <v>¿El trazo final quedó marcado, verificado y con referencias que permitan reponerlo si se borra?</v>
       </c>
       <c r="E11" t="str">
-        <v>Verificación documental</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F11" t="str">
-        <v>TRAZO INICIAL</v>
+        <v>TRAZO REPLANTEADO</v>
       </c>
     </row>
     <row r="12">
@@ -635,13 +635,13 @@
         <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C12" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="str">
-        <v>¿Se verificaron el alineamiento, las medidas y la escuadra del levantamiento?</v>
+        <v>¿El levantamiento lo ejecutó un topógrafo calificado, con habilitación vigente?</v>
       </c>
       <c r="E12" t="str">
-        <v>Medición topográfica</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F12" t="str">
         <v>TRAZO INICIAL</v>
@@ -655,13 +655,13 @@
         <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C13" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="str">
-        <v>¿El levantamiento coincide con el plano base, sin modificaciones? (de haberlas, detallarlas en observaciones)</v>
+        <v>¿El equipo topográfico cuenta con certificado de calibración VIGENTE a la fecha del trabajo?</v>
       </c>
       <c r="E13" t="str">
-        <v>Verificación contra plano</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F13" t="str">
         <v>TRAZO INICIAL</v>
@@ -675,16 +675,16 @@
         <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C14" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="str">
-        <v>¿Las dimensiones levantadas de la estructura coinciden con el plano?</v>
+        <v>¿Se partió de puntos de control (BM y ejes) verificados y no alterados desde el último uso?</v>
       </c>
       <c r="E14" t="str">
         <v>Medición topográfica</v>
       </c>
       <c r="F14" t="str">
-        <v>TRAZO REPLANTEADO</v>
+        <v>TRAZO INICIAL</v>
       </c>
     </row>
     <row r="15">
@@ -695,16 +695,16 @@
         <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C15" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" t="str">
-        <v>¿Se materializaron en campo los vértices de la estructura?</v>
+        <v>¿El terreno fue liberado y entregado, libre de obstrucciones que impidan el levantamiento?</v>
       </c>
       <c r="E15" t="str">
-        <v>Medición topográfica</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F15" t="str">
-        <v>TRAZO REPLANTEADO</v>
+        <v>TRAZO INICIAL</v>
       </c>
     </row>
     <row r="16">
@@ -715,16 +715,16 @@
         <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C16" t="str">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" t="str">
-        <v>¿El trazo final de la estructura quedó marcado y verificado?</v>
+        <v>¿La densidad de puntos permite representar los quiebres reales del terreno, sin zonas interpoladas de más? (indicar zonas de baja densidad en observaciones)</v>
       </c>
       <c r="E16" t="str">
         <v>Medición topográfica</v>
       </c>
       <c r="F16" t="str">
-        <v>TRAZO REPLANTEADO</v>
+        <v>TRAZO INICIAL</v>
       </c>
     </row>
     <row r="17">
@@ -735,96 +735,96 @@
         <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C17" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" t="str">
-        <v>¿Los espacios levantados quedaron señalizados en campo?</v>
+        <v>¿El cierre del levantamiento está dentro de la tolerancia especificada? (registrar el error en observaciones)</v>
       </c>
       <c r="E17" t="str">
-        <v>Inspección visual</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F17" t="str">
-        <v>TRAZO REPLANTEADO</v>
+        <v>TRAZO INICIAL</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>LIPMPP</v>
+        <v>CTPT</v>
       </c>
       <c r="B18" t="str">
-        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
+        <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C18" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D18" t="str">
-        <v>Diámetro de pernos de anclaje</v>
+        <v>¿Las dimensiones levantadas coinciden con el plano, con desviación dentro de ±10 mm?</v>
       </c>
       <c r="E18" t="str">
-        <v>list-[3/8", 5/8", 3/4"]</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F18" t="str">
-        <v>DATOS DEL ELEMENTO Y EQUIPO</v>
+        <v>TRAZO REPLANTEADO</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>LIPMPP</v>
+        <v>CTPT</v>
       </c>
       <c r="B19" t="str">
-        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
+        <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C19" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D19" t="str">
-        <v>Equipo topográfico utilizado</v>
+        <v>¿Las diferencias entre el terreno levantado y el plano de proyecto están identificadas y cuantificadas? (afectan metrados y movimiento de tierras)</v>
       </c>
       <c r="E19" t="str">
-        <v>texto-[]</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F19" t="str">
-        <v>DATOS DEL ELEMENTO Y EQUIPO</v>
+        <v>TRAZO REPLANTEADO</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>LIPMPP</v>
+        <v>CTPT</v>
       </c>
       <c r="B20" t="str">
-        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
+        <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C20" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D20" t="str">
-        <v>N° de serie del equipo</v>
+        <v>¿Se materializaron en campo los vértices, con marca estable y protegida?</v>
       </c>
       <c r="E20" t="str">
-        <v>texto-[]</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F20" t="str">
-        <v>DATOS DEL ELEMENTO Y EQUIPO</v>
+        <v>TRAZO REPLANTEADO</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>LIPMPP</v>
+        <v>CTPT</v>
       </c>
       <c r="B21" t="str">
-        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
+        <v>CONTROL TOPOGRÁFICO LEVANTAMIENTO DEL TERRENO</v>
       </c>
       <c r="C21" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D21" t="str">
-        <v>Fecha de calibración del equipo</v>
+        <v>¿Los espacios levantados quedaron señalizados en campo y con referencias reponibles?</v>
       </c>
       <c r="E21" t="str">
-        <v>fecha-[]</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F21" t="str">
-        <v>DATOS DEL ELEMENTO Y EQUIPO</v>
+        <v>TRAZO REPLANTEADO</v>
       </c>
     </row>
     <row r="22">
@@ -835,16 +835,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C22" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D22" t="str">
-        <v>¿La base de la plancha metálica está correctamente ejecutada?</v>
+        <v>Diámetro de pernos de anclaje</v>
       </c>
       <c r="E22" t="str">
-        <v>list-[CONFORME, OBSERVADO, N/A]</v>
+        <v>list-[3/8", 5/8", 3/4"]</v>
       </c>
       <c r="F22" t="str">
-        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
+        <v>DATOS DEL ELEMENTO Y EQUIPO</v>
       </c>
     </row>
     <row r="23">
@@ -855,16 +855,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C23" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23" t="str">
-        <v>¿Los pernos de anclaje tienen la longitud y el diámetro especificados?</v>
+        <v>Equipo topográfico utilizado</v>
       </c>
       <c r="E23" t="str">
-        <v>list-[CONFORME, OBSERVADO, N/A]</v>
+        <v>texto-[]</v>
       </c>
       <c r="F23" t="str">
-        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
+        <v>DATOS DEL ELEMENTO Y EQUIPO</v>
       </c>
     </row>
     <row r="24">
@@ -875,16 +875,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C24" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D24" t="str">
-        <v>¿La plancha metálica está alineada según el plano?</v>
+        <v>N° de serie del equipo</v>
       </c>
       <c r="E24" t="str">
-        <v>list-[CONFORME, OBSERVADO, N/A]</v>
+        <v>texto-[]</v>
       </c>
       <c r="F24" t="str">
-        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
+        <v>DATOS DEL ELEMENTO Y EQUIPO</v>
       </c>
     </row>
     <row r="25">
@@ -895,16 +895,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C25" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" t="str">
-        <v>¿La plancha metálica y los pernos están nivelados?</v>
+        <v>Fecha de calibración del equipo</v>
       </c>
       <c r="E25" t="str">
-        <v>list-[CONFORME, OBSERVADO, N/A]</v>
+        <v>fecha-[]</v>
       </c>
       <c r="F25" t="str">
-        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
+        <v>DATOS DEL ELEMENTO Y EQUIPO</v>
       </c>
     </row>
     <row r="26">
@@ -915,10 +915,10 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C26" t="str">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26" t="str">
-        <v>¿La plancha y los pernos de anclaje guardan el alineamiento entre sí?</v>
+        <v>¿La superficie de apoyo de la plancha está limpia, nivelada y sin lechada suelta?</v>
       </c>
       <c r="E26" t="str">
         <v>list-[CONFORME, OBSERVADO, N/A]</v>
@@ -935,16 +935,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C27" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27" t="str">
-        <v>col-[A][Eje / Elemento] // col-[B][Norte (plano)] // col-[C][Este (plano)] // col-[D][Z (plano)] // col-[E][Norte (campo)] // col-[F][Este (campo)] // col-[G][Z (campo)] // col-[H][Var. Norte (m)] // col-[I][Var. Este (m)] // col-[J][Var. Z (m)] // col-[K][Dentro de tolerancia (1=Sí)]</v>
+        <v>¿Los pernos de anclaje tienen la longitud, el diámetro y el grado especificados, con rosca útil suficiente?</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>list-[CONFORME, OBSERVADO, N/A]</v>
       </c>
       <c r="F27" t="str">
-        <v>CONTROL DE COORDENADAS</v>
+        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
       </c>
     </row>
     <row r="28">
@@ -955,16 +955,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C28" t="str">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28" t="str">
-        <v>Detalle 1</v>
+        <v>¿La rosca de los pernos está protegida y sin daños ni concreto adherido?</v>
       </c>
       <c r="E28" t="str">
-        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#11E-#11B]:dec[3] // numerico-fx[#11F-#11C]:dec[3] // numerico-fx[#11G-#11D]:dec[3] // numerico-fx[SI(Y(ABS(#11H)&lt;=0.02, ABS(#11I)&lt;=0.02, ABS(#11J)&lt;=0.02), 1, 0)]:dec[0]</v>
+        <v>list-[CONFORME, OBSERVADO, N/A]</v>
       </c>
       <c r="F28" t="str">
-        <v>CONTROL DE COORDENADAS</v>
+        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
       </c>
     </row>
     <row r="29">
@@ -975,16 +975,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C29" t="str">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D29" t="str">
-        <v>Detalle 2</v>
+        <v>¿La plancha está alineada según el plano, con desviación dentro de la tolerancia de montaje?</v>
       </c>
       <c r="E29" t="str">
-        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#12E-#12B]:dec[3] // numerico-fx[#12F-#12C]:dec[3] // numerico-fx[#12G-#12D]:dec[3] // numerico-fx[SI(Y(ABS(#12H)&lt;=0.02, ABS(#12I)&lt;=0.02, ABS(#12J)&lt;=0.02), 1, 0)]:dec[0]</v>
+        <v>list-[CONFORME, OBSERVADO, N/A]</v>
       </c>
       <c r="F29" t="str">
-        <v>CONTROL DE COORDENADAS</v>
+        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
       </c>
     </row>
     <row r="30">
@@ -995,16 +995,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C30" t="str">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D30" t="str">
-        <v>Detalle 3</v>
+        <v>¿La plancha y los pernos están nivelados, verificados con nivel de precisión?</v>
       </c>
       <c r="E30" t="str">
-        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#13E-#13B]:dec[3] // numerico-fx[#13F-#13C]:dec[3] // numerico-fx[#13G-#13D]:dec[3] // numerico-fx[SI(Y(ABS(#13H)&lt;=0.02, ABS(#13I)&lt;=0.02, ABS(#13J)&lt;=0.02), 1, 0)]:dec[0]</v>
+        <v>list-[CONFORME, OBSERVADO, N/A]</v>
       </c>
       <c r="F30" t="str">
-        <v>CONTROL DE COORDENADAS</v>
+        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
       </c>
     </row>
     <row r="31">
@@ -1015,16 +1015,16 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C31" t="str">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D31" t="str">
-        <v>Detalle 4</v>
+        <v>¿La plantilla mantuvo la separación entre pernos durante el vaciado, sin desplazamiento?</v>
       </c>
       <c r="E31" t="str">
-        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#14E-#14B]:dec[3] // numerico-fx[#14F-#14C]:dec[3] // numerico-fx[#14G-#14D]:dec[3] // numerico-fx[SI(Y(ABS(#14H)&lt;=0.02, ABS(#14I)&lt;=0.02, ABS(#14J)&lt;=0.02), 1, 0)]:dec[0]</v>
+        <v>list-[CONFORME, OBSERVADO, N/A]</v>
       </c>
       <c r="F31" t="str">
-        <v>CONTROL DE COORDENADAS</v>
+        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
       </c>
     </row>
     <row r="32">
@@ -1035,136 +1035,136 @@
         <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C32" t="str">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D32" t="str">
-        <v>Detalle 5</v>
+        <v>¿Las coordenadas medidas en campo están dentro de la tolerancia de ±2 cm registrada en la tabla?</v>
       </c>
       <c r="E32" t="str">
-        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#15E-#15B]:dec[3] // numerico-fx[#15F-#15C]:dec[3] // numerico-fx[#15G-#15D]:dec[3] // numerico-fx[SI(Y(ABS(#15H)&lt;=0.02, ABS(#15I)&lt;=0.02, ABS(#15J)&lt;=0.02), 1, 0)]:dec[0]</v>
+        <v>list-[CONFORME, OBSERVADO, N/A]</v>
       </c>
       <c r="F32" t="str">
-        <v>CONTROL DE COORDENADAS</v>
+        <v>CHECK LIST — INSTALACIÓN DE PLANCHAS Y PERNOS</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>PA</v>
+        <v>LIPMPP</v>
       </c>
       <c r="B33" t="str">
-        <v>PROTOCOLO DE ACERO</v>
+        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C33" t="str">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D33" t="str">
-        <v>¿El acero cuenta con certificado de calidad del lote y corresponde al grado especificado? (grado y diámetro trazables a la colada)</v>
+        <v>col-[A][Eje / Elemento] // col-[B][Norte (plano)] // col-[C][Este (plano)] // col-[D][Z (plano)] // col-[E][Norte (campo)] // col-[F][Este (campo)] // col-[G][Z (campo)] // col-[H][Var. Norte (m)] // col-[I][Var. Este (m)] // col-[J][Var. Z (m)] // col-[K][Dentro de tolerancia (1=Sí)]</v>
       </c>
       <c r="E33" t="str">
-        <v>Verificación documental</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v>INSPECCIÓN</v>
+        <v>CONTROL DE COORDENADAS</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>PA</v>
+        <v>LIPMPP</v>
       </c>
       <c r="B34" t="str">
-        <v>PROTOCOLO DE ACERO</v>
+        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C34" t="str">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D34" t="str">
-        <v>¿El procedimiento de habilitación y colocación vigente está disponible en el frente y el personal fue instruido en él?</v>
+        <v>Detalle 1</v>
       </c>
       <c r="E34" t="str">
-        <v>Verificación documental</v>
+        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#13E-#13B]:dec[3] // numerico-fx[#13F-#13C]:dec[3] // numerico-fx[#13G-#13D]:dec[3] // numerico-fx[SI(Y(ABS(#13H)&lt;=0.02, ABS(#13I)&lt;=0.02, ABS(#13J)&lt;=0.02), 1, 0)]:dec[0]</v>
       </c>
       <c r="F34" t="str">
-        <v>INSPECCIÓN</v>
+        <v>CONTROL DE COORDENADAS</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>PA</v>
+        <v>LIPMPP</v>
       </c>
       <c r="B35" t="str">
-        <v>PROTOCOLO DE ACERO</v>
+        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C35" t="str">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D35" t="str">
-        <v>¿Se contrastaron los planos de las tres especialidades y NO quedan interferencias sin resolver? (listarlas en observaciones)</v>
+        <v>Detalle 2</v>
       </c>
       <c r="E35" t="str">
-        <v>Verificación contra plano</v>
+        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#14E-#14B]:dec[3] // numerico-fx[#14F-#14C]:dec[3] // numerico-fx[#14G-#14D]:dec[3] // numerico-fx[SI(Y(ABS(#14H)&lt;=0.02, ABS(#14I)&lt;=0.02, ABS(#14J)&lt;=0.02), 1, 0)]:dec[0]</v>
       </c>
       <c r="F35" t="str">
-        <v>INSPECCIÓN</v>
+        <v>CONTROL DE COORDENADAS</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>PA</v>
+        <v>LIPMPP</v>
       </c>
       <c r="B36" t="str">
-        <v>PROTOCOLO DE ACERO</v>
+        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C36" t="str">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D36" t="str">
-        <v>¿Los ejes y niveles del elemento fueron verificados topográficamente, con desviación dentro de ±10 mm respecto al plano?</v>
+        <v>Detalle 3</v>
       </c>
       <c r="E36" t="str">
-        <v>Medición topográfica</v>
+        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#15E-#15B]:dec[3] // numerico-fx[#15F-#15C]:dec[3] // numerico-fx[#15G-#15D]:dec[3] // numerico-fx[SI(Y(ABS(#15H)&lt;=0.02, ABS(#15I)&lt;=0.02, ABS(#15J)&lt;=0.02), 1, 0)]:dec[0]</v>
       </c>
       <c r="F36" t="str">
-        <v>INSPECCIÓN</v>
+        <v>CONTROL DE COORDENADAS</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>PA</v>
+        <v>LIPMPP</v>
       </c>
       <c r="B37" t="str">
-        <v>PROTOCOLO DE ACERO</v>
+        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C37" t="str">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D37" t="str">
-        <v>¿Los diámetros de las barras coinciden con el plano, verificados por marca de laminado o calibrador en al menos 3 barras por lecho?</v>
+        <v>Detalle 4</v>
       </c>
       <c r="E37" t="str">
-        <v>Medición en campo</v>
+        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#16E-#16B]:dec[3] // numerico-fx[#16F-#16C]:dec[3] // numerico-fx[#16G-#16D]:dec[3] // numerico-fx[SI(Y(ABS(#16H)&lt;=0.02, ABS(#16I)&lt;=0.02, ABS(#16J)&lt;=0.02), 1, 0)]:dec[0]</v>
       </c>
       <c r="F37" t="str">
-        <v>INSPECCIÓN</v>
+        <v>CONTROL DE COORDENADAS</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>PA</v>
+        <v>LIPMPP</v>
       </c>
       <c r="B38" t="str">
-        <v>PROTOCOLO DE ACERO</v>
+        <v>LIBERACIÓN DE INSTALACIÓN DE PLANCHAS METÁLICAS Y PERNOS PARA PEDESTAL</v>
       </c>
       <c r="C38" t="str">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D38" t="str">
-        <v>¿La cantidad de barras es EXACTAMENTE la del plano y el espaciamiento no se desvía más de ±2 cm?</v>
+        <v>Detalle 5</v>
       </c>
       <c r="E38" t="str">
-        <v>Medición en campo</v>
+        <v>texto-[] // numerico-[]:dec[3]:ej[8674250.000] // numerico-[]:dec[3]:ej[476320.000] // numerico-[]:dec[3]:ej[3260.000] // numerico-[]:dec[3]:ej[8674250.008] // numerico-[]:dec[3]:ej[476320.006] // numerico-[]:dec[3]:ej[3260.004] // numerico-fx[#17E-#17B]:dec[3] // numerico-fx[#17F-#17C]:dec[3] // numerico-fx[#17G-#17D]:dec[3] // numerico-fx[SI(Y(ABS(#17H)&lt;=0.02, ABS(#17I)&lt;=0.02, ABS(#17J)&lt;=0.02), 1, 0)]:dec[0]</v>
       </c>
       <c r="F38" t="str">
-        <v>INSPECCIÓN</v>
+        <v>CONTROL DE COORDENADAS</v>
       </c>
     </row>
     <row r="39">
@@ -1175,13 +1175,13 @@
         <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C39" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D39" t="str">
-        <v>¿Los traslapes cumplen la longitud indicada en el plano?</v>
+        <v>¿El acero cuenta con certificado de calidad del lote y corresponde al grado especificado? (grado y diámetro trazables a la colada)</v>
       </c>
       <c r="E39" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F39" t="str">
         <v>INSPECCIÓN</v>
@@ -1195,13 +1195,13 @@
         <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C40" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D40" t="str">
-        <v>¿NINGÚN traslape cae en zona de confinamiento ni donde el plano lo prohíbe? (RNE E.060 — cumplir la longitud no basta si está en la zona de máximo esfuerzo)</v>
+        <v>¿El procedimiento de habilitación y colocación vigente está disponible en el frente y el personal fue instruido en él?</v>
       </c>
       <c r="E40" t="str">
-        <v>Verificación contra plano</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F40" t="str">
         <v>INSPECCIÓN</v>
@@ -1215,13 +1215,13 @@
         <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C41" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D41" t="str">
-        <v>¿El espaciamiento de estribos cumple ±2 cm y la longitud de la zona de confinamiento coincide con el detalle? (RNE E.060)</v>
+        <v>¿Se contrastaron los planos de las tres especialidades y NO quedan interferencias sin resolver? (listarlas en observaciones)</v>
       </c>
       <c r="E41" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F41" t="str">
         <v>INSPECCIÓN</v>
@@ -1235,13 +1235,13 @@
         <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C42" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D42" t="str">
-        <v>¿El recubrimiento está garantizado con dados o separadores del espesor especificado, en cantidad suficiente para que la armadura no ceda durante el vaciado?</v>
+        <v>¿Los ejes y niveles del elemento fueron verificados topográficamente, con desviación dentro de ±10 mm respecto al plano?</v>
       </c>
       <c r="E42" t="str">
-        <v>Medición en campo</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F42" t="str">
         <v>INSPECCIÓN</v>
@@ -1255,13 +1255,13 @@
         <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C43" t="str">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D43" t="str">
-        <v>¿Las armaduras están ancladas, fijadas y arriostradas de modo que no se desplacen durante el vaciado y el vibrado?</v>
+        <v>¿Los diámetros de las barras coinciden con el plano, verificados por marca de laminado o calibrador en al menos 3 barras por lecho?</v>
       </c>
       <c r="E43" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F43" t="str">
         <v>INSPECCIÓN</v>
@@ -1275,13 +1275,13 @@
         <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C44" t="str">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D44" t="str">
-        <v>¿Las barras están libres de óxido no adherente, grasa, aceite, pintura o lechada que reduzcan la adherencia con el concreto?</v>
+        <v>¿La cantidad de barras es EXACTAMENTE la del plano y el espaciamiento no se desvía más de ±2 cm?</v>
       </c>
       <c r="E44" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F44" t="str">
         <v>INSPECCIÓN</v>
@@ -1295,13 +1295,13 @@
         <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C45" t="str">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D45" t="str">
-        <v>¿El frente cuenta con las protecciones colectivas requeridas y las esperas verticales están tapadas? (líneas de vida, plataformas, barandas y tapas antiempalamiento)</v>
+        <v>¿Los traslapes cumplen la longitud indicada en el plano?</v>
       </c>
       <c r="E45" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F45" t="str">
         <v>INSPECCIÓN</v>
@@ -1309,122 +1309,122 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B46" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C46" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D46" t="str">
-        <v>¿El procedimiento de vaciado está definido para este elemento, incluyendo qué hacer ante lluvia, falla de bomba o junta fría no prevista?</v>
+        <v>¿NINGÚN traslape cae en zona de confinamiento ni donde el plano lo prohíbe? (RNE E.060 — cumplir la longitud no basta si está en la zona de máximo esfuerzo)</v>
       </c>
       <c r="E46" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F46" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B47" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C47" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D47" t="str">
-        <v>¿Los niveles de vaciado están marcados en el elemento y verificados topográficamente?</v>
+        <v>¿El espaciamiento de estribos cumple ±2 cm y la longitud de la zona de confinamiento coincide con el detalle? (RNE E.060)</v>
       </c>
       <c r="E47" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F47" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B48" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C48" t="str">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D48" t="str">
-        <v>¿Las juntas de construcción están en la ubicación prevista, con la superficie rugosa, limpia y saturada pero sin agua libre?</v>
+        <v>¿El recubrimiento está garantizado con dados o separadores del espesor especificado, en cantidad suficiente para que la armadura no ceda durante el vaciado?</v>
       </c>
       <c r="E48" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F48" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B49" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C49" t="str">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D49" t="str">
-        <v>¿El acero de refuerzo está LIBERADO con su protocolo aprobado?</v>
+        <v>¿Las armaduras están ancladas, fijadas y arriostradas de modo que no se desplacen durante el vaciado y el vibrado?</v>
       </c>
       <c r="E49" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F49" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B50" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C50" t="str">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D50" t="str">
-        <v>¿El encofrado está LIBERADO con su protocolo aprobado?</v>
+        <v>¿Las barras están libres de óxido no adherente, grasa, aceite, pintura o lechada que reduzcan la adherencia con el concreto?</v>
       </c>
       <c r="E50" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F50" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PCC</v>
+        <v>PA</v>
       </c>
       <c r="B51" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
+        <v>PROTOCOLO DE ACERO</v>
       </c>
       <c r="C51" t="str">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D51" t="str">
-        <v>¿Las instalaciones sanitarias embebidas están liberadas, tapadas y aseguradas para que no se desplacen durante el vaciado?</v>
+        <v>¿El frente cuenta con las protecciones colectivas requeridas y las esperas verticales están tapadas? (líneas de vida, plataformas, barandas y tapas antiempalamiento)</v>
       </c>
       <c r="E51" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F51" t="str">
-        <v>INSPECCIÓN PREVIA AL VACIADO</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="52">
@@ -1435,10 +1435,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C52" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D52" t="str">
-        <v>¿Las instalaciones eléctricas embebidas están liberadas, con guía y tapadas para que no se llenen de concreto?</v>
+        <v>¿El procedimiento de vaciado está definido para este elemento, incluyendo qué hacer ante lluvia, falla de bomba o junta fría no prevista?</v>
       </c>
       <c r="E52" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1455,10 +1455,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C53" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D53" t="str">
-        <v>¿Las instalaciones mecánicas embebidas están liberadas y aseguradas?</v>
+        <v>¿Los niveles de vaciado están marcados en el elemento y verificados topográficamente?</v>
       </c>
       <c r="E53" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1475,10 +1475,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C54" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D54" t="str">
-        <v>¿Los anclajes para estructuras metálicas están en posición, con plantilla y nivel verificados?</v>
+        <v>¿Las juntas de construcción están en la ubicación prevista, con la superficie rugosa, limpia y saturada pero sin agua libre?</v>
       </c>
       <c r="E54" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1495,10 +1495,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C55" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D55" t="str">
-        <v>¿El equipo de vaciado está operativo y se cuenta con vibrador de RESERVA en el frente? (una falla a media losa deja cangrejeras)</v>
+        <v>¿El acero de refuerzo está LIBERADO con su protocolo aprobado?</v>
       </c>
       <c r="E55" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1515,10 +1515,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C56" t="str">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D56" t="str">
-        <v>¿Las condiciones de clima y temperatura permiten vaciar según especificación, y se previó el manejo si cambian?</v>
+        <v>¿El encofrado está LIBERADO con su protocolo aprobado?</v>
       </c>
       <c r="E56" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1535,16 +1535,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C57" t="str">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D57" t="str">
-        <v>N° de batch</v>
+        <v>¿Las instalaciones sanitarias embebidas están liberadas, tapadas y aseguradas para que no se desplacen durante el vaciado?</v>
       </c>
       <c r="E57" t="str">
-        <v>texto-[]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F57" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="58">
@@ -1555,16 +1555,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C58" t="str">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D58" t="str">
-        <v>Tipo de concreto</v>
+        <v>¿Las instalaciones eléctricas embebidas están liberadas, con guía y tapadas para que no se llenen de concreto?</v>
       </c>
       <c r="E58" t="str">
-        <v>list-[HECHO EN OBRA, PREMEZCLADO]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F58" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="59">
@@ -1575,16 +1575,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C59" t="str">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D59" t="str">
-        <v>f'c de diseño (kg/cm²)</v>
+        <v>¿Las instalaciones mecánicas embebidas están liberadas y aseguradas?</v>
       </c>
       <c r="E59" t="str">
-        <v>numerico-[100:700]:dec[0]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F59" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="60">
@@ -1595,16 +1595,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C60" t="str">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D60" t="str">
-        <v>Slump de diseño (pulg)</v>
+        <v>¿Los anclajes para estructuras metálicas están en posición, con plantilla y nivel verificados?</v>
       </c>
       <c r="E60" t="str">
-        <v>numerico-[1:10]:dec[1]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F60" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="61">
@@ -1615,16 +1615,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C61" t="str">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D61" t="str">
-        <v>Volumen total (m³)</v>
+        <v>¿El equipo de vaciado está operativo y se cuenta con vibrador de RESERVA en el frente? (una falla a media losa deja cangrejeras)</v>
       </c>
       <c r="E61" t="str">
-        <v>numerico-[0:500]:dec[2]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F61" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="62">
@@ -1635,16 +1635,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C62" t="str">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D62" t="str">
-        <v>Tipo de colocación</v>
+        <v>¿Las condiciones de clima y temperatura permiten vaciar según especificación, y se previó el manejo si cambian?</v>
       </c>
       <c r="E62" t="str">
-        <v>list-[DIRECTO, CON BOMBA, OTROS]</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F62" t="str">
-        <v>DATOS DE LA COLOCACIÓN</v>
+        <v>INSPECCIÓN PREVIA AL VACIADO</v>
       </c>
     </row>
     <row r="63">
@@ -1655,13 +1655,13 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C63" t="str">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D63" t="str">
-        <v>Tipo de acabado</v>
+        <v>N° de batch</v>
       </c>
       <c r="E63" t="str">
-        <v>list-[CARAVISTA, FROTACHADO, OTROS]</v>
+        <v>texto-[]</v>
       </c>
       <c r="F63" t="str">
         <v>DATOS DE LA COLOCACIÓN</v>
@@ -1675,16 +1675,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C64" t="str">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D64" t="str">
-        <v>col-[A][Guía / Batch] // col-[B][Hora mezclado] // col-[C][Hora colocación] // col-[D][Slump (pulg)] // col-[E][Temp. (°C)] // col-[F][Volumen (m³)] // col-[G][Código de testigos]</v>
+        <v>Tipo de concreto</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>list-[HECHO EN OBRA, PREMEZCLADO]</v>
       </c>
       <c r="F64" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="65">
@@ -1695,16 +1695,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C65" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D65" t="str">
-        <v>Batch 1</v>
+        <v>f'c de diseño (kg/cm²)</v>
       </c>
       <c r="E65" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>numerico-[100:700]:dec[0]</v>
       </c>
       <c r="F65" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="66">
@@ -1715,16 +1715,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C66" t="str">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D66" t="str">
-        <v>Batch 2</v>
+        <v>Slump de diseño (pulg)</v>
       </c>
       <c r="E66" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>numerico-[1:10]:dec[1]</v>
       </c>
       <c r="F66" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="67">
@@ -1735,16 +1735,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C67" t="str">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D67" t="str">
-        <v>Batch 3</v>
+        <v>Volumen total (m³)</v>
       </c>
       <c r="E67" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>numerico-[0:500]:dec[2]</v>
       </c>
       <c r="F67" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="68">
@@ -1755,16 +1755,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C68" t="str">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D68" t="str">
-        <v>Batch 4</v>
+        <v>Tipo de colocación</v>
       </c>
       <c r="E68" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>list-[DIRECTO, CON BOMBA, OTROS]</v>
       </c>
       <c r="F68" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="69">
@@ -1775,16 +1775,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C69" t="str">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D69" t="str">
-        <v>Batch 5</v>
+        <v>Tipo de acabado</v>
       </c>
       <c r="E69" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v>list-[CARAVISTA, FROTACHADO, OTROS]</v>
       </c>
       <c r="F69" t="str">
-        <v>REGISTRO DE BATCHES</v>
+        <v>DATOS DE LA COLOCACIÓN</v>
       </c>
     </row>
     <row r="70">
@@ -1795,13 +1795,13 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C70" t="str">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D70" t="str">
-        <v>Batch 6</v>
+        <v>col-[A][Guía / Batch] // col-[B][Hora mezclado] // col-[C][Hora colocación] // col-[D][Slump (pulg)] // col-[E][Temp. (°C)] // col-[F][Volumen (m³)] // col-[G][Código de testigos]</v>
       </c>
       <c r="E70" t="str">
-        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
+        <v/>
       </c>
       <c r="F70" t="str">
         <v>REGISTRO DE BATCHES</v>
@@ -1815,13 +1815,13 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C71" t="str">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D71" t="str">
-        <v>Volumen total colocado (m³)</v>
+        <v>Batch 1</v>
       </c>
       <c r="E71" t="str">
-        <v>numerico-fx[SUMA(#20F:#25F)]:dec[2]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F71" t="str">
         <v>REGISTRO DE BATCHES</v>
@@ -1835,16 +1835,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C72" t="str">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D72" t="str">
-        <v>¿Se tomaron las probetas según norma (un juego por cada 50 m³ o fracción, mínimo uno por día de vaciado), identificadas y protegidas en obra? (NTP 339.033)</v>
+        <v>Batch 2</v>
       </c>
       <c r="E72" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F72" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="73">
@@ -1855,16 +1855,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C73" t="str">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D73" t="str">
-        <v>¿El slump de cada batch se mantuvo dentro de la tolerancia del diseño y se rechazó el que no cumplía? (registrar rechazos en observaciones)</v>
+        <v>Batch 3</v>
       </c>
       <c r="E73" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F73" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="74">
@@ -1875,16 +1875,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C74" t="str">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D74" t="str">
-        <v>¿El acabado superficial corresponde al especificado y está libre de cangrejeras, segregación o juntas frías? (describir y ubicar cualquier defecto en observaciones)</v>
+        <v>Batch 4</v>
       </c>
       <c r="E74" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F74" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="75">
@@ -1895,16 +1895,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C75" t="str">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D75" t="str">
-        <v>¿El desplome del elemento terminado es menor a 6 mm por cada 3 m de altura y los niveles cumplen ±10 mm?</v>
+        <v>Batch 5</v>
       </c>
       <c r="E75" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F75" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="76">
@@ -1915,16 +1915,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C76" t="str">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D76" t="str">
-        <v>¿Los elementos embebidos quedaron en su posición final, sin desplazamiento respecto al plano?</v>
+        <v>Batch 6</v>
       </c>
       <c r="E76" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F76" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="77">
@@ -1935,16 +1935,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C77" t="str">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D77" t="str">
-        <v>¿El curado se inició apenas el acabado lo permitió y se mantendrá al menos 7 días? (RNE E.060 — sin curado no se alcanza el f'c)</v>
+        <v>Volumen total colocado (m³)</v>
       </c>
       <c r="E77" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>numerico-fx[SUMA(#20F:#25F)]:dec[2]</v>
       </c>
       <c r="F77" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="78">
@@ -1955,10 +1955,10 @@
         <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C78" t="str">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D78" t="str">
-        <v>¿El área quedó ordenada y los residuos de concreto se retiraron antes de fraguar?</v>
+        <v>¿Se tomaron las probetas según norma (un juego por cada 50 m³ o fracción, mínimo uno por día de vaciado), identificadas y protegidas en obra? (NTP 339.033)</v>
       </c>
       <c r="E78" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -1969,122 +1969,122 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B79" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C79" t="str">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D79" t="str">
-        <v>¿El diseño del encofrado y del apuntalamiento está aprobado y disponible en el frente, para las cargas de este elemento?</v>
+        <v>¿El slump de cada batch se mantuvo dentro de la tolerancia del diseño y se rechazó el que no cumplía? (registrar rechazos en observaciones)</v>
       </c>
       <c r="E79" t="str">
-        <v>Verificación documental</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F79" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B80" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C80" t="str">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D80" t="str">
-        <v>¿El trazo y los niveles del encofrado fueron verificados topográficamente, con desviación dentro de ±10 mm?</v>
+        <v>¿El acabado superficial corresponde al especificado y está libre de cangrejeras, segregación o juntas frías? (describir y ubicar cualquier defecto en observaciones)</v>
       </c>
       <c r="E80" t="str">
-        <v>Medición topográfica</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F80" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B81" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C81" t="str">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D81" t="str">
-        <v>¿El desplome del encofrado es menor a 6 mm por cada 3 m de altura y no hay paneles alabeados ni deformados?</v>
+        <v>¿El desplome del elemento terminado es menor a 6 mm por cada 3 m de altura y los niveles cumplen ±10 mm?</v>
       </c>
       <c r="E81" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F81" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B82" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C82" t="str">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D82" t="str">
-        <v>¿Las dimensiones internas están dentro de la tolerancia de la sección? (+12 mm / −6 mm respecto al plano)</v>
+        <v>¿Los elementos embebidos quedaron en su posición final, sin desplazamiento respecto al plano?</v>
       </c>
       <c r="E82" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F82" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B83" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C83" t="str">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D83" t="str">
-        <v>¿El apuntalamiento está completo, arriostrado y apoyado sobre superficie firme y nivelada, capaz de resistir el concreto fresco sin asentarse?</v>
+        <v>¿El curado se inició apenas el acabado lo permitió y se mantendrá al menos 7 días? (RNE E.060 — sin curado no se alcanza el f'c)</v>
       </c>
       <c r="E83" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F83" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B84" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C84" t="str">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D84" t="str">
-        <v>¿Las juntas y encuentros del encofrado están sellados de modo que no se fugue lechada durante el vaciado?</v>
+        <v>¿El área quedó ordenada y los residuos de concreto se retiraron antes de fraguar?</v>
       </c>
       <c r="E84" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F84" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="85">
@@ -2095,13 +2095,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C85" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D85" t="str">
-        <v>¿Los separadores laterales mantienen la armadura a la distancia correcta de la cara del encofrado en toda la altura?</v>
+        <v>¿El diseño del encofrado y del apuntalamiento está aprobado y disponible en el frente, para las cargas de este elemento?</v>
       </c>
       <c r="E85" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F85" t="str">
         <v>INSPECCIÓN</v>
@@ -2115,13 +2115,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C86" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D86" t="str">
-        <v>¿El interior del encofrado está libre de recortes, alambres, aserrín y agua empozada?</v>
+        <v>¿El trazo y los niveles del encofrado fueron verificados topográficamente, con desviación dentro de ±10 mm?</v>
       </c>
       <c r="E86" t="str">
-        <v>Inspección visual</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F86" t="str">
         <v>INSPECCIÓN</v>
@@ -2135,13 +2135,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C87" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D87" t="str">
-        <v>¿El desmoldante se aplicó ANTES de montar la armadura, o sin contaminarla? (el desmoldante sobre las barras anula la adherencia con el concreto)</v>
+        <v>¿El desplome del encofrado es menor a 6 mm por cada 3 m de altura y no hay paneles alabeados ni deformados?</v>
       </c>
       <c r="E87" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F87" t="str">
         <v>INSPECCIÓN</v>
@@ -2155,13 +2155,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C88" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D88" t="str">
-        <v>¿Los pases y tubos de instalaciones sanitarias están según plano y fijados para no desplazarse durante el vaciado?</v>
+        <v>¿Las dimensiones internas están dentro de la tolerancia de la sección? (+12 mm / −6 mm respecto al plano)</v>
       </c>
       <c r="E88" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F88" t="str">
         <v>INSPECCIÓN</v>
@@ -2175,13 +2175,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C89" t="str">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D89" t="str">
-        <v>¿Los pases y tubos de instalaciones eléctricas están según plano y fijados para no desplazarse durante el vaciado?</v>
+        <v>¿El apuntalamiento está completo, arriostrado y apoyado sobre superficie firme y nivelada, capaz de resistir el concreto fresco sin asentarse?</v>
       </c>
       <c r="E89" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F89" t="str">
         <v>INSPECCIÓN</v>
@@ -2195,13 +2195,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C90" t="str">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D90" t="str">
-        <v>¿Los soportes y anclajes para instalaciones y estructuras metálicas están en su posición final y asegurados?</v>
+        <v>¿Las juntas y encuentros del encofrado están sellados de modo que no se fugue lechada durante el vaciado?</v>
       </c>
       <c r="E90" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F90" t="str">
         <v>INSPECCIÓN</v>
@@ -2215,13 +2215,13 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C91" t="str">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D91" t="str">
-        <v>¿Está definido el plazo mínimo de desencofrado para este elemento y comunicado al personal? (evita el desencofrado prematuro)</v>
+        <v>¿Los separadores laterales mantienen la armadura a la distancia correcta de la cara del encofrado en toda la altura?</v>
       </c>
       <c r="E91" t="str">
-        <v>Verificación documental</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F91" t="str">
         <v>INSPECCIÓN</v>
@@ -2235,10 +2235,10 @@
         <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C92" t="str">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D92" t="str">
-        <v>¿El frente cuenta con accesos seguros, barandas y protección de bordes, y la zona bajo el encofrado está señalizada?</v>
+        <v>¿El interior del encofrado está libre de recortes, alambres, aserrín y agua empozada?</v>
       </c>
       <c r="E92" t="str">
         <v>Inspección visual</v>
@@ -2249,19 +2249,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B93" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C93" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D93" t="str">
-        <v>¿La varilla quedó alineada y centrada en su posición definitiva?</v>
+        <v>¿El desmoldante se aplicó ANTES de montar la armadura, o sin contaminarla? (el desmoldante sobre las barras anula la adherencia con el concreto)</v>
       </c>
       <c r="E93" t="str">
-        <v>Medición topográfica</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F93" t="str">
         <v>INSPECCIÓN</v>
@@ -2269,19 +2269,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B94" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C94" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D94" t="str">
-        <v>¿Se respetó el recubrimiento mínimo de 2 cm respecto al borde del concreto?</v>
+        <v>¿Los pases y tubos de instalaciones sanitarias están según plano y fijados para no desplazarse durante el vaciado?</v>
       </c>
       <c r="E94" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F94" t="str">
         <v>INSPECCIÓN</v>
@@ -2289,19 +2289,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B95" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C95" t="str">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D95" t="str">
-        <v>¿La perforación se ejecutó con rotomartillo y broca de carburo para concreto?</v>
+        <v>¿Los pases y tubos de instalaciones eléctricas están según plano y fijados para no desplazarse durante el vaciado?</v>
       </c>
       <c r="E95" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F95" t="str">
         <v>INSPECCIÓN</v>
@@ -2309,19 +2309,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B96" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C96" t="str">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D96" t="str">
-        <v>¿El diámetro de la perforación es mayor que el de la varilla, según la ficha técnica del anclaje?</v>
+        <v>¿Los soportes y anclajes para instalaciones y estructuras metálicas están en su posición final y asegurados?</v>
       </c>
       <c r="E96" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F96" t="str">
         <v>INSPECCIÓN</v>
@@ -2329,19 +2329,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B97" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C97" t="str">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D97" t="str">
-        <v>¿La perforación alcanza al menos 200 mm de profundidad en el concreto estructural?</v>
+        <v>¿Está definido el plazo mínimo de desencofrado para este elemento y comunicado al personal? (evita el desencofrado prematuro)</v>
       </c>
       <c r="E97" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F97" t="str">
         <v>INSPECCIÓN</v>
@@ -2349,16 +2349,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B98" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C98" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D98" t="str">
-        <v>¿Se limpió la perforación con aire comprimido y escobilla antes de inyectar?</v>
+        <v>¿El frente cuenta con accesos seguros, barandas y protección de bordes, y la zona bajo el encofrado está señalizada?</v>
       </c>
       <c r="E98" t="str">
         <v>Inspección visual</v>
@@ -2375,13 +2375,13 @@
         <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C99" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D99" t="str">
-        <v>¿El adhesivo se inyectó desde el fondo hasta dos tercios del volumen de la perforación?</v>
+        <v>¿El adhesivo está vigente (dentro de su fecha de caducidad) y se conservó según su ficha técnica?</v>
       </c>
       <c r="E99" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F99" t="str">
         <v>INSPECCIÓN</v>
@@ -2395,13 +2395,13 @@
         <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C100" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D100" t="str">
-        <v>¿La varilla se insertó girando hasta el fondo, cubriendo todo el corrugado con resina?</v>
+        <v>¿Se verificó con detector que la perforación NO corta armadura existente? (marcar los desvíos en observaciones)</v>
       </c>
       <c r="E100" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F100" t="str">
         <v>INSPECCIÓN</v>
@@ -2415,13 +2415,13 @@
         <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C101" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D101" t="str">
-        <v>¿Se respetó el tiempo de curado según la temperatura ambiente? (20 °C: 24 h · 10 °C: 48 h · menos de 5 °C: 72 h)</v>
+        <v>¿La varilla quedó alineada y centrada en su posición definitiva?</v>
       </c>
       <c r="E101" t="str">
-        <v>Verificación documental</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F101" t="str">
         <v>INSPECCIÓN</v>
@@ -2435,10 +2435,13 @@
         <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C102" t="str">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="D102" t="str">
+        <v>¿Se respetó el recubrimiento mínimo de 2 cm respecto al borde del concreto?</v>
       </c>
       <c r="E102" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F102" t="str">
         <v>INSPECCIÓN</v>
@@ -2446,219 +2449,219 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B103" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C103" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D103" t="str">
-        <v>¿Las tuberías y accesorios siguen el trazo del plano y los diámetros coinciden, verificados tramo por tramo?</v>
+        <v>¿La perforación se ejecutó con rotomartillo y broca de carburo para concreto?</v>
       </c>
       <c r="E103" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F103" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B104" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C104" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D104" t="str">
-        <v>¿El material y la clase corresponden a lo especificado, con marcado de fabricante y clase legible en la tubería?</v>
+        <v>¿El diámetro de la perforación es el que indica la ficha técnica del anclaje para esa varilla?</v>
       </c>
       <c r="E104" t="str">
-        <v>Verificación documental</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F104" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B105" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C105" t="str">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D105" t="str">
-        <v>¿El material está libre de fisuras, deformaciones por calor o golpes que comprometan la estanqueidad?</v>
+        <v>¿La perforación alcanza al menos 200 mm de profundidad en el concreto estructural, medida con sonda?</v>
       </c>
       <c r="E105" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F105" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B106" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C106" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D106" t="str">
-        <v>¿La pendiente de los tramos de desagüe cumple el mínimo especificado (≥ 1 %), verificada con nivel en cada tramo?</v>
+        <v>¿Se limpió la perforación con el ciclo completo (soplar, escobillar, soplar) hasta que sale sin polvo?</v>
       </c>
       <c r="E106" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F106" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B107" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C107" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D107" t="str">
-        <v>¿Las uniones se ejecutaron con la técnica y el pegamento especificados, respetando el tiempo de fraguado antes de probar?</v>
+        <v>¿El adhesivo se inyectó desde el fondo hacia afuera, sin dejar burbujas ni vacíos?</v>
       </c>
       <c r="E107" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F107" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B108" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C108" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D108" t="str">
-        <v>¿Se ejecutó la prueba de estanqueidad del tramo y se mantuvo SIN pérdida durante el tiempo especificado? (registrar resultado en observaciones)</v>
+        <v>¿La varilla se insertó girando hasta el fondo y rebosó adhesivo, señal de que el corrugado quedó cubierto?</v>
       </c>
       <c r="E108" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F108" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B109" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C109" t="str">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D109" t="str">
-        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
+        <v>¿Se respetó el tiempo de curado según la temperatura ambiente MEDIDA? (20 °C: 24 h · 10 °C: 48 h · menos de 5 °C: 72 h)</v>
       </c>
       <c r="E109" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F109" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>PIS</v>
+        <v>PAA</v>
       </c>
       <c r="B110" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C110" t="str">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D110" t="str">
-        <v>¿Los terminales expuestos y las cajas de paso quedaron taponeados para impedir el ingreso de concreto o residuos?</v>
+        <v>¿Los anclajes se mantuvieron sin carga ni vibración durante todo el curado?</v>
       </c>
       <c r="E110" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F110" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B111" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C111" t="str">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D111" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿Se ejecutó el ensayo de arranque en la proporción especificada y todos alcanzaron la carga de prueba? (registrar valores en observaciones)</v>
       </c>
       <c r="E111" t="str">
-        <v>Verificación contra plano</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F111" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B112" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C112" t="str">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D112" t="str">
-        <v>¿El diámetro de la tubería corresponde al plano y el material y clase son los especificados?</v>
+        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas y extracción de polvo?</v>
       </c>
       <c r="E112" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F112" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B113" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C113" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" t="str">
-        <v>¿Las tuberías están libres de aplastamientos y roturas, y los radios de curvatura son mayores a 6 veces el diámetro? (curvas cerradas impiden el cableado)</v>
+        <v>¿Las tuberías y accesorios siguen el trazo del plano y los diámetros coinciden, verificados tramo por tramo?</v>
       </c>
       <c r="E113" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F113" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2666,19 +2669,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B114" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C114" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D114" t="str">
-        <v>¿Los accesorios son del mismo material y clase que la tubería, con marcado legible? (uniones, conectores y curvas)</v>
+        <v>¿El material y la clase corresponden a lo especificado, con marcado de fabricante y clase legible en la tubería?</v>
       </c>
       <c r="E114" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F114" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2686,19 +2689,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B115" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C115" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D115" t="str">
-        <v>¿Las cajas están en el trazo y a la altura especificada, con desviación menor a ±2 cm? (octogonales, rectangulares y de paso)</v>
+        <v>¿El material está libre de fisuras, deformaciones por calor o golpes que comprometan la estanqueidad?</v>
       </c>
       <c r="E115" t="str">
-        <v>Medición topográfica</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F115" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2706,19 +2709,19 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B116" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C116" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D116" t="str">
-        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
+        <v>¿La pendiente de los tramos de desagüe cumple el mínimo especificado (≥ 1 %), verificada con nivel en cada tramo?</v>
       </c>
       <c r="E116" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F116" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2726,19 +2729,19 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B117" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C117" t="str">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D117" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿Las uniones se ejecutaron con la técnica y el pegamento especificados, respetando el tiempo de fraguado antes de probar?</v>
       </c>
       <c r="E117" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F117" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2746,19 +2749,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B118" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C118" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D118" t="str">
-        <v>¿Las tuberías y accesorios están en buen estado, sin tramos expuestos a golpes durante el vaciado?</v>
+        <v>¿Se ejecutó la prueba de estanqueidad del tramo y se mantuvo SIN pérdida durante el tiempo especificado? (registrar resultado en observaciones)</v>
       </c>
       <c r="E118" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F118" t="str">
         <v>DESCRIPCIÓN DE ACTIVIDADES</v>
@@ -2766,16 +2769,16 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>PIE</v>
+        <v>PIS</v>
       </c>
       <c r="B119" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C119" t="str">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D119" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
       </c>
       <c r="E119" t="str">
         <v>Inspección visual</v>
@@ -2786,202 +2789,202 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B120" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C120" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D120" t="str">
-        <v>¿La red instalada corresponde al tipo previsto y está diferenciada en obra? (agua fría / agua caliente)</v>
+        <v>¿Los terminales expuestos y las cajas de paso quedaron taponeados para impedir el ingreso de concreto o residuos?</v>
       </c>
       <c r="E120" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F120" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B121" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C121" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" t="str">
-        <v>¿El material y la clase de la red son los especificados? (PVC, PPR o acero, con marcado legible)</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E121" t="str">
-        <v>Verificación documental</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F121" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B122" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C122" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D122" t="str">
-        <v>¿Los puntos de agua están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
+        <v>¿El diámetro de la tubería corresponde al plano y el material y clase son los especificados?</v>
       </c>
       <c r="E122" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F122" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B123" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C123" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D123" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿Las tuberías están libres de aplastamientos y roturas, y los radios de curvatura son mayores a 6 veces el diámetro? (curvas cerradas impiden el cableado)</v>
       </c>
       <c r="E123" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F123" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B124" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C124" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D124" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
+        <v>¿Los accesorios son del mismo material y clase que la tubería, con marcado legible? (uniones, conectores y curvas)</v>
       </c>
       <c r="E124" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F124" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B125" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C125" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D125" t="str">
-        <v>¿El tipo y la separación entre salidas corresponden al aparato previsto, medida entre ejes? (ovalín, inodoro, urinario u otro)</v>
+        <v>¿Las cajas están en el trazo y a la altura especificada, con desviación menor a ±2 cm? (octogonales, rectangulares y de paso)</v>
       </c>
       <c r="E125" t="str">
-        <v>Medición en campo</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F125" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B126" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C126" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D126" t="str">
-        <v>¿Se instaló la válvula de paso donde indica el plano y queda accesible para mantenimiento?</v>
+        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
       </c>
       <c r="E126" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F126" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B127" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C127" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D127" t="str">
-        <v>¿El tramo pasó la prueba de presión sin pérdida durante el tiempo especificado? (registrar valor en observaciones)</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E127" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F127" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B128" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C128" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D128" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Las tuberías y accesorios están en buen estado, sin tramos expuestos a golpes durante el vaciado?</v>
       </c>
       <c r="E128" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F128" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B129" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C129" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D129" t="str">
-        <v>¿Los puntos de desagüe están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E129" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F129" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="130">
@@ -2992,16 +2995,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C130" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D130" t="str">
-        <v>¿El material y la clase de la red son los especificados? (PVC o PPR, con marcado legible)</v>
+        <v>¿La red instalada corresponde al tipo previsto y está diferenciada en obra? (agua fría / agua caliente)</v>
       </c>
       <c r="E130" t="str">
-        <v>Verificación documental</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F130" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="131">
@@ -3012,16 +3015,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C131" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D131" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC, PPR o acero, con marcado legible)</v>
       </c>
       <c r="E131" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F131" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="132">
@@ -3032,16 +3035,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C132" t="str">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D132" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
+        <v>¿Los puntos de agua están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E132" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F132" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="133">
@@ -3052,16 +3055,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C133" t="str">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D133" t="str">
-        <v>¿La pendiente de los ramales cumple el mínimo especificado (≥ 1 %), verificada con nivel?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E133" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F133" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="134">
@@ -3072,16 +3075,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C134" t="str">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D134" t="str">
-        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E134" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F134" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="135">
@@ -3092,16 +3095,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C135" t="str">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D135" t="str">
-        <v>¿Se instalaron los puntos de urinario, registro y sumidero previstos, y los registros quedan accesibles?</v>
+        <v>¿El tipo y la separación entre salidas corresponden al aparato previsto, medida entre ejes? (ovalín, inodoro, urinario u otro)</v>
       </c>
       <c r="E135" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F135" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="136">
@@ -3112,16 +3115,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C136" t="str">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D136" t="str">
-        <v>¿El tramo pasó la prueba de estanqueidad sin pérdida durante el tiempo especificado?</v>
+        <v>¿Se instaló la válvula de paso donde indica el plano y queda accesible para mantenimiento?</v>
       </c>
       <c r="E136" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F136" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="137">
@@ -3132,16 +3135,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C137" t="str">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D137" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿El tramo pasó la prueba de presión sin pérdida durante el tiempo especificado? (registrar valor en observaciones)</v>
       </c>
       <c r="E137" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F137" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="138">
@@ -3152,16 +3155,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C138" t="str">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D138" t="str">
-        <v>¿Los puntos de ventilación están en la ubicación y altura del plano, con desviación menor a ±2 cm?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E138" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F138" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="139">
@@ -3172,16 +3175,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C139" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D139" t="str">
-        <v>¿El material y la clase de la red son los especificados? (PVC o PPR)</v>
+        <v>¿Los puntos de desagüe están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E139" t="str">
-        <v>Verificación documental</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F139" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="140">
@@ -3192,16 +3195,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C140" t="str">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D140" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC o PPR, con marcado legible)</v>
       </c>
       <c r="E140" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F140" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="141">
@@ -3212,16 +3215,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C141" t="str">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D141" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E141" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F141" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="142">
@@ -3232,16 +3235,16 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C142" t="str">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D142" t="str">
-        <v>¿La ventilación remata según el plano y el recorrido queda libre de obstrucciones o tramos ahogados?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E142" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F142" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="143">
@@ -3252,207 +3255,207 @@
         <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C143" t="str">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D143" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿La pendiente de los ramales cumple el mínimo especificado (≥ 1 %), verificada con nivel?</v>
       </c>
       <c r="E143" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F143" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B144" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C144" t="str">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D144" t="str">
-        <v>¿La caja equipotencial y las cajas de paso están ubicadas según el plano y quedan accesibles para su medición posterior?</v>
+        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
       </c>
       <c r="E144" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F144" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B145" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C145" t="str">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D145" t="str">
-        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
+        <v>¿Se instalaron los puntos de urinario, registro y sumidero previstos, y los registros quedan accesibles?</v>
       </c>
       <c r="E145" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F145" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B146" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C146" t="str">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D146" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿El tramo pasó la prueba de estanqueidad sin pérdida durante el tiempo especificado?</v>
       </c>
       <c r="E146" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F146" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B147" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C147" t="str">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D147" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E147" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F147" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B148" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C148" t="str">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D148" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Los puntos de ventilación están en la ubicación y altura del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E148" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F148" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B149" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C149" t="str">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D149" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC o PPR)</v>
       </c>
       <c r="E149" t="str">
-        <v>Verificación contra plano</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F149" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B150" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C150" t="str">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D150" t="str">
-        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E150" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F150" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B151" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C151" t="str">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D151" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E151" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F151" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B152" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C152" t="str">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D152" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿La ventilación remata según el plano y el recorrido queda libre de obstrucciones o tramos ahogados?</v>
       </c>
       <c r="E152" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F152" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B153" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C153" t="str">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D153" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -3461,7 +3464,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F153" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="154">
@@ -3472,16 +3475,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C154" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D154" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿La caja equipotencial y las cajas de paso están ubicadas según el plano y quedan accesibles para su medición posterior?</v>
       </c>
       <c r="E154" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F154" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="155">
@@ -3492,7 +3495,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C155" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D155" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -3501,7 +3504,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F155" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="156">
@@ -3512,7 +3515,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C156" t="str">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D156" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -3521,7 +3524,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F156" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="157">
@@ -3532,7 +3535,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C157" t="str">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D157" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -3541,7 +3544,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F157" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="158">
@@ -3552,7 +3555,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C158" t="str">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D158" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -3561,7 +3564,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F158" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="159">
@@ -3572,7 +3575,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C159" t="str">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D159" t="str">
         <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
@@ -3581,7 +3584,7 @@
         <v>Verificación contra plano</v>
       </c>
       <c r="F159" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="160">
@@ -3592,7 +3595,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C160" t="str">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D160" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -3601,7 +3604,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F160" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="161">
@@ -3612,7 +3615,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C161" t="str">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D161" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -3621,7 +3624,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F161" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="162">
@@ -3632,7 +3635,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C162" t="str">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D162" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -3641,7 +3644,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F162" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="163">
@@ -3652,7 +3655,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C163" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D163" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -3661,7 +3664,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F163" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="164">
@@ -3672,7 +3675,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C164" t="str">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D164" t="str">
         <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
@@ -3681,7 +3684,7 @@
         <v>Verificación contra plano</v>
       </c>
       <c r="F164" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="165">
@@ -3692,7 +3695,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C165" t="str">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D165" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -3701,7 +3704,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F165" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="166">
@@ -3712,7 +3715,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C166" t="str">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D166" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -3721,7 +3724,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F166" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="167">
@@ -3732,7 +3735,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C167" t="str">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D167" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -3741,7 +3744,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F167" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="168">
@@ -3752,7 +3755,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C168" t="str">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D168" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -3761,7 +3764,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F168" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="169">
@@ -3772,16 +3775,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C169" t="str">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D169" t="str">
-        <v>¿Los puntos están ubicados según el plano, con desviación menor a 2 cm? (ACI y plano de intrusión)</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E169" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F169" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="170">
@@ -3792,7 +3795,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C170" t="str">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D170" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -3801,7 +3804,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F170" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="171">
@@ -3812,7 +3815,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C171" t="str">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D171" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -3821,7 +3824,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F171" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="172">
@@ -3832,7 +3835,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C172" t="str">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D172" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -3841,7 +3844,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F172" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="173">
@@ -3852,7 +3855,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C173" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D173" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -3861,7 +3864,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F173" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="174">
@@ -3872,7 +3875,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C174" t="str">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D174" t="str">
         <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
@@ -3881,7 +3884,7 @@
         <v>Verificación contra plano</v>
       </c>
       <c r="F174" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="175">
@@ -3892,7 +3895,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C175" t="str">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D175" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -3901,7 +3904,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F175" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="176">
@@ -3912,7 +3915,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C176" t="str">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D176" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -3921,7 +3924,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F176" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="177">
@@ -3932,7 +3935,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C177" t="str">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D177" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -3941,7 +3944,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F177" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="178">
@@ -3952,7 +3955,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C178" t="str">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D178" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -3961,7 +3964,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F178" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="179">
@@ -3972,16 +3975,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C179" t="str">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D179" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿Los puntos están ubicados según el plano, con desviación menor a 2 cm? (ACI y plano de intrusión)</v>
       </c>
       <c r="E179" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F179" t="str">
-        <v>DATA</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="180">
@@ -3992,7 +3995,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C180" t="str">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D180" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -4001,7 +4004,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F180" t="str">
-        <v>DATA</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="181">
@@ -4012,7 +4015,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C181" t="str">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D181" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -4021,7 +4024,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F181" t="str">
-        <v>DATA</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="182">
@@ -4032,7 +4035,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C182" t="str">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D182" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -4041,7 +4044,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F182" t="str">
-        <v>DATA</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="183">
@@ -4052,7 +4055,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C183" t="str">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D183" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -4061,7 +4064,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F183" t="str">
-        <v>DATA</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="184">
@@ -4072,7 +4075,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C184" t="str">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D184" t="str">
         <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
@@ -4081,7 +4084,7 @@
         <v>Verificación contra plano</v>
       </c>
       <c r="F184" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="185">
@@ -4092,7 +4095,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C185" t="str">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D185" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -4101,7 +4104,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F185" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="186">
@@ -4112,7 +4115,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C186" t="str">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D186" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -4121,7 +4124,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F186" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="187">
@@ -4132,7 +4135,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C187" t="str">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D187" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -4141,7 +4144,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F187" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="188">
@@ -4152,7 +4155,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C188" t="str">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D188" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -4161,198 +4164,198 @@
         <v>Inspección visual</v>
       </c>
       <c r="F188" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B189" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C189" t="str">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D189" t="str">
-        <v>¿La zanja está en el trazo del plano y libre de interferencias con otras redes? (registrar cruces en observaciones)</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E189" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F189" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B190" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C190" t="str">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D190" t="str">
-        <v>¿El ancho y la PROFUNDIDAD de la zanja cumplen el detalle, medidos cada tramo? (la profundidad protege la red del tránsito superior)</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E190" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F190" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B191" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C191" t="str">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="D191" t="str">
-        <v>¿La cama de arena tiene el espesor indicado y está libre de piedras que puedan dañar el ducto?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E191" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F191" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B192" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C192" t="str">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D192" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E192" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F192" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B193" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C193" t="str">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D193" t="str">
-        <v>¿La cantidad de tuberías es exactamente la del plano, contadas una a una en el tramo?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E193" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F193" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B194" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C194" t="str">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D194" t="str">
-        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E194" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F194" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B195" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C195" t="str">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D195" t="str">
-        <v>¿Se verificó que pasa la guía por cada ducto ANTES de tapar la zanja?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E195" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F195" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B196" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C196" t="str">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D196" t="str">
-        <v>¿La cinta o malla de advertencia está a la altura del detalle sobre el ducto, medida antes de completar el relleno? (evita el corte accidental en excavaciones futuras)</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E196" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F196" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B197" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C197" t="str">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D197" t="str">
-        <v>¿El relleno y la compactación se ejecutaron por capas según especificación, sin dañar el ducto?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E197" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F197" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B198" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C198" t="str">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D198" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -4361,7 +4364,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F198" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="199">
@@ -4372,16 +4375,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C199" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D199" t="str">
-        <v>¿El diámetro y la cantidad de tuberías que llegan al buzón corresponden al plano, contadas una a una?</v>
+        <v>¿La zanja está en el trazo del plano y libre de interferencias con otras redes? (registrar cruces en observaciones)</v>
       </c>
       <c r="E199" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F199" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="200">
@@ -4392,16 +4395,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C200" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D200" t="str">
-        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
+        <v>¿El ancho y la PROFUNDIDAD de la zanja cumplen el detalle, medidos cada tramo? (la profundidad protege la red del tránsito superior)</v>
       </c>
       <c r="E200" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F200" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="201">
@@ -4412,16 +4415,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C201" t="str">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D201" t="str">
-        <v>¿Se respeta la distancia mínima entre el NPT y la tubería, medida en el punto más desfavorable del tramo?</v>
+        <v>¿La cama de arena tiene el espesor indicado y está libre de piedras que puedan dañar el ducto?</v>
       </c>
       <c r="E201" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F201" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="202">
@@ -4432,16 +4435,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C202" t="str">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D202" t="str">
-        <v>¿Las entradas al buzón quedaron selladas para impedir el ingreso de agua o tierra a los ductos?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E202" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F202" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="203">
@@ -4452,16 +4455,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C203" t="str">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D203" t="str">
-        <v>¿El sumidero del buzón drena sin empozar, verificado vertiendo agua?</v>
+        <v>¿La cantidad de tuberías es exactamente la del plano, contadas una a una en el tramo?</v>
       </c>
       <c r="E203" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F203" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="204">
@@ -4472,16 +4475,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C204" t="str">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D204" t="str">
-        <v>¿La tapa instalada es de la clase especificada para el tránsito de esa zona y queda enrasada con el nivel de piso?</v>
+        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
       </c>
       <c r="E204" t="str">
-        <v>Verificación documental</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F204" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="205">
@@ -4492,16 +4495,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C205" t="str">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D205" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Se verificó que pasa la guía por cada ducto ANTES de tapar la zanja?</v>
       </c>
       <c r="E205" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F205" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="206">
@@ -4512,16 +4515,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C206" t="str">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D206" t="str">
-        <v>¿El trazo y replanteo de la red colgada fue verificado topográficamente, con desviación menor a ±2 cm?</v>
+        <v>¿La cinta o malla de advertencia está a la altura del detalle sobre el ducto, medida antes de completar el relleno? (evita el corte accidental en excavaciones futuras)</v>
       </c>
       <c r="E206" t="str">
-        <v>Medición topográfica</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F206" t="str">
-        <v>REDES COLGADAS</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="207">
@@ -4532,16 +4535,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C207" t="str">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D207" t="str">
-        <v>¿El diámetro y la cantidad de tuberías o bandejas corresponden al plano, contadas una a una?</v>
+        <v>¿El relleno y la compactación se ejecutaron por capas según especificación, sin dañar el ducto?</v>
       </c>
       <c r="E207" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F207" t="str">
-        <v>REDES COLGADAS</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="208">
@@ -4552,16 +4555,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C208" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D208" t="str">
-        <v>¿La separación entre tuberías o bandejas cumple el detalle, medida en al menos 3 puntos?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E208" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F208" t="str">
-        <v>REDES COLGADAS</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="209">
@@ -4572,16 +4575,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C209" t="str">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D209" t="str">
-        <v>¿Se respeta la distancia mínima entre el NPT y la tubería o bandeja, medida en el punto más desfavorable?</v>
+        <v>¿El diámetro y la cantidad de tuberías que llegan al buzón corresponden al plano, contadas una a una?</v>
       </c>
       <c r="E209" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F209" t="str">
-        <v>REDES COLGADAS</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="210">
@@ -4592,16 +4595,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C210" t="str">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D210" t="str">
-        <v>¿Los soportes están al espaciamiento especificado y anclados a elemento estructural, no a falso cielo ni a tabique?</v>
+        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
       </c>
       <c r="E210" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F210" t="str">
-        <v>REDES COLGADAS</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="211">
@@ -4612,16 +4615,16 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C211" t="str">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D211" t="str">
-        <v>¿Se verificó que pasa la guía por cada ducto antes de cerrar el falso cielo?</v>
+        <v>¿Se respeta la distancia mínima entre el NPT y la tubería, medida en el punto más desfavorable del tramo?</v>
       </c>
       <c r="E211" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F211" t="str">
-        <v>REDES COLGADAS</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="212">
@@ -4632,216 +4635,216 @@
         <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C212" t="str">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D212" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Las entradas al buzón quedaron selladas para impedir el ingreso de agua o tierra a los ductos?</v>
       </c>
       <c r="E212" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F212" t="str">
-        <v>REDES COLGADAS</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B213" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C213" t="str">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D213" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿El sumidero del buzón drena sin empozar, verificado vertiendo agua?</v>
       </c>
       <c r="E213" t="str">
-        <v>Verificación contra plano</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F213" t="str">
-        <v>AMBIENTE 1</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B214" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C214" t="str">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D214" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿La tapa instalada es de la clase especificada para el tránsito de esa zona y queda enrasada con el nivel de piso?</v>
       </c>
       <c r="E214" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F214" t="str">
-        <v>AMBIENTE 1</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B215" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C215" t="str">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D215" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E215" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F215" t="str">
-        <v>AMBIENTE 1</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B216" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C216" t="str">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D216" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿El trazo y replanteo de la red colgada fue verificado topográficamente, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E216" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F216" t="str">
-        <v>AMBIENTE 1</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B217" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C217" t="str">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D217" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿El diámetro y la cantidad de tuberías o bandejas corresponden al plano, contadas una a una?</v>
       </c>
       <c r="E217" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F217" t="str">
-        <v>AMBIENTE 2</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B218" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C218" t="str">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D218" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿La separación entre tuberías o bandejas cumple el detalle, medida en al menos 3 puntos?</v>
       </c>
       <c r="E218" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F218" t="str">
-        <v>AMBIENTE 2</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B219" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C219" t="str">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D219" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿Se respeta la distancia mínima entre el NPT y la tubería o bandeja, medida en el punto más desfavorable?</v>
       </c>
       <c r="E219" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F219" t="str">
-        <v>AMBIENTE 2</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B220" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C220" t="str">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D220" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿Los soportes están al espaciamiento especificado y anclados a elemento estructural, no a falso cielo ni a tabique?</v>
       </c>
       <c r="E220" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F220" t="str">
-        <v>AMBIENTE 2</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B221" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C221" t="str">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D221" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿Se verificó que pasa la guía por cada ducto antes de cerrar el falso cielo?</v>
       </c>
       <c r="E221" t="str">
-        <v>Verificación contra plano</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F221" t="str">
-        <v>AMBIENTE 3</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B222" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C222" t="str">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D222" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E222" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F222" t="str">
-        <v>AMBIENTE 3</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="223">
@@ -4852,16 +4855,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C223" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D223" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
       </c>
       <c r="E223" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F223" t="str">
-        <v>AMBIENTE 3</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="224">
@@ -4872,16 +4875,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C224" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D224" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
       </c>
       <c r="E224" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F224" t="str">
-        <v>AMBIENTE 3</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="225">
@@ -4892,16 +4895,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C225" t="str">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D225" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿La sirena se activa al operar el detector de humo?</v>
       </c>
       <c r="E225" t="str">
-        <v>Verificación contra plano</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F225" t="str">
-        <v>AMBIENTE 4</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="226">
@@ -4912,16 +4915,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C226" t="str">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D226" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
       </c>
       <c r="E226" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F226" t="str">
-        <v>AMBIENTE 4</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="227">
@@ -4932,16 +4935,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C227" t="str">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D227" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
       </c>
       <c r="E227" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F227" t="str">
-        <v>AMBIENTE 4</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="228">
@@ -4952,16 +4955,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C228" t="str">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D228" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
       </c>
       <c r="E228" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F228" t="str">
-        <v>AMBIENTE 4</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="229">
@@ -4972,16 +4975,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C229" t="str">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D229" t="str">
-        <v>¿Los dispositivos están ubicados según el plano? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
       </c>
       <c r="E229" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F229" t="str">
-        <v>AMBIENTE 5</v>
+        <v>AMBIENTE 2</v>
       </c>
     </row>
     <row r="230">
@@ -4992,7 +4995,7 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C230" t="str">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D230" t="str">
         <v>¿La sirena se activa al operar el sensor de temperatura?</v>
@@ -5001,7 +5004,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F230" t="str">
-        <v>AMBIENTE 5</v>
+        <v>AMBIENTE 2</v>
       </c>
     </row>
     <row r="231">
@@ -5012,7 +5015,7 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C231" t="str">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D231" t="str">
         <v>¿La sirena se activa al operar el detector de humo?</v>
@@ -5021,7 +5024,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F231" t="str">
-        <v>AMBIENTE 5</v>
+        <v>AMBIENTE 2</v>
       </c>
     </row>
     <row r="232">
@@ -5032,21 +5035,421 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C232" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D232" t="str">
-        <v>¿El tablero de control reconoce e identifica correctamente el circuito de alarma?</v>
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
       </c>
       <c r="E232" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F232" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B233" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C233" t="str">
+        <v>11</v>
+      </c>
+      <c r="D233" t="str">
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+      </c>
+      <c r="E233" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F233" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B234" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C234" t="str">
+        <v>12</v>
+      </c>
+      <c r="D234" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E234" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F234" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B235" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C235" t="str">
+        <v>13</v>
+      </c>
+      <c r="D235" t="str">
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E235" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F235" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B236" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C236" t="str">
+        <v>14</v>
+      </c>
+      <c r="D236" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E236" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F236" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B237" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C237" t="str">
+        <v>15</v>
+      </c>
+      <c r="D237" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E237" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F237" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B238" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C238" t="str">
+        <v>16</v>
+      </c>
+      <c r="D238" t="str">
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+      </c>
+      <c r="E238" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F238" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B239" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C239" t="str">
+        <v>17</v>
+      </c>
+      <c r="D239" t="str">
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+      </c>
+      <c r="E239" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F239" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B240" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C240" t="str">
+        <v>18</v>
+      </c>
+      <c r="D240" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E240" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F240" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B241" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C241" t="str">
+        <v>19</v>
+      </c>
+      <c r="D241" t="str">
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E241" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F241" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B242" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C242" t="str">
+        <v>20</v>
+      </c>
+      <c r="D242" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E242" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F242" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B243" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C243" t="str">
+        <v>21</v>
+      </c>
+      <c r="D243" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E243" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F243" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B244" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C244" t="str">
+        <v>22</v>
+      </c>
+      <c r="D244" t="str">
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+      </c>
+      <c r="E244" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F244" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B245" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C245" t="str">
+        <v>23</v>
+      </c>
+      <c r="D245" t="str">
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+      </c>
+      <c r="E245" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F245" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B246" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C246" t="str">
+        <v>24</v>
+      </c>
+      <c r="D246" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E246" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F246" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B247" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C247" t="str">
+        <v>25</v>
+      </c>
+      <c r="D247" t="str">
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E247" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F247" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B248" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C248" t="str">
+        <v>26</v>
+      </c>
+      <c r="D248" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E248" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F248" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B249" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C249" t="str">
+        <v>27</v>
+      </c>
+      <c r="D249" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E249" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F249" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B250" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C250" t="str">
+        <v>28</v>
+      </c>
+      <c r="D250" t="str">
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+      </c>
+      <c r="E250" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F250" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B251" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C251" t="str">
+        <v>29</v>
+      </c>
+      <c r="D251" t="str">
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+      </c>
+      <c r="E251" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F251" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B252" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C252" t="str">
+        <v>30</v>
+      </c>
+      <c r="D252" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E252" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F252" t="str">
         <v>AMBIENTE 5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F232"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F252"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/01 Proyecto_Mercado_Mayorista/02 Excel Maestro/MAESTRO_Mercado_Mayorista_v1.xlsx
+++ b/01 Proyecto_Mercado_Mayorista/02 Excel Maestro/MAESTRO_Mercado_Mayorista_v1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F277"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -1938,10 +1938,10 @@
         <v>26</v>
       </c>
       <c r="D77" t="str">
-        <v>Volumen total colocado (m³)</v>
+        <v>Batch 7</v>
       </c>
       <c r="E77" t="str">
-        <v>numerico-fx[SUMA(#20F:#25F)]:dec[2]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F77" t="str">
         <v>REGISTRO DE BATCHES</v>
@@ -1958,13 +1958,13 @@
         <v>27</v>
       </c>
       <c r="D78" t="str">
-        <v>¿Se tomaron las probetas según norma (un juego por cada 50 m³ o fracción, mínimo uno por día de vaciado), identificadas y protegidas en obra? (NTP 339.033)</v>
+        <v>Batch 8</v>
       </c>
       <c r="E78" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F78" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="79">
@@ -1978,13 +1978,13 @@
         <v>28</v>
       </c>
       <c r="D79" t="str">
-        <v>¿El slump de cada batch se mantuvo dentro de la tolerancia del diseño y se rechazó el que no cumplía? (registrar rechazos en observaciones)</v>
+        <v>Batch 9</v>
       </c>
       <c r="E79" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F79" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="80">
@@ -1998,13 +1998,13 @@
         <v>29</v>
       </c>
       <c r="D80" t="str">
-        <v>¿El acabado superficial corresponde al especificado y está libre de cangrejeras, segregación o juntas frías? (describir y ubicar cualquier defecto en observaciones)</v>
+        <v>Batch 10</v>
       </c>
       <c r="E80" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>texto-[] // hora-[] // hora-[] // numerico-[1:10]:dec[1] // numerico-[5:40]:dec[1] // numerico-[0:100]:dec[2] // texto-[]</v>
       </c>
       <c r="F80" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="81">
@@ -2018,13 +2018,13 @@
         <v>30</v>
       </c>
       <c r="D81" t="str">
-        <v>¿El desplome del elemento terminado es menor a 6 mm por cada 3 m de altura y los niveles cumplen ±10 mm?</v>
+        <v>Volumen total colocado (m³)</v>
       </c>
       <c r="E81" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>numerico-fx[SUMA(#20F:#29F)]:dec[2]</v>
       </c>
       <c r="F81" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="82">
@@ -2038,13 +2038,13 @@
         <v>31</v>
       </c>
       <c r="D82" t="str">
-        <v>¿Los elementos embebidos quedaron en su posición final, sin desplazamiento respecto al plano?</v>
+        <v>Desviación de volumen (%)</v>
       </c>
       <c r="E82" t="str">
-        <v>list-[SI, NO, NA]</v>
+        <v>numerico-fx[SI(#16A&gt;0, (#30A-#16A)/#16A*100, 0)]:dec[1]</v>
       </c>
       <c r="F82" t="str">
-        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
+        <v>REGISTRO DE BATCHES</v>
       </c>
     </row>
     <row r="83">
@@ -2058,7 +2058,7 @@
         <v>32</v>
       </c>
       <c r="D83" t="str">
-        <v>¿El curado se inició apenas el acabado lo permitió y se mantendrá al menos 7 días? (RNE E.060 — sin curado no se alcanza el f'c)</v>
+        <v>¿Se tomaron las probetas según norma (un juego por cada 50 m³ o fracción, mínimo uno por día de vaciado), identificadas y protegidas en obra? (NTP 339.033)</v>
       </c>
       <c r="E83" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -2078,7 +2078,7 @@
         <v>33</v>
       </c>
       <c r="D84" t="str">
-        <v>¿El área quedó ordenada y los residuos de concreto se retiraron antes de fraguar?</v>
+        <v>¿El slump de cada batch se mantuvo dentro de la tolerancia del diseño y se rechazó el que no cumplía? (registrar rechazos en observaciones)</v>
       </c>
       <c r="E84" t="str">
         <v>list-[SI, NO, NA]</v>
@@ -2089,519 +2089,519 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B85" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C85" t="str">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D85" t="str">
-        <v>¿El diseño del encofrado y del apuntalamiento está aprobado y disponible en el frente, para las cargas de este elemento?</v>
+        <v>¿El acabado superficial corresponde al especificado y está libre de cangrejeras, segregación o juntas frías? (describir y ubicar cualquier defecto en observaciones)</v>
       </c>
       <c r="E85" t="str">
-        <v>Verificación documental</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F85" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B86" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C86" t="str">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D86" t="str">
-        <v>¿El trazo y los niveles del encofrado fueron verificados topográficamente, con desviación dentro de ±10 mm?</v>
+        <v>¿El desplome del elemento terminado es menor a 6 mm por cada 3 m de altura y los niveles cumplen ±10 mm?</v>
       </c>
       <c r="E86" t="str">
-        <v>Medición topográfica</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F86" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B87" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C87" t="str">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D87" t="str">
-        <v>¿El desplome del encofrado es menor a 6 mm por cada 3 m de altura y no hay paneles alabeados ni deformados?</v>
+        <v>¿Los elementos embebidos quedaron en su posición final, sin desplazamiento respecto al plano?</v>
       </c>
       <c r="E87" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F87" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B88" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C88" t="str">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D88" t="str">
-        <v>¿Las dimensiones internas están dentro de la tolerancia de la sección? (+12 mm / −6 mm respecto al plano)</v>
+        <v>¿El curado se inició apenas el acabado lo permitió y se mantendrá al menos 7 días? (RNE E.060 — sin curado no se alcanza el f'c)</v>
       </c>
       <c r="E88" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F88" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PE</v>
+        <v>PCC</v>
       </c>
       <c r="B89" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE CONCRETO</v>
       </c>
       <c r="C89" t="str">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="D89" t="str">
-        <v>¿El apuntalamiento está completo, arriostrado y apoyado sobre superficie firme y nivelada, capaz de resistir el concreto fresco sin asentarse?</v>
+        <v>¿El área quedó ordenada y los residuos de concreto se retiraron antes de fraguar?</v>
       </c>
       <c r="E89" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F89" t="str">
-        <v>INSPECCIÓN</v>
+        <v>INSPECCIÓN POSTERIOR AL VACIADO</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B90" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C90" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D90" t="str">
-        <v>¿Las juntas y encuentros del encofrado están sellados de modo que no se fugue lechada durante el vaciado?</v>
+        <v>Elemento vaciado</v>
       </c>
       <c r="E90" t="str">
-        <v>Inspección visual</v>
+        <v>texto-[]</v>
       </c>
       <c r="F90" t="str">
-        <v>INSPECCIÓN</v>
+        <v>DATOS DEL VACIADO Y DISEÑO</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B91" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C91" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D91" t="str">
-        <v>¿Los separadores laterales mantienen la armadura a la distancia correcta de la cara del encofrado en toda la altura?</v>
+        <v>f'c de diseño (kg/cm²)</v>
       </c>
       <c r="E91" t="str">
-        <v>Medición en campo</v>
+        <v>numerico-[100:700]:dec[0]:ej[210]</v>
       </c>
       <c r="F91" t="str">
-        <v>INSPECCIÓN</v>
+        <v>DATOS DEL VACIADO Y DISEÑO</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B92" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C92" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D92" t="str">
-        <v>¿El interior del encofrado está libre de recortes, alambres, aserrín y agua empozada?</v>
+        <v>Fecha de vaciado</v>
       </c>
       <c r="E92" t="str">
-        <v>Inspección visual</v>
+        <v>fecha-[]</v>
       </c>
       <c r="F92" t="str">
-        <v>INSPECCIÓN</v>
+        <v>DATOS DEL VACIADO Y DISEÑO</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B93" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C93" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D93" t="str">
-        <v>¿El desmoldante se aplicó ANTES de montar la armadura, o sin contaminarla? (el desmoldante sobre las barras anula la adherencia con el concreto)</v>
+        <v>Guía / batch de origen</v>
       </c>
       <c r="E93" t="str">
-        <v>Inspección visual</v>
+        <v>texto-[]</v>
       </c>
       <c r="F93" t="str">
-        <v>INSPECCIÓN</v>
+        <v>DATOS DEL VACIADO Y DISEÑO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B94" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C94" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D94" t="str">
-        <v>¿Los pases y tubos de instalaciones sanitarias están según plano y fijados para no desplazarse durante el vaciado?</v>
+        <v>Laboratorio que ejecutó el ensayo</v>
       </c>
       <c r="E94" t="str">
-        <v>Verificación contra plano</v>
+        <v>texto-[]</v>
       </c>
       <c r="F94" t="str">
-        <v>INSPECCIÓN</v>
+        <v>DATOS DEL VACIADO Y DISEÑO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B95" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C95" t="str">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D95" t="str">
-        <v>¿Los pases y tubos de instalaciones eléctricas están según plano y fijados para no desplazarse durante el vaciado?</v>
+        <v>col-[A][Código de testigo] // col-[B][Fecha de rotura] // col-[C][Edad (días)] // col-[D][Diámetro (cm)] // col-[E][Altura (cm)] // col-[F][Carga máxima (kN)] // col-[G][Área (cm²)] // col-[H][f'c obtenido (kg/cm²)] // col-[I][% del diseño] // col-[J][Cumple individual (1=Sí)]</v>
       </c>
       <c r="E95" t="str">
-        <v>Verificación contra plano</v>
+        <v/>
       </c>
       <c r="F95" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B96" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C96" t="str">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D96" t="str">
-        <v>¿Los soportes y anclajes para instalaciones y estructuras metálicas están en su posición final y asegurados?</v>
+        <v>Testigo 1</v>
       </c>
       <c r="E96" t="str">
-        <v>Verificación contra plano</v>
+        <v>texto-[] // fecha-[] // numerico-[1:90]:dec[0]:ej[28] // numerico-[5:30]:dec[1]:ej[15.0] // numerico-[10:60]:dec[1]:ej[30.0] // numerico-[0:3000]:dec[1]:ej[371.0] // numerico-fx[3.14159265*POTENCIA(#7D/2, 2)]:dec[2] // numerico-fx[SI(#7G&gt;0, #7F*101.9716/#7G, 0)]:dec[1] // numerico-fx[SI(#2A&gt;0, #7H/#2A*100, 0)]:dec[1] // numerico-fx[SI(#7H &gt;= #2A - SI(#2A&lt;=350, 35, #2A*0.10), 1, 0)]:dec[0]</v>
       </c>
       <c r="F96" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B97" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C97" t="str">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D97" t="str">
-        <v>¿Está definido el plazo mínimo de desencofrado para este elemento y comunicado al personal? (evita el desencofrado prematuro)</v>
+        <v>Testigo 2</v>
       </c>
       <c r="E97" t="str">
-        <v>Verificación documental</v>
+        <v>texto-[] // fecha-[] // numerico-[1:90]:dec[0]:ej[28] // numerico-[5:30]:dec[1]:ej[15.0] // numerico-[10:60]:dec[1]:ej[30.0] // numerico-[0:3000]:dec[1]:ej[371.0] // numerico-fx[3.14159265*POTENCIA(#8D/2, 2)]:dec[2] // numerico-fx[SI(#8G&gt;0, #8F*101.9716/#8G, 0)]:dec[1] // numerico-fx[SI(#2A&gt;0, #8H/#2A*100, 0)]:dec[1] // numerico-fx[SI(#8H &gt;= #2A - SI(#2A&lt;=350, 35, #2A*0.10), 1, 0)]:dec[0]</v>
       </c>
       <c r="F97" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>PE</v>
+        <v>RCP</v>
       </c>
       <c r="B98" t="str">
-        <v>PROTOCOLO DE ENCOFRADO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C98" t="str">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D98" t="str">
-        <v>¿El frente cuenta con accesos seguros, barandas y protección de bordes, y la zona bajo el encofrado está señalizada?</v>
+        <v>Testigo 3</v>
       </c>
       <c r="E98" t="str">
-        <v>Inspección visual</v>
+        <v>texto-[] // fecha-[] // numerico-[1:90]:dec[0]:ej[28] // numerico-[5:30]:dec[1]:ej[15.0] // numerico-[10:60]:dec[1]:ej[30.0] // numerico-[0:3000]:dec[1]:ej[371.0] // numerico-fx[3.14159265*POTENCIA(#9D/2, 2)]:dec[2] // numerico-fx[SI(#9G&gt;0, #9F*101.9716/#9G, 0)]:dec[1] // numerico-fx[SI(#2A&gt;0, #9H/#2A*100, 0)]:dec[1] // numerico-fx[SI(#9H &gt;= #2A - SI(#2A&lt;=350, 35, #2A*0.10), 1, 0)]:dec[0]</v>
       </c>
       <c r="F98" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B99" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C99" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D99" t="str">
-        <v>¿El adhesivo está vigente (dentro de su fecha de caducidad) y se conservó según su ficha técnica?</v>
+        <v>Testigo 4</v>
       </c>
       <c r="E99" t="str">
-        <v>Verificación documental</v>
+        <v>texto-[] // fecha-[] // numerico-[1:90]:dec[0]:ej[28] // numerico-[5:30]:dec[1]:ej[15.0] // numerico-[10:60]:dec[1]:ej[30.0] // numerico-[0:3000]:dec[1]:ej[371.0] // numerico-fx[3.14159265*POTENCIA(#10D/2, 2)]:dec[2] // numerico-fx[SI(#10G&gt;0, #10F*101.9716/#10G, 0)]:dec[1] // numerico-fx[SI(#2A&gt;0, #10H/#2A*100, 0)]:dec[1] // numerico-fx[SI(#10H &gt;= #2A - SI(#2A&lt;=350, 35, #2A*0.10), 1, 0)]:dec[0]</v>
       </c>
       <c r="F99" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B100" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C100" t="str">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D100" t="str">
-        <v>¿Se verificó con detector que la perforación NO corta armadura existente? (marcar los desvíos en observaciones)</v>
+        <v>Testigo 5</v>
       </c>
       <c r="E100" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>texto-[] // fecha-[] // numerico-[1:90]:dec[0]:ej[28] // numerico-[5:30]:dec[1]:ej[15.0] // numerico-[10:60]:dec[1]:ej[30.0] // numerico-[0:3000]:dec[1]:ej[371.0] // numerico-fx[3.14159265*POTENCIA(#11D/2, 2)]:dec[2] // numerico-fx[SI(#11G&gt;0, #11F*101.9716/#11G, 0)]:dec[1] // numerico-fx[SI(#2A&gt;0, #11H/#2A*100, 0)]:dec[1] // numerico-fx[SI(#11H &gt;= #2A - SI(#2A&lt;=350, 35, #2A*0.10), 1, 0)]:dec[0]</v>
       </c>
       <c r="F100" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B101" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C101" t="str">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D101" t="str">
-        <v>¿La varilla quedó alineada y centrada en su posición definitiva?</v>
+        <v>Testigo 6</v>
       </c>
       <c r="E101" t="str">
-        <v>Medición topográfica</v>
+        <v>texto-[] // fecha-[] // numerico-[1:90]:dec[0]:ej[28] // numerico-[5:30]:dec[1]:ej[15.0] // numerico-[10:60]:dec[1]:ej[30.0] // numerico-[0:3000]:dec[1]:ej[371.0] // numerico-fx[3.14159265*POTENCIA(#12D/2, 2)]:dec[2] // numerico-fx[SI(#12G&gt;0, #12F*101.9716/#12G, 0)]:dec[1] // numerico-fx[SI(#2A&gt;0, #12H/#2A*100, 0)]:dec[1] // numerico-fx[SI(#12H &gt;= #2A - SI(#2A&lt;=350, 35, #2A*0.10), 1, 0)]:dec[0]</v>
       </c>
       <c r="F101" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B102" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C102" t="str">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D102" t="str">
-        <v>¿Se respetó el recubrimiento mínimo de 2 cm respecto al borde del concreto?</v>
+        <v>f'c promedio de los testigos (kg/cm²)</v>
       </c>
       <c r="E102" t="str">
-        <v>Medición en campo</v>
+        <v>numerico-fx[PROMEDIO(#7H:#12H)]:dec[1]</v>
       </c>
       <c r="F102" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B103" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C103" t="str">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D103" t="str">
-        <v>¿La perforación se ejecutó con rotomartillo y broca de carburo para concreto?</v>
+        <v>f'c mínimo individual (kg/cm²)</v>
       </c>
       <c r="E103" t="str">
-        <v>Inspección visual</v>
+        <v>numerico-fx[MIN(#7H:#12H)]:dec[1]</v>
       </c>
       <c r="F103" t="str">
-        <v>INSPECCIÓN</v>
+        <v>RESULTADOS DE ROTURA</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B104" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C104" t="str">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D104" t="str">
-        <v>¿El diámetro de la perforación es el que indica la ficha técnica del anclaje para esa varilla?</v>
+        <v>¿El f'c PROMEDIO alcanza o supera el f'c de diseño? (RNE E.060 — es el criterio principal de aceptación)</v>
       </c>
       <c r="E104" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F104" t="str">
-        <v>INSPECCIÓN</v>
+        <v>EVALUACIÓN DEL RESULTADO</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B105" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C105" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D105" t="str">
-        <v>¿La perforación alcanza al menos 200 mm de profundidad en el concreto estructural, medida con sonda?</v>
+        <v>¿NINGÚN testigo individual quedó por debajo del margen admitido? (35 kg/cm² si f'c ≤ 350; 10 % si es mayor)</v>
       </c>
       <c r="E105" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F105" t="str">
-        <v>INSPECCIÓN</v>
+        <v>EVALUACIÓN DEL RESULTADO</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B106" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C106" t="str">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D106" t="str">
-        <v>¿Se limpió la perforación con el ciclo completo (soplar, escobillar, soplar) hasta que sale sin polvo?</v>
+        <v>¿Las probetas se moldearon, curaron y transportaron según norma hasta el ensayo? (NTP 339.033 — un mal curado da resistencias bajas que NO son culpa del concreto)</v>
       </c>
       <c r="E106" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F106" t="str">
-        <v>INSPECCIÓN</v>
+        <v>EVALUACIÓN DEL RESULTADO</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B107" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C107" t="str">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D107" t="str">
-        <v>¿El adhesivo se inyectó desde el fondo hacia afuera, sin dejar burbujas ni vacíos?</v>
+        <v>¿El tipo de falla observado es el normal, sin indicios de mal moldeo o refrentado defectuoso?</v>
       </c>
       <c r="E107" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F107" t="str">
-        <v>INSPECCIÓN</v>
+        <v>EVALUACIÓN DEL RESULTADO</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B108" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C108" t="str">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D108" t="str">
-        <v>¿La varilla se insertó girando hasta el fondo y rebosó adhesivo, señal de que el corrugado quedó cubierto?</v>
+        <v>¿El laboratorio está acreditado y su certificado quedó adjunto al expediente?</v>
       </c>
       <c r="E108" t="str">
-        <v>Inspección visual</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F108" t="str">
-        <v>INSPECCIÓN</v>
+        <v>EVALUACIÓN DEL RESULTADO</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>PAA</v>
+        <v>RCP</v>
       </c>
       <c r="B109" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>RESISTENCIA A COMPRESIÓN DE PROBETAS</v>
       </c>
       <c r="C109" t="str">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D109" t="str">
-        <v>¿Se respetó el tiempo de curado según la temperatura ambiente MEDIDA? (20 °C: 24 h · 10 °C: 48 h · menos de 5 °C: 72 h)</v>
+        <v>¿El resultado se comunicó al residente y a la supervisión, y de ser NO CONFORME se abrió la no conformidad correspondiente?</v>
       </c>
       <c r="E109" t="str">
-        <v>Medición en campo</v>
+        <v>list-[SI, NO, NA]</v>
       </c>
       <c r="F109" t="str">
-        <v>INSPECCIÓN</v>
+        <v>EVALUACIÓN DEL RESULTADO</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B110" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C110" t="str">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D110" t="str">
-        <v>¿Los anclajes se mantuvieron sin carga ni vibración durante todo el curado?</v>
+        <v>¿El diseño del encofrado y del apuntalamiento está aprobado y disponible en el frente, para las cargas de este elemento?</v>
       </c>
       <c r="E110" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F110" t="str">
         <v>INSPECCIÓN</v>
@@ -2609,19 +2609,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B111" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C111" t="str">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D111" t="str">
-        <v>¿Se ejecutó el ensayo de arranque en la proporción especificada y todos alcanzaron la carga de prueba? (registrar valores en observaciones)</v>
+        <v>¿El trazo y los niveles del encofrado fueron verificados topográficamente, con desviación dentro de ±10 mm?</v>
       </c>
       <c r="E111" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F111" t="str">
         <v>INSPECCIÓN</v>
@@ -2629,19 +2629,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>PAA</v>
+        <v>PE</v>
       </c>
       <c r="B112" t="str">
-        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C112" t="str">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D112" t="str">
-        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas y extracción de polvo?</v>
+        <v>¿El desplome del encofrado es menor a 6 mm por cada 3 m de altura y no hay paneles alabeados ni deformados?</v>
       </c>
       <c r="E112" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F112" t="str">
         <v>INSPECCIÓN</v>
@@ -2649,1013 +2649,1013 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>PIS</v>
+        <v>PE</v>
       </c>
       <c r="B113" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C113" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D113" t="str">
-        <v>¿Las tuberías y accesorios siguen el trazo del plano y los diámetros coinciden, verificados tramo por tramo?</v>
+        <v>¿Las dimensiones internas están dentro de la tolerancia de la sección? (+12 mm / −6 mm respecto al plano)</v>
       </c>
       <c r="E113" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F113" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>PIS</v>
+        <v>PE</v>
       </c>
       <c r="B114" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C114" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D114" t="str">
-        <v>¿El material y la clase corresponden a lo especificado, con marcado de fabricante y clase legible en la tubería?</v>
+        <v>¿El apuntalamiento está completo, arriostrado y apoyado sobre superficie firme y nivelada, capaz de resistir el concreto fresco sin asentarse?</v>
       </c>
       <c r="E114" t="str">
-        <v>Verificación documental</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F114" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>PIS</v>
+        <v>PE</v>
       </c>
       <c r="B115" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C115" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D115" t="str">
-        <v>¿El material está libre de fisuras, deformaciones por calor o golpes que comprometan la estanqueidad?</v>
+        <v>¿Las juntas y encuentros del encofrado están sellados de modo que no se fugue lechada durante el vaciado?</v>
       </c>
       <c r="E115" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F115" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>PIS</v>
+        <v>PE</v>
       </c>
       <c r="B116" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C116" t="str">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D116" t="str">
-        <v>¿La pendiente de los tramos de desagüe cumple el mínimo especificado (≥ 1 %), verificada con nivel en cada tramo?</v>
+        <v>¿Los separadores laterales mantienen la armadura a la distancia correcta de la cara del encofrado en toda la altura?</v>
       </c>
       <c r="E116" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F116" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>PIS</v>
+        <v>PE</v>
       </c>
       <c r="B117" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C117" t="str">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D117" t="str">
-        <v>¿Las uniones se ejecutaron con la técnica y el pegamento especificados, respetando el tiempo de fraguado antes de probar?</v>
+        <v>¿El interior del encofrado está libre de recortes, alambres, aserrín y agua empozada?</v>
       </c>
       <c r="E117" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F117" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>PIS</v>
+        <v>PE</v>
       </c>
       <c r="B118" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C118" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D118" t="str">
-        <v>¿Se ejecutó la prueba de estanqueidad del tramo y se mantuvo SIN pérdida durante el tiempo especificado? (registrar resultado en observaciones)</v>
+        <v>¿El desmoldante se aplicó ANTES de montar la armadura, o sin contaminarla? (el desmoldante sobre las barras anula la adherencia con el concreto)</v>
       </c>
       <c r="E118" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F118" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>PIS</v>
+        <v>PE</v>
       </c>
       <c r="B119" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C119" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D119" t="str">
-        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
+        <v>¿Los pases y tubos de instalaciones sanitarias están según plano y fijados para no desplazarse durante el vaciado?</v>
       </c>
       <c r="E119" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F119" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>PIS</v>
+        <v>PE</v>
       </c>
       <c r="B120" t="str">
-        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C120" t="str">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D120" t="str">
-        <v>¿Los terminales expuestos y las cajas de paso quedaron taponeados para impedir el ingreso de concreto o residuos?</v>
+        <v>¿Los pases y tubos de instalaciones eléctricas están según plano y fijados para no desplazarse durante el vaciado?</v>
       </c>
       <c r="E120" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F120" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>PIE</v>
+        <v>PE</v>
       </c>
       <c r="B121" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C121" t="str">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D121" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿Los soportes y anclajes para instalaciones y estructuras metálicas están en su posición final y asegurados?</v>
       </c>
       <c r="E121" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F121" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>PIE</v>
+        <v>PE</v>
       </c>
       <c r="B122" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C122" t="str">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D122" t="str">
-        <v>¿El diámetro de la tubería corresponde al plano y el material y clase son los especificados?</v>
+        <v>¿Está definido el plazo mínimo de desencofrado para este elemento y comunicado al personal? (evita el desencofrado prematuro)</v>
       </c>
       <c r="E122" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F122" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PIE</v>
+        <v>PE</v>
       </c>
       <c r="B123" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE ENCOFRADO</v>
       </c>
       <c r="C123" t="str">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D123" t="str">
-        <v>¿Las tuberías están libres de aplastamientos y roturas, y los radios de curvatura son mayores a 6 veces el diámetro? (curvas cerradas impiden el cableado)</v>
+        <v>¿El frente cuenta con accesos seguros, barandas y protección de bordes, y la zona bajo el encofrado está señalizada?</v>
       </c>
       <c r="E123" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F123" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B124" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C124" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D124" t="str">
-        <v>¿Los accesorios son del mismo material y clase que la tubería, con marcado legible? (uniones, conectores y curvas)</v>
+        <v>¿El adhesivo está vigente (dentro de su fecha de caducidad) y se conservó según su ficha técnica?</v>
       </c>
       <c r="E124" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F124" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B125" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C125" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D125" t="str">
-        <v>¿Las cajas están en el trazo y a la altura especificada, con desviación menor a ±2 cm? (octogonales, rectangulares y de paso)</v>
+        <v>¿Se verificó con detector que la perforación NO corta armadura existente? (marcar los desvíos en observaciones)</v>
       </c>
       <c r="E125" t="str">
-        <v>Medición topográfica</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F125" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B126" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C126" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D126" t="str">
-        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
+        <v>¿La varilla quedó alineada y centrada en su posición definitiva?</v>
       </c>
       <c r="E126" t="str">
-        <v>Inspección visual</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F126" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B127" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C127" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D127" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿Se respetó el recubrimiento mínimo de 2 cm respecto al borde del concreto?</v>
       </c>
       <c r="E127" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F127" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B128" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C128" t="str">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D128" t="str">
-        <v>¿Las tuberías y accesorios están en buen estado, sin tramos expuestos a golpes durante el vaciado?</v>
+        <v>¿La perforación se ejecutó con rotomartillo y broca de carburo para concreto?</v>
       </c>
       <c r="E128" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F128" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>PIE</v>
+        <v>PAA</v>
       </c>
       <c r="B129" t="str">
-        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C129" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D129" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿El diámetro de la perforación es el que indica la ficha técnica del anclaje para esa varilla?</v>
       </c>
       <c r="E129" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F129" t="str">
-        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>PPIS</v>
+        <v>PAA</v>
       </c>
       <c r="B130" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C130" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D130" t="str">
-        <v>¿La red instalada corresponde al tipo previsto y está diferenciada en obra? (agua fría / agua caliente)</v>
+        <v>¿La perforación alcanza al menos 200 mm de profundidad en el concreto estructural, medida con sonda?</v>
       </c>
       <c r="E130" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F130" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>PPIS</v>
+        <v>PAA</v>
       </c>
       <c r="B131" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C131" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D131" t="str">
-        <v>¿El material y la clase de la red son los especificados? (PVC, PPR o acero, con marcado legible)</v>
+        <v>¿Se limpió la perforación con el ciclo completo (soplar, escobillar, soplar) hasta que sale sin polvo?</v>
       </c>
       <c r="E131" t="str">
-        <v>Verificación documental</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F131" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>PPIS</v>
+        <v>PAA</v>
       </c>
       <c r="B132" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C132" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D132" t="str">
-        <v>¿Los puntos de agua están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
+        <v>¿El adhesivo se inyectó desde el fondo hacia afuera, sin dejar burbujas ni vacíos?</v>
       </c>
       <c r="E132" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F132" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>PPIS</v>
+        <v>PAA</v>
       </c>
       <c r="B133" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C133" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D133" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿La varilla se insertó girando hasta el fondo y rebosó adhesivo, señal de que el corrugado quedó cubierto?</v>
       </c>
       <c r="E133" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F133" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>PPIS</v>
+        <v>PAA</v>
       </c>
       <c r="B134" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C134" t="str">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D134" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
+        <v>¿Se respetó el tiempo de curado según la temperatura ambiente MEDIDA? (20 °C: 24 h · 10 °C: 48 h · menos de 5 °C: 72 h)</v>
       </c>
       <c r="E134" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F134" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PPIS</v>
+        <v>PAA</v>
       </c>
       <c r="B135" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C135" t="str">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D135" t="str">
-        <v>¿El tipo y la separación entre salidas corresponden al aparato previsto, medida entre ejes? (ovalín, inodoro, urinario u otro)</v>
+        <v>¿Los anclajes se mantuvieron sin carga ni vibración durante todo el curado?</v>
       </c>
       <c r="E135" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F135" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>PPIS</v>
+        <v>PAA</v>
       </c>
       <c r="B136" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C136" t="str">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D136" t="str">
-        <v>¿Se instaló la válvula de paso donde indica el plano y queda accesible para mantenimiento?</v>
+        <v>¿Se ejecutó el ensayo de arranque en la proporción especificada y todos alcanzaron la carga de prueba? (registrar valores en observaciones)</v>
       </c>
       <c r="E136" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F136" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>PPIS</v>
+        <v>PAA</v>
       </c>
       <c r="B137" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE PERFORACIÓN Y ANCLAJE DE ACERO</v>
       </c>
       <c r="C137" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D137" t="str">
-        <v>¿El tramo pasó la prueba de presión sin pérdida durante el tiempo especificado? (registrar valor en observaciones)</v>
+        <v>¿El frente de trabajo cuenta con las protecciones de seguridad requeridas y extracción de polvo?</v>
       </c>
       <c r="E137" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F137" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>INSPECCIÓN</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B138" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C138" t="str">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D138" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Las tuberías y accesorios siguen el trazo del plano y los diámetros coinciden, verificados tramo por tramo?</v>
       </c>
       <c r="E138" t="str">
-        <v>Inspección visual</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F138" t="str">
-        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B139" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C139" t="str">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D139" t="str">
-        <v>¿Los puntos de desagüe están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
+        <v>¿El material y la clase corresponden a lo especificado, con marcado de fabricante y clase legible en la tubería?</v>
       </c>
       <c r="E139" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F139" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B140" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C140" t="str">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D140" t="str">
-        <v>¿El material y la clase de la red son los especificados? (PVC o PPR, con marcado legible)</v>
+        <v>¿El material está libre de fisuras, deformaciones por calor o golpes que comprometan la estanqueidad?</v>
       </c>
       <c r="E140" t="str">
-        <v>Verificación documental</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F140" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B141" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C141" t="str">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D141" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿La pendiente de cada tramo cumple el mínimo POR DIÁMETRO, verificada con nivel? (2": 2 % · 3": 1,5 % · 4" o mayor: 1 % — RNE IS.010)</v>
       </c>
       <c r="E141" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F141" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B142" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C142" t="str">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D142" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
+        <v>¿Las uniones se ejecutaron con la técnica y el pegamento especificados, respetando el tiempo de fraguado antes de probar?</v>
       </c>
       <c r="E142" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F142" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B143" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C143" t="str">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D143" t="str">
-        <v>¿La pendiente de los ramales cumple el mínimo especificado (≥ 1 %), verificada con nivel?</v>
+        <v>¿Se ejecutó la prueba de estanqueidad del tramo y se mantuvo SIN pérdida durante el tiempo especificado? (registrar resultado en observaciones)</v>
       </c>
       <c r="E143" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F143" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B144" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C144" t="str">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D144" t="str">
-        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
+        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
       </c>
       <c r="E144" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F144" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>PPIS</v>
+        <v>PIS</v>
       </c>
       <c r="B145" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE TUBERÍA (INSTALACIONES SANITARIAS)</v>
       </c>
       <c r="C145" t="str">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D145" t="str">
-        <v>¿Se instalaron los puntos de urinario, registro y sumidero previstos, y los registros quedan accesibles?</v>
+        <v>¿Los terminales expuestos y las cajas de paso quedaron taponeados para impedir el ingreso de concreto o residuos?</v>
       </c>
       <c r="E145" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F145" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B146" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C146" t="str">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D146" t="str">
-        <v>¿El tramo pasó la prueba de estanqueidad sin pérdida durante el tiempo especificado?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E146" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F146" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B147" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C147" t="str">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D147" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿El diámetro de la tubería corresponde al plano y el material y clase son los especificados?</v>
       </c>
       <c r="E147" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F147" t="str">
-        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B148" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C148" t="str">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D148" t="str">
-        <v>¿Los puntos de ventilación están en la ubicación y altura del plano, con desviación menor a ±2 cm?</v>
+        <v>¿Las tuberías están libres de aplastamientos y roturas, y los radios de curvatura son mayores a 6 veces el diámetro? (curvas cerradas impiden el cableado)</v>
       </c>
       <c r="E148" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F148" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B149" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C149" t="str">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D149" t="str">
-        <v>¿El material y la clase de la red son los especificados? (PVC o PPR)</v>
+        <v>¿Los accesorios son del mismo material y clase que la tubería, con marcado legible? (uniones, conectores y curvas)</v>
       </c>
       <c r="E149" t="str">
-        <v>Verificación documental</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F149" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B150" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C150" t="str">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D150" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿Las cajas están en el trazo y a la altura especificada, con desviación menor a ±2 cm? (octogonales, rectangulares y de paso)</v>
       </c>
       <c r="E150" t="str">
-        <v>Medición en campo</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F150" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B151" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C151" t="str">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D151" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
+        <v>¿Los soportes están al espaciamiento especificado y sujetan la tubería sin deformarla ni impedir su dilatación?</v>
       </c>
       <c r="E151" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F151" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B152" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C152" t="str">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D152" t="str">
-        <v>¿La ventilación remata según el plano y el recorrido queda libre de obstrucciones o tramos ahogados?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E152" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F152" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>PPIS</v>
+        <v>PIE</v>
       </c>
       <c r="B153" t="str">
-        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C153" t="str">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D153" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Las tuberías y accesorios están en buen estado, sin tramos expuestos a golpes durante el vaciado?</v>
       </c>
       <c r="E153" t="str">
         <v>Inspección visual</v>
       </c>
       <c r="F153" t="str">
-        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>PPIE</v>
+        <v>PIE</v>
       </c>
       <c r="B154" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C154" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D154" t="str">
-        <v>¿La caja equipotencial y las cajas de paso están ubicadas según el plano y quedan accesibles para su medición posterior?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E154" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F154" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>DESCRIPCIÓN DE ACTIVIDADES</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B155" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C155" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="str">
-        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
+        <v>¿La red instalada corresponde al tipo previsto y está diferenciada en obra? (agua fría / agua caliente)</v>
       </c>
       <c r="E155" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F155" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B156" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C156" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D156" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC, PPR o acero, con marcado legible)</v>
       </c>
       <c r="E156" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F156" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B157" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C157" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D157" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿Los puntos de agua están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E157" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F157" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B158" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C158" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D158" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E158" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F158" t="str">
-        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B159" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C159" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D159" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E159" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F159" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B160" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C160" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D160" t="str">
-        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
+        <v>¿El tipo y la separación entre salidas corresponden al aparato previsto, medida entre ejes? (ovalín, inodoro, urinario u otro)</v>
       </c>
       <c r="E160" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F160" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B161" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C161" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D161" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿Se instaló la válvula de paso donde indica el plano y queda accesible para mantenimiento?</v>
       </c>
       <c r="E161" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F161" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B162" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C162" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D162" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿El tramo pasó la prueba de presión sin pérdida durante el tiempo especificado? (registrar valor en observaciones)</v>
       </c>
       <c r="E162" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F162" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B163" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C163" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D163" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -3664,58 +3664,58 @@
         <v>Inspección visual</v>
       </c>
       <c r="F163" t="str">
-        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
+        <v>VERIFICACIÓN PUNTOS DE AGUA</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B164" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C164" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D164" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿Los puntos de desagüe están en la ubicación y a la ALTURA del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E164" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F164" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B165" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C165" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D165" t="str">
-        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC o PPR, con marcado legible)</v>
       </c>
       <c r="E165" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F165" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B166" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C166" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D166" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -3724,238 +3724,238 @@
         <v>Medición en campo</v>
       </c>
       <c r="F166" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B167" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C167" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D167" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E167" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F167" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B168" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C168" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D168" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿La pendiente de cada ramal cumple el mínimo POR DIÁMETRO, verificada con nivel? (2": 2 % · 3": 1,5 % · 4" o mayor: 1 % — RNE IS.010)</v>
       </c>
       <c r="E168" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F168" t="str">
-        <v>ALUMBRADO</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B169" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C169" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D169" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿El tipo de salida corresponde al aparato previsto? (ovalín, inodoro u otro)</v>
       </c>
       <c r="E169" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F169" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B170" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C170" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D170" t="str">
-        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
+        <v>¿Se instalaron los puntos de urinario, registro y sumidero previstos, y los registros quedan accesibles?</v>
       </c>
       <c r="E170" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F170" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B171" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C171" t="str">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D171" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿El tramo pasó la prueba de estanqueidad sin pérdida durante el tiempo especificado?</v>
       </c>
       <c r="E171" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F171" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B172" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C172" t="str">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D172" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E172" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F172" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE DESAGÜE</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B173" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C173" t="str">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D173" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Los puntos de ventilación están en la ubicación y altura del plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E173" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F173" t="str">
-        <v>TOMACORRIENTES</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B174" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C174" t="str">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D174" t="str">
-        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
+        <v>¿El material y la clase de la red son los especificados? (PVC o PPR)</v>
       </c>
       <c r="E174" t="str">
-        <v>Verificación contra plano</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F174" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B175" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C175" t="str">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D175" t="str">
-        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E175" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F175" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B176" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C176" t="str">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D176" t="str">
-        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E176" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F176" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B177" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C177" t="str">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D177" t="str">
-        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
+        <v>¿La ventilación remata según el plano y el recorrido queda libre de obstrucciones o tramos ahogados?</v>
       </c>
       <c r="E177" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F177" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>PPIE</v>
+        <v>PPIS</v>
       </c>
       <c r="B178" t="str">
-        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE COLOCACIÓN DE PUNTOS DE INSTALACIONES SANITARIAS</v>
       </c>
       <c r="C178" t="str">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D178" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -3964,7 +3964,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F178" t="str">
-        <v>LUZ DE EMERGENCIA</v>
+        <v>VERIFICACIÓN PUNTOS DE VENTILACIÓN</v>
       </c>
     </row>
     <row r="179">
@@ -3975,16 +3975,16 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C179" t="str">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D179" t="str">
-        <v>¿Los puntos están ubicados según el plano, con desviación menor a 2 cm? (ACI y plano de intrusión)</v>
+        <v>¿La caja equipotencial y las cajas de paso están ubicadas según el plano y quedan accesibles para su medición posterior?</v>
       </c>
       <c r="E179" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F179" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="180">
@@ -3995,7 +3995,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C180" t="str">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D180" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -4004,7 +4004,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F180" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="181">
@@ -4015,7 +4015,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C181" t="str">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D181" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -4024,7 +4024,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F181" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="182">
@@ -4035,7 +4035,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C182" t="str">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D182" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -4044,7 +4044,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F182" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="183">
@@ -4055,7 +4055,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C183" t="str">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D183" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -4064,7 +4064,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F183" t="str">
-        <v>SISTEMA DE ALARMA</v>
+        <v>VERIFICACIÓN SISTEMA DE PUESTA A TIERRA</v>
       </c>
     </row>
     <row r="184">
@@ -4075,7 +4075,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C184" t="str">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D184" t="str">
         <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
@@ -4084,7 +4084,7 @@
         <v>Verificación contra plano</v>
       </c>
       <c r="F184" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="185">
@@ -4095,7 +4095,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C185" t="str">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D185" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -4104,7 +4104,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F185" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="186">
@@ -4115,7 +4115,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C186" t="str">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D186" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -4124,7 +4124,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F186" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="187">
@@ -4135,7 +4135,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C187" t="str">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D187" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -4144,7 +4144,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F187" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="188">
@@ -4155,7 +4155,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C188" t="str">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D188" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -4164,7 +4164,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F188" t="str">
-        <v>SISTEMA DE AIRE ACONDICIONADO</v>
+        <v>VERIFICACIÓN PUNTOS DE FUERZA</v>
       </c>
     </row>
     <row r="189">
@@ -4175,7 +4175,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C189" t="str">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D189" t="str">
         <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
@@ -4184,7 +4184,7 @@
         <v>Verificación contra plano</v>
       </c>
       <c r="F189" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="190">
@@ -4195,7 +4195,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C190" t="str">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D190" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -4204,7 +4204,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F190" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="191">
@@ -4215,7 +4215,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C191" t="str">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D191" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -4224,7 +4224,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F191" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="192">
@@ -4235,7 +4235,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C192" t="str">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D192" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -4244,7 +4244,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F192" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="193">
@@ -4255,7 +4255,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C193" t="str">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D193" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -4264,7 +4264,7 @@
         <v>Inspección visual</v>
       </c>
       <c r="F193" t="str">
-        <v>DATA</v>
+        <v>ALUMBRADO</v>
       </c>
     </row>
     <row r="194">
@@ -4275,7 +4275,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C194" t="str">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D194" t="str">
         <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
@@ -4284,7 +4284,7 @@
         <v>Verificación contra plano</v>
       </c>
       <c r="F194" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="195">
@@ -4295,7 +4295,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C195" t="str">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D195" t="str">
         <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
@@ -4304,7 +4304,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F195" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="196">
@@ -4315,7 +4315,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C196" t="str">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D196" t="str">
         <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
@@ -4324,7 +4324,7 @@
         <v>Medición en campo</v>
       </c>
       <c r="F196" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="197">
@@ -4335,7 +4335,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C197" t="str">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D197" t="str">
         <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
@@ -4344,7 +4344,7 @@
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F197" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="198">
@@ -4355,7 +4355,7 @@
         <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C198" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D198" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -4364,198 +4364,198 @@
         <v>Inspección visual</v>
       </c>
       <c r="F198" t="str">
-        <v>CIRCUITO CERRADO TV - CCTV</v>
+        <v>TOMACORRIENTES</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B199" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C199" t="str">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D199" t="str">
-        <v>¿La zanja está en el trazo del plano y libre de interferencias con otras redes? (registrar cruces en observaciones)</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E199" t="str">
         <v>Verificación contra plano</v>
       </c>
       <c r="F199" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B200" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C200" t="str">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D200" t="str">
-        <v>¿El ancho y la PROFUNDIDAD de la zanja cumplen el detalle, medidos cada tramo? (la profundidad protege la red del tránsito superior)</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E200" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F200" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B201" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C201" t="str">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D201" t="str">
-        <v>¿La cama de arena tiene el espesor indicado y está libre de piedras que puedan dañar el ducto?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E201" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F201" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B202" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C202" t="str">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D202" t="str">
-        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E202" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F202" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B203" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C203" t="str">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D203" t="str">
-        <v>¿La cantidad de tuberías es exactamente la del plano, contadas una a una en el tramo?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E203" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F203" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>LUZ DE EMERGENCIA</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B204" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C204" t="str">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D204" t="str">
-        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
+        <v>¿Los puntos están ubicados según el plano, con desviación menor a 2 cm? (ACI y plano de intrusión)</v>
       </c>
       <c r="E204" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F204" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B205" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C205" t="str">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D205" t="str">
-        <v>¿Se verificó que pasa la guía por cada ducto ANTES de tapar la zanja?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E205" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F205" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B206" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C206" t="str">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D206" t="str">
-        <v>¿La cinta o malla de advertencia está a la altura del detalle sobre el ducto, medida antes de completar el relleno? (evita el corte accidental en excavaciones futuras)</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E206" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F206" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B207" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C207" t="str">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D207" t="str">
-        <v>¿El relleno y la compactación se ejecutaron por capas según especificación, sin dañar el ducto?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E207" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F207" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B208" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C208" t="str">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D208" t="str">
         <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
@@ -4564,787 +4564,787 @@
         <v>Inspección visual</v>
       </c>
       <c r="F208" t="str">
-        <v>TRABAJOS EN TERRENO</v>
+        <v>SISTEMA DE ALARMA</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B209" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C209" t="str">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D209" t="str">
-        <v>¿El diámetro y la cantidad de tuberías que llegan al buzón corresponden al plano, contadas una a una?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E209" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F209" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B210" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C210" t="str">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D210" t="str">
-        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E210" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F210" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B211" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C211" t="str">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D211" t="str">
-        <v>¿Se respeta la distancia mínima entre el NPT y la tubería, medida en el punto más desfavorable del tramo?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E211" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F211" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B212" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C212" t="str">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D212" t="str">
-        <v>¿Las entradas al buzón quedaron selladas para impedir el ingreso de agua o tierra a los ductos?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E212" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F212" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B213" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C213" t="str">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D213" t="str">
-        <v>¿El sumidero del buzón drena sin empozar, verificado vertiendo agua?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E213" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F213" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>SISTEMA DE AIRE ACONDICIONADO</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B214" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C214" t="str">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D214" t="str">
-        <v>¿La tapa instalada es de la clase especificada para el tránsito de esa zona y queda enrasada con el nivel de piso?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E214" t="str">
-        <v>Verificación documental</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F214" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B215" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C215" t="str">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D215" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E215" t="str">
-        <v>Inspección visual</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F215" t="str">
-        <v>TRABAJOS EN BUZÓN</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B216" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C216" t="str">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D216" t="str">
-        <v>¿El trazo y replanteo de la red colgada fue verificado topográficamente, con desviación menor a ±2 cm?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E216" t="str">
-        <v>Medición topográfica</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F216" t="str">
-        <v>REDES COLGADAS</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B217" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C217" t="str">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D217" t="str">
-        <v>¿El diámetro y la cantidad de tuberías o bandejas corresponden al plano, contadas una a una?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E217" t="str">
-        <v>Medición en campo</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F217" t="str">
-        <v>REDES COLGADAS</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B218" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C218" t="str">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D218" t="str">
-        <v>¿La separación entre tuberías o bandejas cumple el detalle, medida en al menos 3 puntos?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E218" t="str">
-        <v>Medición en campo</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F218" t="str">
-        <v>REDES COLGADAS</v>
+        <v>DATA</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B219" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C219" t="str">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D219" t="str">
-        <v>¿Se respeta la distancia mínima entre el NPT y la tubería o bandeja, medida en el punto más desfavorable?</v>
+        <v>¿Los puntos están en la ubicación del plano, con desviación menor a 2 cm respecto al eje de referencia?</v>
       </c>
       <c r="E219" t="str">
-        <v>Medición en campo</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F219" t="str">
-        <v>REDES COLGADAS</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B220" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C220" t="str">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D220" t="str">
-        <v>¿Los soportes están al espaciamiento especificado y anclados a elemento estructural, no a falso cielo ni a tabique?</v>
+        <v>¿El diámetro, el recorrido, la caja y la ALTURA corresponden al plano, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E220" t="str">
         <v>Medición en campo</v>
       </c>
       <c r="F220" t="str">
-        <v>REDES COLGADAS</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B221" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C221" t="str">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D221" t="str">
-        <v>¿Se verificó que pasa la guía por cada ducto antes de cerrar el falso cielo?</v>
+        <v>¿La cantidad de puntos de salida es EXACTAMENTE la del plano? (un punto de menos obliga a picar después)</v>
       </c>
       <c r="E221" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F221" t="str">
-        <v>REDES COLGADAS</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>PRE</v>
+        <v>PPIE</v>
       </c>
       <c r="B222" t="str">
-        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C222" t="str">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D222" t="str">
-        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
+        <v>¿Los ductos quedaron con alambre guía y los extremos tapados, y se verificó que pasa la guía entre cajas?</v>
       </c>
       <c r="E222" t="str">
-        <v>Inspección visual</v>
+        <v>Prueba de funcionamiento</v>
       </c>
       <c r="F222" t="str">
-        <v>REDES COLGADAS</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>PDA</v>
+        <v>PPIE</v>
       </c>
       <c r="B223" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE PUNTOS EN INSTALACIONES ELÉCTRICAS</v>
       </c>
       <c r="C223" t="str">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D223" t="str">
-        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E223" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F223" t="str">
-        <v>AMBIENTE 1</v>
+        <v>CIRCUITO CERRADO TV - CCTV</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B224" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C224" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D224" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿La zanja está en el trazo del plano y libre de interferencias con otras redes? (registrar cruces en observaciones)</v>
       </c>
       <c r="E224" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F224" t="str">
-        <v>AMBIENTE 1</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B225" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C225" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D225" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿El ancho y la PROFUNDIDAD de la zanja cumplen el detalle, medidos cada tramo? (la profundidad protege la red del tránsito superior)</v>
       </c>
       <c r="E225" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F225" t="str">
-        <v>AMBIENTE 1</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B226" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C226" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D226" t="str">
-        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+        <v>¿La cama de arena tiene el espesor indicado y está libre de piedras que puedan dañar el ducto?</v>
       </c>
       <c r="E226" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F226" t="str">
-        <v>AMBIENTE 1</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B227" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C227" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D227" t="str">
-        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+        <v>¿El diámetro y el recorrido de la tubería corresponden al plano, sin reducciones ni desvíos no autorizados?</v>
       </c>
       <c r="E227" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F227" t="str">
-        <v>AMBIENTE 1</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B228" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C228" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D228" t="str">
-        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+        <v>¿La cantidad de tuberías es exactamente la del plano, contadas una a una en el tramo?</v>
       </c>
       <c r="E228" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F228" t="str">
-        <v>AMBIENTE 1</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B229" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C229" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D229" t="str">
-        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
       </c>
       <c r="E229" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F229" t="str">
-        <v>AMBIENTE 2</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B230" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C230" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D230" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿Se verificó que pasa la guía por cada ducto ANTES de tapar la zanja?</v>
       </c>
       <c r="E230" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F230" t="str">
-        <v>AMBIENTE 2</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B231" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C231" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D231" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿La cinta o malla de advertencia está a la altura del detalle sobre el ducto, medida antes de completar el relleno? (evita el corte accidental en excavaciones futuras)</v>
       </c>
       <c r="E231" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F231" t="str">
-        <v>AMBIENTE 2</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B232" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C232" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D232" t="str">
-        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+        <v>¿El relleno y la compactación se ejecutaron por capas según especificación, sin dañar el ducto?</v>
       </c>
       <c r="E232" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F232" t="str">
-        <v>AMBIENTE 2</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B233" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C233" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D233" t="str">
-        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E233" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F233" t="str">
-        <v>AMBIENTE 2</v>
+        <v>TRABAJOS EN TERRENO</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B234" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C234" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D234" t="str">
-        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+        <v>¿El diámetro y la cantidad de tuberías que llegan al buzón corresponden al plano, contadas una a una?</v>
       </c>
       <c r="E234" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F234" t="str">
-        <v>AMBIENTE 2</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B235" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C235" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D235" t="str">
-        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿La separación entre tuberías cumple el detalle, medida en al menos 3 puntos del tramo?</v>
       </c>
       <c r="E235" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F235" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B236" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C236" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D236" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿Se respeta la distancia mínima entre el NPT y la tubería, medida en el punto más desfavorable del tramo?</v>
       </c>
       <c r="E236" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F236" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B237" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C237" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D237" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿Las entradas al buzón quedaron selladas para impedir el ingreso de agua o tierra a los ductos?</v>
       </c>
       <c r="E237" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F237" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B238" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C238" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D238" t="str">
-        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+        <v>¿El sumidero del buzón drena sin empozar, verificado vertiendo agua?</v>
       </c>
       <c r="E238" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F238" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B239" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C239" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D239" t="str">
-        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+        <v>¿La tapa instalada es de la clase especificada para el tránsito de esa zona y queda enrasada con el nivel de piso?</v>
       </c>
       <c r="E239" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Verificación documental</v>
       </c>
       <c r="F239" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B240" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C240" t="str">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D240" t="str">
-        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E240" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F240" t="str">
-        <v>AMBIENTE 3</v>
+        <v>TRABAJOS EN BUZÓN</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B241" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C241" t="str">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D241" t="str">
-        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿El trazo y replanteo de la red colgada fue verificado topográficamente, con desviación menor a ±2 cm?</v>
       </c>
       <c r="E241" t="str">
-        <v>Verificación contra plano</v>
+        <v>Medición topográfica</v>
       </c>
       <c r="F241" t="str">
-        <v>AMBIENTE 4</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B242" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C242" t="str">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D242" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿El diámetro y la cantidad de tuberías o bandejas corresponden al plano, contadas una a una?</v>
       </c>
       <c r="E242" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F242" t="str">
-        <v>AMBIENTE 4</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B243" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C243" t="str">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D243" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿La separación entre tuberías o bandejas cumple el detalle, medida en al menos 3 puntos?</v>
       </c>
       <c r="E243" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F243" t="str">
-        <v>AMBIENTE 4</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B244" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C244" t="str">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D244" t="str">
-        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+        <v>¿Se respeta la distancia mínima entre el NPT y la tubería o bandeja, medida en el punto más desfavorable?</v>
       </c>
       <c r="E244" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F244" t="str">
-        <v>AMBIENTE 4</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B245" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C245" t="str">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D245" t="str">
-        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+        <v>¿Los soportes están al espaciamiento especificado y anclados a elemento estructural, no a falso cielo ni a tabique?</v>
       </c>
       <c r="E245" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Medición en campo</v>
       </c>
       <c r="F245" t="str">
-        <v>AMBIENTE 4</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B246" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C246" t="str">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D246" t="str">
-        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+        <v>¿Se verificó que pasa la guía por cada ducto antes de cerrar el falso cielo?</v>
       </c>
       <c r="E246" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F246" t="str">
-        <v>AMBIENTE 4</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>PDA</v>
+        <v>PRE</v>
       </c>
       <c r="B247" t="str">
-        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+        <v>PROTOCOLO DE REDES ELÉCTRICAS</v>
       </c>
       <c r="C247" t="str">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D247" t="str">
-        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+        <v>¿El área quedó libre de residuos, recortes y material sobrante que puedan obstruir el trabajo posterior?</v>
       </c>
       <c r="E247" t="str">
-        <v>Verificación contra plano</v>
+        <v>Inspección visual</v>
       </c>
       <c r="F247" t="str">
-        <v>AMBIENTE 5</v>
+        <v>REDES COLGADAS</v>
       </c>
     </row>
     <row r="248">
@@ -5355,16 +5355,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C248" t="str">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D248" t="str">
-        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
       </c>
       <c r="E248" t="str">
-        <v>Prueba de funcionamiento</v>
+        <v>Verificación contra plano</v>
       </c>
       <c r="F248" t="str">
-        <v>AMBIENTE 5</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="249">
@@ -5375,16 +5375,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C249" t="str">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D249" t="str">
-        <v>¿La sirena se activa al operar el detector de humo?</v>
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
       </c>
       <c r="E249" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F249" t="str">
-        <v>AMBIENTE 5</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="250">
@@ -5395,16 +5395,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C250" t="str">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D250" t="str">
-        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+        <v>¿La sirena se activa al operar el detector de humo?</v>
       </c>
       <c r="E250" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F250" t="str">
-        <v>AMBIENTE 5</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="251">
@@ -5415,16 +5415,16 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C251" t="str">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D251" t="str">
-        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
       </c>
       <c r="E251" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F251" t="str">
-        <v>AMBIENTE 5</v>
+        <v>AMBIENTE 1</v>
       </c>
     </row>
     <row r="252">
@@ -5435,21 +5435,521 @@
         <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
       </c>
       <c r="C252" t="str">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D252" t="str">
-        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
       </c>
       <c r="E252" t="str">
         <v>Prueba de funcionamiento</v>
       </c>
       <c r="F252" t="str">
+        <v>AMBIENTE 1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B253" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C253" t="str">
+        <v>6</v>
+      </c>
+      <c r="D253" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E253" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F253" t="str">
+        <v>AMBIENTE 1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B254" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C254" t="str">
+        <v>7</v>
+      </c>
+      <c r="D254" t="str">
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E254" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F254" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B255" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C255" t="str">
+        <v>8</v>
+      </c>
+      <c r="D255" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E255" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F255" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B256" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C256" t="str">
+        <v>9</v>
+      </c>
+      <c r="D256" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E256" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F256" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B257" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C257" t="str">
+        <v>10</v>
+      </c>
+      <c r="D257" t="str">
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+      </c>
+      <c r="E257" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F257" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B258" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C258" t="str">
+        <v>11</v>
+      </c>
+      <c r="D258" t="str">
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+      </c>
+      <c r="E258" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F258" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B259" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C259" t="str">
+        <v>12</v>
+      </c>
+      <c r="D259" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E259" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F259" t="str">
+        <v>AMBIENTE 2</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B260" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C260" t="str">
+        <v>13</v>
+      </c>
+      <c r="D260" t="str">
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E260" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F260" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B261" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C261" t="str">
+        <v>14</v>
+      </c>
+      <c r="D261" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E261" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F261" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B262" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C262" t="str">
+        <v>15</v>
+      </c>
+      <c r="D262" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E262" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F262" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B263" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C263" t="str">
+        <v>16</v>
+      </c>
+      <c r="D263" t="str">
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+      </c>
+      <c r="E263" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F263" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B264" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C264" t="str">
+        <v>17</v>
+      </c>
+      <c r="D264" t="str">
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+      </c>
+      <c r="E264" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F264" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B265" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C265" t="str">
+        <v>18</v>
+      </c>
+      <c r="D265" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E265" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F265" t="str">
+        <v>AMBIENTE 3</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B266" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C266" t="str">
+        <v>19</v>
+      </c>
+      <c r="D266" t="str">
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E266" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F266" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B267" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C267" t="str">
+        <v>20</v>
+      </c>
+      <c r="D267" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E267" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F267" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B268" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C268" t="str">
+        <v>21</v>
+      </c>
+      <c r="D268" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E268" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F268" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B269" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C269" t="str">
+        <v>22</v>
+      </c>
+      <c r="D269" t="str">
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+      </c>
+      <c r="E269" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F269" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B270" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C270" t="str">
+        <v>23</v>
+      </c>
+      <c r="D270" t="str">
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+      </c>
+      <c r="E270" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F270" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B271" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C271" t="str">
+        <v>24</v>
+      </c>
+      <c r="D271" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E271" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F271" t="str">
+        <v>AMBIENTE 4</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B272" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C272" t="str">
+        <v>25</v>
+      </c>
+      <c r="D272" t="str">
+        <v>¿Los dispositivos están ubicados según el plano, respetando las distancias a muros y difusores de aire? (sensor de temperatura, detector de humo, luz estroboscópica, estación manual y sirena)</v>
+      </c>
+      <c r="E272" t="str">
+        <v>Verificación contra plano</v>
+      </c>
+      <c r="F272" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B273" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C273" t="str">
+        <v>26</v>
+      </c>
+      <c r="D273" t="str">
+        <v>¿La sirena se activa al operar el sensor de temperatura?</v>
+      </c>
+      <c r="E273" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F273" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B274" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C274" t="str">
+        <v>27</v>
+      </c>
+      <c r="D274" t="str">
+        <v>¿La sirena se activa al operar el detector de humo?</v>
+      </c>
+      <c r="E274" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F274" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B275" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C275" t="str">
+        <v>28</v>
+      </c>
+      <c r="D275" t="str">
+        <v>¿El tablero identifica la zona CORRECTA al activarse el dispositivo? (una alarma sin zona correcta retrasa la respuesta)</v>
+      </c>
+      <c r="E275" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F275" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B276" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C276" t="str">
+        <v>29</v>
+      </c>
+      <c r="D276" t="str">
+        <v>¿La alarma es audible y la luz estroboscópica visible desde todo el ambiente, incluso con las puertas cerradas?</v>
+      </c>
+      <c r="E276" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F276" t="str">
+        <v>AMBIENTE 5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>PDA</v>
+      </c>
+      <c r="B277" t="str">
+        <v>PROTOCOLO DE DETECCIÓN Y ALARMAS CONTRA INCENDIO</v>
+      </c>
+      <c r="C277" t="str">
+        <v>30</v>
+      </c>
+      <c r="D277" t="str">
+        <v>¿El sistema siguió operando al simular corte de energía, con la autonomía de respaldo especificada?</v>
+      </c>
+      <c r="E277" t="str">
+        <v>Prueba de funcionamiento</v>
+      </c>
+      <c r="F277" t="str">
         <v>AMBIENTE 5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F252"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F277"/>
   </ignoredErrors>
 </worksheet>
 </file>